--- a/iLgs/App_Data/CustodianVehiclesTemplate.xlsx
+++ b/iLgs/App_Data/CustodianVehiclesTemplate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/New folder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{C24A2B6E-C141-4441-9F51-293C5BCBCD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6D0B644-6035-4346-91AD-9258584C999A}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{C24A2B6E-C141-4441-9F51-293C5BCBCD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE6E18DE-8BCD-4932-864B-1BA9B65FB6FB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{49C2EA6D-0E15-4E51-9FB1-ADBE484D14AF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
   <si>
     <t>Custodian
 Item
@@ -220,6 +220,18 @@
   </si>
   <si>
     <t xml:space="preserve">Department : </t>
+  </si>
+  <si>
+    <t>Certified Correct by:</t>
+  </si>
+  <si>
+    <t>Signature over Printed Name</t>
+  </si>
+  <si>
+    <t>Custodian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Assistant to the Custodian</t>
   </si>
 </sst>
 </file>
@@ -230,7 +242,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -289,6 +301,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri  "/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri  "/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -304,7 +325,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -680,6 +701,24 @@
       <bottom style="thick">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -687,7 +726,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -737,16 +776,94 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -761,33 +878,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -806,71 +896,34 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -888,6 +941,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1187,21 +1244,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00C28830-284B-4C5E-B18C-8421255AA9A0}">
-  <dimension ref="A1:AR9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AR15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="13.44140625" customWidth="1"/>
     <col min="2" max="2" width="18.88671875" customWidth="1"/>
     <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.44140625" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.5546875" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" customWidth="1"/>
     <col min="7" max="7" width="10.88671875" customWidth="1"/>
     <col min="8" max="8" width="9.77734375" customWidth="1"/>
     <col min="9" max="9" width="9.21875" customWidth="1"/>
     <col min="10" max="10" width="7.33203125" customWidth="1"/>
-    <col min="11" max="11" width="18.77734375" customWidth="1"/>
-    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="11" max="12" width="15" customWidth="1"/>
     <col min="13" max="13" width="12.33203125" customWidth="1"/>
     <col min="14" max="14" width="11.5546875" customWidth="1"/>
     <col min="16" max="16" width="14.6640625" customWidth="1"/>
@@ -1223,7 +1279,7 @@
     <col min="42" max="42" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:44" ht="20.399999999999999" customHeight="1">
       <c r="A1" s="19"/>
       <c r="B1" s="20"/>
       <c r="C1" s="1"/>
@@ -1267,7 +1323,7 @@
       <c r="AP1" s="2"/>
       <c r="AQ1" s="2"/>
     </row>
-    <row r="2" spans="1:44" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:44" ht="15.6">
       <c r="A2" s="19" t="s">
         <v>47</v>
       </c>
@@ -1313,7 +1369,7 @@
       <c r="AP2" s="2"/>
       <c r="AQ2" s="2"/>
     </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:44">
       <c r="A3" s="4"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -1357,7 +1413,7 @@
       <c r="AP3" s="2"/>
       <c r="AQ3" s="2"/>
     </row>
-    <row r="4" spans="1:44" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:44" ht="15.6">
       <c r="A4" s="21" t="s">
         <v>50</v>
       </c>
@@ -1377,8 +1433,8 @@
       <c r="R4" s="15"/>
       <c r="U4" s="12"/>
       <c r="Z4" s="13"/>
-      <c r="AG4" s="25"/>
-      <c r="AH4" s="25"/>
+      <c r="AG4" s="52"/>
+      <c r="AH4" s="52"/>
       <c r="AI4" s="15"/>
       <c r="AJ4" s="15"/>
       <c r="AK4" s="2"/>
@@ -1389,7 +1445,7 @@
       <c r="AP4" s="2"/>
       <c r="AQ4" s="2"/>
     </row>
-    <row r="5" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:44" ht="15" thickBot="1">
       <c r="A5" s="7"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1434,245 +1490,340 @@
       <c r="AP5" s="2"/>
       <c r="AQ5" s="2"/>
     </row>
-    <row r="6" spans="1:44" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26" t="s">
+    <row r="6" spans="1:44" ht="15" customHeight="1" thickTop="1">
+      <c r="A6" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="33" t="s">
+      <c r="C6" s="57"/>
+      <c r="D6" s="28" t="s">
         <v>1</v>
       </c>
       <c r="E6" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="39" t="s">
+      <c r="F6" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="42" t="s">
+      <c r="G6" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="43"/>
-      <c r="L6" s="43"/>
-      <c r="M6" s="43"/>
-      <c r="N6" s="43"/>
-      <c r="O6" s="44"/>
-      <c r="P6" s="42" t="s">
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="62"/>
+      <c r="P6" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="Q6" s="43"/>
-      <c r="R6" s="43"/>
-      <c r="S6" s="43"/>
-      <c r="T6" s="43"/>
-      <c r="U6" s="44"/>
-      <c r="V6" s="45" t="s">
+      <c r="Q6" s="61"/>
+      <c r="R6" s="61"/>
+      <c r="S6" s="61"/>
+      <c r="T6" s="61"/>
+      <c r="U6" s="62"/>
+      <c r="V6" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="W6" s="26" t="s">
+      <c r="W6" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="X6" s="26" t="s">
+      <c r="X6" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="Y6" s="48" t="s">
+      <c r="Y6" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="Z6" s="51" t="s">
+      <c r="Z6" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="AA6" s="33" t="s">
+      <c r="AA6" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="AB6" s="33" t="s">
+      <c r="AB6" s="28" t="s">
         <v>12</v>
       </c>
       <c r="AC6" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="AD6" s="65" t="s">
+      <c r="AD6" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="AE6" s="66"/>
-      <c r="AF6" s="67"/>
-      <c r="AG6" s="48" t="s">
+      <c r="AE6" s="39"/>
+      <c r="AF6" s="40"/>
+      <c r="AG6" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="AH6" s="68" t="s">
+      <c r="AH6" s="41" t="s">
         <v>15</v>
       </c>
       <c r="AI6" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="AJ6" s="39" t="s">
+      <c r="AJ6" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="AK6" s="26" t="s">
+      <c r="AK6" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="AL6" s="33" t="s">
+      <c r="AL6" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="AM6" s="33" t="s">
+      <c r="AM6" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="AN6" s="33" t="s">
+      <c r="AN6" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="AO6" s="33" t="s">
+      <c r="AO6" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="AP6" s="33" t="s">
+      <c r="AP6" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="AQ6" s="48" t="s">
+      <c r="AQ6" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="AR6" s="48" t="s">
+      <c r="AR6" s="31" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A7" s="27"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="34"/>
+    <row r="7" spans="1:44">
+      <c r="A7" s="47"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="29"/>
       <c r="E7" s="37"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="54" t="s">
+      <c r="F7" s="50"/>
+      <c r="G7" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="56" t="s">
+      <c r="H7" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="56" t="s">
+      <c r="I7" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="J7" s="56" t="s">
+      <c r="J7" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="K7" s="56" t="s">
+      <c r="K7" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="L7" s="56" t="s">
+      <c r="L7" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="M7" s="56" t="s">
+      <c r="M7" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="N7" s="56" t="s">
+      <c r="N7" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="O7" s="57" t="s">
+      <c r="O7" s="70" t="s">
         <v>33</v>
       </c>
-      <c r="P7" s="58" t="s">
+      <c r="P7" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="Q7" s="56" t="s">
+      <c r="Q7" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="R7" s="56" t="s">
+      <c r="R7" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="S7" s="59" t="s">
+      <c r="S7" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="T7" s="60"/>
-      <c r="U7" s="61" t="s">
+      <c r="T7" s="69"/>
+      <c r="U7" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="V7" s="46"/>
-      <c r="W7" s="27"/>
-      <c r="X7" s="27"/>
-      <c r="Y7" s="49"/>
-      <c r="Z7" s="52"/>
-      <c r="AA7" s="34"/>
-      <c r="AB7" s="34"/>
+      <c r="V7" s="64"/>
+      <c r="W7" s="47"/>
+      <c r="X7" s="47"/>
+      <c r="Y7" s="32"/>
+      <c r="Z7" s="54"/>
+      <c r="AA7" s="29"/>
+      <c r="AB7" s="29"/>
       <c r="AC7" s="37"/>
-      <c r="AD7" s="63" t="s">
+      <c r="AD7" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="AE7" s="64" t="s">
+      <c r="AE7" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="AF7" s="63" t="s">
+      <c r="AF7" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="AG7" s="49"/>
-      <c r="AH7" s="69"/>
+      <c r="AG7" s="32"/>
+      <c r="AH7" s="42"/>
       <c r="AI7" s="37"/>
-      <c r="AJ7" s="40"/>
-      <c r="AK7" s="27"/>
-      <c r="AL7" s="34"/>
-      <c r="AM7" s="34"/>
-      <c r="AN7" s="34"/>
-      <c r="AO7" s="34"/>
-      <c r="AP7" s="34"/>
-      <c r="AQ7" s="49"/>
-      <c r="AR7" s="49"/>
+      <c r="AJ7" s="50"/>
+      <c r="AK7" s="47"/>
+      <c r="AL7" s="29"/>
+      <c r="AM7" s="29"/>
+      <c r="AN7" s="29"/>
+      <c r="AO7" s="29"/>
+      <c r="AP7" s="29"/>
+      <c r="AQ7" s="32"/>
+      <c r="AR7" s="32"/>
     </row>
-    <row r="8" spans="1:44" ht="31.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="28"/>
+    <row r="8" spans="1:44" ht="31.2" customHeight="1" thickBot="1">
+      <c r="A8" s="48"/>
       <c r="B8" s="22" t="s">
         <v>42</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="35"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="35"/>
-      <c r="M8" s="35"/>
-      <c r="N8" s="35"/>
-      <c r="O8" s="41"/>
-      <c r="P8" s="28"/>
-      <c r="Q8" s="35"/>
-      <c r="R8" s="35"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="51"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="30"/>
+      <c r="R8" s="30"/>
       <c r="S8" s="23" t="s">
         <v>44</v>
       </c>
       <c r="T8" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="U8" s="62"/>
-      <c r="V8" s="47"/>
-      <c r="W8" s="28"/>
-      <c r="X8" s="28"/>
-      <c r="Y8" s="50"/>
-      <c r="Z8" s="53"/>
-      <c r="AA8" s="35"/>
-      <c r="AB8" s="35"/>
-      <c r="AC8" s="38"/>
-      <c r="AD8" s="35"/>
-      <c r="AE8" s="38"/>
-      <c r="AF8" s="35"/>
-      <c r="AG8" s="50"/>
-      <c r="AH8" s="55"/>
-      <c r="AI8" s="38"/>
-      <c r="AJ8" s="41"/>
-      <c r="AK8" s="28"/>
-      <c r="AL8" s="35"/>
-      <c r="AM8" s="35"/>
-      <c r="AN8" s="35"/>
-      <c r="AO8" s="35"/>
-      <c r="AP8" s="35"/>
-      <c r="AQ8" s="50"/>
-      <c r="AR8" s="50"/>
+      <c r="U8" s="67"/>
+      <c r="V8" s="65"/>
+      <c r="W8" s="48"/>
+      <c r="X8" s="48"/>
+      <c r="Y8" s="33"/>
+      <c r="Z8" s="55"/>
+      <c r="AA8" s="30"/>
+      <c r="AB8" s="30"/>
+      <c r="AC8" s="35"/>
+      <c r="AD8" s="30"/>
+      <c r="AE8" s="35"/>
+      <c r="AF8" s="30"/>
+      <c r="AG8" s="33"/>
+      <c r="AH8" s="43"/>
+      <c r="AI8" s="35"/>
+      <c r="AJ8" s="51"/>
+      <c r="AK8" s="48"/>
+      <c r="AL8" s="30"/>
+      <c r="AM8" s="30"/>
+      <c r="AN8" s="30"/>
+      <c r="AO8" s="30"/>
+      <c r="AP8" s="30"/>
+      <c r="AQ8" s="33"/>
+      <c r="AR8" s="33"/>
     </row>
-    <row r="9" spans="1:44" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:44" ht="15" thickTop="1"/>
+    <row r="11" spans="1:44">
+      <c r="B11" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+    </row>
+    <row r="12" spans="1:44">
+      <c r="B12" s="27"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+    </row>
+    <row r="13" spans="1:44">
+      <c r="B13" s="25"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="25"/>
+    </row>
+    <row r="14" spans="1:44">
+      <c r="B14" s="25"/>
+      <c r="C14" s="73" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="73" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" s="73"/>
+      <c r="I14" s="73"/>
+      <c r="J14" s="73"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="25"/>
+    </row>
+    <row r="15" spans="1:44">
+      <c r="B15" s="25"/>
+      <c r="C15" s="74" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="74"/>
+      <c r="E15" s="74"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="74" t="s">
+        <v>54</v>
+      </c>
+      <c r="H15" s="74"/>
+      <c r="I15" s="74"/>
+      <c r="J15" s="74"/>
+      <c r="K15" s="74"/>
+      <c r="L15" s="25"/>
+    </row>
   </sheetData>
-  <mergeCells count="46">
+  <mergeCells count="50">
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="G14:K14"/>
+    <mergeCell ref="G15:K15"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B6:C7"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="AG4:AH4"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="AB6:AB8"/>
     <mergeCell ref="AR6:AR8"/>
     <mergeCell ref="AC6:AC8"/>
     <mergeCell ref="AD6:AF6"/>
@@ -1686,39 +1837,23 @@
     <mergeCell ref="AK6:AK8"/>
     <mergeCell ref="AL6:AL8"/>
     <mergeCell ref="AM6:AM8"/>
+    <mergeCell ref="AJ6:AJ8"/>
     <mergeCell ref="AN6:AN8"/>
     <mergeCell ref="AP6:AP8"/>
     <mergeCell ref="AQ6:AQ8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H8"/>
     <mergeCell ref="I7:I8"/>
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="K7:K8"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="N7:N8"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="Q7:Q8"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="AG4:AH4"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B6:C7"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
     <mergeCell ref="G6:O6"/>
     <mergeCell ref="P6:U6"/>
     <mergeCell ref="V6:V8"/>
     <mergeCell ref="W6:W8"/>
     <mergeCell ref="X6:X8"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="AB6:AB8"/>
     <mergeCell ref="U7:U8"/>
+    <mergeCell ref="Q7:Q8"/>
+    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="L7:L8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1727,7 +1862,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4FF280D-8901-47F7-A49B-A58CF91F8AB2}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1736,7 +1871,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E66AD95-083B-4AB7-B7E6-04F3E141ECAC}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/iLgs/App_Data/CustodianVehiclesTemplate.xlsx
+++ b/iLgs/App_Data/CustodianVehiclesTemplate.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/New folder/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Templates New/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{C24A2B6E-C141-4441-9F51-293C5BCBCD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE6E18DE-8BCD-4932-864B-1BA9B65FB6FB}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="8_{C24A2B6E-C141-4441-9F51-293C5BCBCD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AE0AA3C-FFEF-448B-99FC-C19C75DFA131}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{49C2EA6D-0E15-4E51-9FB1-ADBE484D14AF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
   <si>
     <t>Custodian
 Item
@@ -232,6 +232,9 @@
   </si>
   <si>
     <t xml:space="preserve">  Assistant to the Custodian</t>
+  </si>
+  <si>
+    <t>Verified by:</t>
   </si>
 </sst>
 </file>
@@ -726,7 +729,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -740,21 +743,11 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -766,7 +759,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -776,152 +768,156 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1247,41 +1243,46 @@
   <dimension ref="A1:AR15"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" customWidth="1"/>
-    <col min="2" max="2" width="18.88671875" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.44140625" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" customWidth="1"/>
-    <col min="6" max="6" width="24.88671875" customWidth="1"/>
-    <col min="7" max="7" width="10.88671875" customWidth="1"/>
-    <col min="8" max="8" width="9.77734375" customWidth="1"/>
-    <col min="9" max="9" width="9.21875" customWidth="1"/>
-    <col min="10" max="10" width="7.33203125" customWidth="1"/>
-    <col min="11" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="12.33203125" customWidth="1"/>
-    <col min="14" max="14" width="11.5546875" customWidth="1"/>
-    <col min="16" max="16" width="14.6640625" customWidth="1"/>
-    <col min="17" max="17" width="12.33203125" customWidth="1"/>
-    <col min="18" max="18" width="17.33203125" customWidth="1"/>
-    <col min="19" max="19" width="11.5546875" customWidth="1"/>
-    <col min="20" max="20" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.44140625" customWidth="1"/>
-    <col min="25" max="25" width="13.44140625" customWidth="1"/>
-    <col min="26" max="26" width="11.21875" customWidth="1"/>
-    <col min="27" max="27" width="11.5546875" customWidth="1"/>
-    <col min="28" max="28" width="13.77734375" customWidth="1"/>
-    <col min="29" max="29" width="11.109375" customWidth="1"/>
-    <col min="30" max="30" width="13.44140625" customWidth="1"/>
-    <col min="31" max="31" width="14.33203125" customWidth="1"/>
-    <col min="32" max="32" width="19.21875" customWidth="1"/>
-    <col min="33" max="33" width="22.88671875" customWidth="1"/>
-    <col min="41" max="41" width="11.109375" customWidth="1"/>
-    <col min="42" max="42" width="11" customWidth="1"/>
+    <col min="1" max="1" width="13.44140625" style="62" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" style="62" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" style="62" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" style="62" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" style="62" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" style="62" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" style="62" customWidth="1"/>
+    <col min="8" max="8" width="9.77734375" style="62" customWidth="1"/>
+    <col min="9" max="9" width="9.21875" style="62" customWidth="1"/>
+    <col min="10" max="10" width="7.33203125" style="62" customWidth="1"/>
+    <col min="11" max="12" width="15" style="62" customWidth="1"/>
+    <col min="13" max="13" width="12.33203125" style="62" customWidth="1"/>
+    <col min="14" max="14" width="11.5546875" style="62" customWidth="1"/>
+    <col min="15" max="15" width="8.88671875" style="62"/>
+    <col min="16" max="16" width="14.6640625" style="62" customWidth="1"/>
+    <col min="17" max="17" width="12.33203125" style="62" customWidth="1"/>
+    <col min="18" max="18" width="17.33203125" style="62" customWidth="1"/>
+    <col min="19" max="19" width="11.5546875" style="62" customWidth="1"/>
+    <col min="20" max="20" width="10.6640625" style="62" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.88671875" style="62"/>
+    <col min="22" max="22" width="12.44140625" style="62" customWidth="1"/>
+    <col min="23" max="24" width="8.88671875" style="62"/>
+    <col min="25" max="25" width="13.44140625" style="62" customWidth="1"/>
+    <col min="26" max="26" width="11.21875" style="62" customWidth="1"/>
+    <col min="27" max="27" width="11.5546875" style="62" customWidth="1"/>
+    <col min="28" max="28" width="13.77734375" style="62" customWidth="1"/>
+    <col min="29" max="29" width="11.109375" style="62" customWidth="1"/>
+    <col min="30" max="30" width="13.44140625" style="62" customWidth="1"/>
+    <col min="31" max="31" width="14.33203125" style="62" customWidth="1"/>
+    <col min="32" max="32" width="19.21875" style="62" customWidth="1"/>
+    <col min="33" max="33" width="22.88671875" style="62" customWidth="1"/>
+    <col min="34" max="40" width="8.88671875" style="62"/>
+    <col min="41" max="41" width="11.109375" style="62" customWidth="1"/>
+    <col min="42" max="42" width="11" style="62" customWidth="1"/>
+    <col min="43" max="16384" width="8.88671875" style="62"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="20.399999999999999" customHeight="1">
-      <c r="A1" s="19"/>
-      <c r="B1" s="20"/>
+      <c r="A1" s="13"/>
+      <c r="B1" s="14"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -1299,7 +1300,7 @@
       <c r="R1" s="5"/>
       <c r="S1" s="2"/>
       <c r="T1" s="2"/>
-      <c r="U1" s="9"/>
+      <c r="U1" s="8"/>
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
       <c r="X1" s="5"/>
@@ -1324,10 +1325,10 @@
       <c r="AQ1" s="2"/>
     </row>
     <row r="2" spans="1:44" ht="15.6">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="20"/>
+      <c r="B2" s="14"/>
       <c r="C2" s="1"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -1345,7 +1346,7 @@
       <c r="R2" s="5"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
-      <c r="U2" s="9"/>
+      <c r="U2" s="8"/>
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
       <c r="X2" s="5"/>
@@ -1389,7 +1390,7 @@
       <c r="R3" s="5"/>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
-      <c r="U3" s="9"/>
+      <c r="U3" s="8"/>
       <c r="V3" s="2"/>
       <c r="W3" s="2"/>
       <c r="X3" s="5"/>
@@ -1414,29 +1415,29 @@
       <c r="AQ3" s="2"/>
     </row>
     <row r="4" spans="1:44" ht="15.6">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="15"/>
-      <c r="U4" s="12"/>
-      <c r="Z4" s="13"/>
-      <c r="AG4" s="52"/>
-      <c r="AH4" s="52"/>
-      <c r="AI4" s="15"/>
-      <c r="AJ4" s="15"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="63"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="U4" s="64"/>
+      <c r="Z4" s="7"/>
+      <c r="AG4" s="65"/>
+      <c r="AH4" s="65"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
       <c r="AK4" s="2"/>
       <c r="AL4" s="2"/>
       <c r="AM4" s="2"/>
@@ -1446,42 +1447,42 @@
       <c r="AQ4" s="2"/>
     </row>
     <row r="5" spans="1:44" ht="15" thickBot="1">
-      <c r="A5" s="7"/>
+      <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="17"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="11"/>
       <c r="K5" s="2"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
       <c r="P5" s="2"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
-      <c r="U5" s="10"/>
+      <c r="U5" s="9"/>
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
       <c r="X5" s="2"/>
       <c r="Y5" s="2"/>
-      <c r="Z5" s="8"/>
+      <c r="Z5" s="7"/>
       <c r="AA5" s="2"/>
       <c r="AB5" s="2"/>
       <c r="AC5" s="2"/>
       <c r="AD5" s="2"/>
       <c r="AE5" s="2"/>
       <c r="AF5" s="2"/>
-      <c r="AG5" s="18"/>
-      <c r="AH5" s="18"/>
-      <c r="AI5" s="17"/>
-      <c r="AJ5" s="17"/>
+      <c r="AG5" s="12"/>
+      <c r="AH5" s="12"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
       <c r="AK5" s="2"/>
       <c r="AL5" s="2"/>
       <c r="AM5" s="2"/>
@@ -1491,339 +1492,333 @@
       <c r="AQ5" s="2"/>
     </row>
     <row r="6" spans="1:44" ht="15" customHeight="1" thickTop="1">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="28" t="s">
+      <c r="C6" s="29"/>
+      <c r="D6" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="49" t="s">
+      <c r="F6" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="60" t="s">
+      <c r="G6" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="61"/>
-      <c r="M6" s="61"/>
-      <c r="N6" s="61"/>
-      <c r="O6" s="62"/>
-      <c r="P6" s="60" t="s">
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="53"/>
+      <c r="M6" s="53"/>
+      <c r="N6" s="53"/>
+      <c r="O6" s="54"/>
+      <c r="P6" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="Q6" s="61"/>
-      <c r="R6" s="61"/>
-      <c r="S6" s="61"/>
-      <c r="T6" s="61"/>
-      <c r="U6" s="62"/>
-      <c r="V6" s="63" t="s">
+      <c r="Q6" s="53"/>
+      <c r="R6" s="53"/>
+      <c r="S6" s="53"/>
+      <c r="T6" s="53"/>
+      <c r="U6" s="54"/>
+      <c r="V6" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="W6" s="46" t="s">
+      <c r="W6" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="X6" s="46" t="s">
+      <c r="X6" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="Y6" s="31" t="s">
+      <c r="Y6" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="Z6" s="53" t="s">
+      <c r="Z6" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="AA6" s="28" t="s">
+      <c r="AA6" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="AB6" s="28" t="s">
+      <c r="AB6" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="AC6" s="36" t="s">
+      <c r="AC6" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="AD6" s="38" t="s">
+      <c r="AD6" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="AE6" s="39"/>
-      <c r="AF6" s="40"/>
-      <c r="AG6" s="31" t="s">
+      <c r="AE6" s="46"/>
+      <c r="AF6" s="47"/>
+      <c r="AG6" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="AH6" s="41" t="s">
+      <c r="AH6" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="AI6" s="36" t="s">
+      <c r="AI6" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="AJ6" s="49" t="s">
+      <c r="AJ6" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="AK6" s="46" t="s">
+      <c r="AK6" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="AL6" s="28" t="s">
+      <c r="AL6" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="AM6" s="28" t="s">
+      <c r="AM6" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="AN6" s="28" t="s">
+      <c r="AN6" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="AO6" s="28" t="s">
+      <c r="AO6" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="AP6" s="28" t="s">
+      <c r="AP6" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="AQ6" s="31" t="s">
+      <c r="AQ6" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="AR6" s="31" t="s">
+      <c r="AR6" s="39" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:44">
-      <c r="A7" s="47"/>
-      <c r="B7" s="58"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="72" t="s">
+      <c r="A7" s="27"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="34" t="s">
+      <c r="H7" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="34" t="s">
+      <c r="I7" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="J7" s="34" t="s">
+      <c r="J7" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="K7" s="34" t="s">
+      <c r="K7" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="L7" s="34" t="s">
+      <c r="L7" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="M7" s="34" t="s">
+      <c r="M7" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="N7" s="34" t="s">
+      <c r="N7" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="O7" s="70" t="s">
+      <c r="O7" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="P7" s="71" t="s">
+      <c r="P7" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="Q7" s="34" t="s">
+      <c r="Q7" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="R7" s="34" t="s">
+      <c r="R7" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="S7" s="68" t="s">
+      <c r="S7" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="T7" s="69"/>
-      <c r="U7" s="66" t="s">
+      <c r="T7" s="61"/>
+      <c r="U7" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="V7" s="64"/>
-      <c r="W7" s="47"/>
-      <c r="X7" s="47"/>
-      <c r="Y7" s="32"/>
-      <c r="Z7" s="54"/>
-      <c r="AA7" s="29"/>
-      <c r="AB7" s="29"/>
-      <c r="AC7" s="37"/>
-      <c r="AD7" s="44" t="s">
+      <c r="V7" s="56"/>
+      <c r="W7" s="27"/>
+      <c r="X7" s="27"/>
+      <c r="Y7" s="40"/>
+      <c r="Z7" s="43"/>
+      <c r="AA7" s="33"/>
+      <c r="AB7" s="33"/>
+      <c r="AC7" s="35"/>
+      <c r="AD7" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="AE7" s="45" t="s">
+      <c r="AE7" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="AF7" s="44" t="s">
+      <c r="AF7" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="AG7" s="32"/>
-      <c r="AH7" s="42"/>
-      <c r="AI7" s="37"/>
-      <c r="AJ7" s="50"/>
-      <c r="AK7" s="47"/>
-      <c r="AL7" s="29"/>
-      <c r="AM7" s="29"/>
-      <c r="AN7" s="29"/>
-      <c r="AO7" s="29"/>
-      <c r="AP7" s="29"/>
-      <c r="AQ7" s="32"/>
-      <c r="AR7" s="32"/>
+      <c r="AG7" s="40"/>
+      <c r="AH7" s="49"/>
+      <c r="AI7" s="35"/>
+      <c r="AJ7" s="38"/>
+      <c r="AK7" s="27"/>
+      <c r="AL7" s="33"/>
+      <c r="AM7" s="33"/>
+      <c r="AN7" s="33"/>
+      <c r="AO7" s="33"/>
+      <c r="AP7" s="33"/>
+      <c r="AQ7" s="40"/>
+      <c r="AR7" s="40"/>
     </row>
     <row r="8" spans="1:44" ht="31.2" customHeight="1" thickBot="1">
-      <c r="A8" s="48"/>
-      <c r="B8" s="22" t="s">
+      <c r="A8" s="23"/>
+      <c r="B8" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="51"/>
-      <c r="P8" s="48"/>
-      <c r="Q8" s="30"/>
-      <c r="R8" s="30"/>
-      <c r="S8" s="23" t="s">
+      <c r="D8" s="19"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="19"/>
+      <c r="S8" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="T8" s="24" t="s">
+      <c r="T8" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="U8" s="67"/>
-      <c r="V8" s="65"/>
-      <c r="W8" s="48"/>
-      <c r="X8" s="48"/>
-      <c r="Y8" s="33"/>
-      <c r="Z8" s="55"/>
-      <c r="AA8" s="30"/>
-      <c r="AB8" s="30"/>
-      <c r="AC8" s="35"/>
-      <c r="AD8" s="30"/>
-      <c r="AE8" s="35"/>
-      <c r="AF8" s="30"/>
-      <c r="AG8" s="33"/>
-      <c r="AH8" s="43"/>
-      <c r="AI8" s="35"/>
-      <c r="AJ8" s="51"/>
-      <c r="AK8" s="48"/>
-      <c r="AL8" s="30"/>
-      <c r="AM8" s="30"/>
-      <c r="AN8" s="30"/>
-      <c r="AO8" s="30"/>
-      <c r="AP8" s="30"/>
-      <c r="AQ8" s="33"/>
-      <c r="AR8" s="33"/>
+      <c r="U8" s="59"/>
+      <c r="V8" s="57"/>
+      <c r="W8" s="23"/>
+      <c r="X8" s="23"/>
+      <c r="Y8" s="41"/>
+      <c r="Z8" s="44"/>
+      <c r="AA8" s="19"/>
+      <c r="AB8" s="19"/>
+      <c r="AC8" s="36"/>
+      <c r="AD8" s="19"/>
+      <c r="AE8" s="36"/>
+      <c r="AF8" s="19"/>
+      <c r="AG8" s="41"/>
+      <c r="AH8" s="25"/>
+      <c r="AI8" s="36"/>
+      <c r="AJ8" s="21"/>
+      <c r="AK8" s="23"/>
+      <c r="AL8" s="19"/>
+      <c r="AM8" s="19"/>
+      <c r="AN8" s="19"/>
+      <c r="AO8" s="19"/>
+      <c r="AP8" s="19"/>
+      <c r="AQ8" s="41"/>
+      <c r="AR8" s="41"/>
     </row>
     <row r="9" spans="1:44" ht="15" thickTop="1"/>
     <row r="11" spans="1:44">
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="67"/>
+      <c r="K11" s="67"/>
+      <c r="L11" s="67"/>
     </row>
     <row r="12" spans="1:44">
-      <c r="B12" s="27"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="25"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="L12" s="25"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="67"/>
+      <c r="K12" s="67"/>
+      <c r="L12" s="67"/>
     </row>
     <row r="13" spans="1:44">
-      <c r="B13" s="25"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="25"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="69"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68"/>
+      <c r="J13" s="68"/>
+      <c r="K13" s="68"/>
+      <c r="L13" s="67"/>
     </row>
     <row r="14" spans="1:44">
-      <c r="B14" s="25"/>
-      <c r="C14" s="73" t="s">
+      <c r="B14" s="67"/>
+      <c r="C14" s="70" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="73" t="s">
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="67"/>
+      <c r="H14" s="70" t="s">
         <v>52</v>
       </c>
-      <c r="H14" s="73"/>
-      <c r="I14" s="73"/>
-      <c r="J14" s="73"/>
-      <c r="K14" s="73"/>
-      <c r="L14" s="25"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="70"/>
+      <c r="L14" s="67"/>
     </row>
     <row r="15" spans="1:44">
-      <c r="B15" s="25"/>
-      <c r="C15" s="74" t="s">
+      <c r="B15" s="67"/>
+      <c r="C15" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="74"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="74" t="s">
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="67"/>
+      <c r="H15" s="71" t="s">
         <v>54</v>
       </c>
-      <c r="H15" s="74"/>
-      <c r="I15" s="74"/>
-      <c r="J15" s="74"/>
-      <c r="K15" s="74"/>
-      <c r="L15" s="25"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="71"/>
+      <c r="L15" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="G14:K14"/>
-    <mergeCell ref="G15:K15"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="N7:N8"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B6:C7"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="AG4:AH4"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="AQ6:AQ8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="G6:O6"/>
+    <mergeCell ref="P6:U6"/>
+    <mergeCell ref="V6:V8"/>
+    <mergeCell ref="W6:W8"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="Q7:Q8"/>
+    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="L7:L8"/>
     <mergeCell ref="AR6:AR8"/>
     <mergeCell ref="AC6:AC8"/>
     <mergeCell ref="AD6:AF6"/>
@@ -1840,20 +1835,26 @@
     <mergeCell ref="AJ6:AJ8"/>
     <mergeCell ref="AN6:AN8"/>
     <mergeCell ref="AP6:AP8"/>
-    <mergeCell ref="AQ6:AQ8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="G6:O6"/>
-    <mergeCell ref="P6:U6"/>
-    <mergeCell ref="V6:V8"/>
-    <mergeCell ref="W6:W8"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="U7:U8"/>
-    <mergeCell ref="Q7:Q8"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="AG4:AH4"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B6:C7"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="H15:K15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/iLgs/App_Data/CustodianVehiclesTemplate.xlsx
+++ b/iLgs/App_Data/CustodianVehiclesTemplate.xlsx
@@ -8,14 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Templates New/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="8_{C24A2B6E-C141-4441-9F51-293C5BCBCD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AE0AA3C-FFEF-448B-99FC-C19C75DFA131}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="8_{C24A2B6E-C141-4441-9F51-293C5BCBCD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B83E77C-30F8-4D7A-85D6-42E4045A9B40}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{49C2EA6D-0E15-4E51-9FB1-ADBE484D14AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -729,7 +727,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -768,151 +766,150 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
@@ -1243,41 +1240,41 @@
   <dimension ref="A1:AR15"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" style="62" customWidth="1"/>
-    <col min="2" max="2" width="18.88671875" style="62" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" style="62" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.44140625" style="62" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" style="62" customWidth="1"/>
-    <col min="6" max="6" width="24.88671875" style="62" customWidth="1"/>
-    <col min="7" max="7" width="10.88671875" style="62" customWidth="1"/>
-    <col min="8" max="8" width="9.77734375" style="62" customWidth="1"/>
-    <col min="9" max="9" width="9.21875" style="62" customWidth="1"/>
-    <col min="10" max="10" width="7.33203125" style="62" customWidth="1"/>
-    <col min="11" max="12" width="15" style="62" customWidth="1"/>
-    <col min="13" max="13" width="12.33203125" style="62" customWidth="1"/>
-    <col min="14" max="14" width="11.5546875" style="62" customWidth="1"/>
-    <col min="15" max="15" width="8.88671875" style="62"/>
-    <col min="16" max="16" width="14.6640625" style="62" customWidth="1"/>
-    <col min="17" max="17" width="12.33203125" style="62" customWidth="1"/>
-    <col min="18" max="18" width="17.33203125" style="62" customWidth="1"/>
-    <col min="19" max="19" width="11.5546875" style="62" customWidth="1"/>
-    <col min="20" max="20" width="10.6640625" style="62" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.88671875" style="62"/>
-    <col min="22" max="22" width="12.44140625" style="62" customWidth="1"/>
-    <col min="23" max="24" width="8.88671875" style="62"/>
-    <col min="25" max="25" width="13.44140625" style="62" customWidth="1"/>
-    <col min="26" max="26" width="11.21875" style="62" customWidth="1"/>
-    <col min="27" max="27" width="11.5546875" style="62" customWidth="1"/>
-    <col min="28" max="28" width="13.77734375" style="62" customWidth="1"/>
-    <col min="29" max="29" width="11.109375" style="62" customWidth="1"/>
-    <col min="30" max="30" width="13.44140625" style="62" customWidth="1"/>
-    <col min="31" max="31" width="14.33203125" style="62" customWidth="1"/>
-    <col min="32" max="32" width="19.21875" style="62" customWidth="1"/>
-    <col min="33" max="33" width="22.88671875" style="62" customWidth="1"/>
-    <col min="34" max="40" width="8.88671875" style="62"/>
-    <col min="41" max="41" width="11.109375" style="62" customWidth="1"/>
-    <col min="42" max="42" width="11" style="62" customWidth="1"/>
-    <col min="43" max="16384" width="8.88671875" style="62"/>
+    <col min="1" max="1" width="13.44140625" style="18" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" style="18" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" style="18" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" style="18" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" style="18" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" style="18" customWidth="1"/>
+    <col min="8" max="8" width="9.77734375" style="18" customWidth="1"/>
+    <col min="9" max="9" width="9.21875" style="18" customWidth="1"/>
+    <col min="10" max="10" width="7.33203125" style="18" customWidth="1"/>
+    <col min="11" max="12" width="15" style="18" customWidth="1"/>
+    <col min="13" max="13" width="12.33203125" style="18" customWidth="1"/>
+    <col min="14" max="14" width="11.5546875" style="18" customWidth="1"/>
+    <col min="15" max="15" width="8.88671875" style="18"/>
+    <col min="16" max="16" width="14.6640625" style="18" customWidth="1"/>
+    <col min="17" max="17" width="12.33203125" style="18" customWidth="1"/>
+    <col min="18" max="18" width="17.33203125" style="18" customWidth="1"/>
+    <col min="19" max="19" width="11.5546875" style="18" customWidth="1"/>
+    <col min="20" max="20" width="10.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.88671875" style="18"/>
+    <col min="22" max="22" width="12.44140625" style="18" customWidth="1"/>
+    <col min="23" max="24" width="8.88671875" style="18"/>
+    <col min="25" max="25" width="13.44140625" style="18" customWidth="1"/>
+    <col min="26" max="26" width="11.21875" style="18" customWidth="1"/>
+    <col min="27" max="27" width="11.5546875" style="18" customWidth="1"/>
+    <col min="28" max="28" width="13.77734375" style="18" customWidth="1"/>
+    <col min="29" max="29" width="11.109375" style="18" customWidth="1"/>
+    <col min="30" max="30" width="13.44140625" style="18" customWidth="1"/>
+    <col min="31" max="31" width="14.33203125" style="18" customWidth="1"/>
+    <col min="32" max="32" width="19.21875" style="18" customWidth="1"/>
+    <col min="33" max="33" width="22.88671875" style="18" customWidth="1"/>
+    <col min="34" max="40" width="8.88671875" style="18"/>
+    <col min="41" max="41" width="11.109375" style="18" customWidth="1"/>
+    <col min="42" max="42" width="11" style="18" customWidth="1"/>
+    <col min="43" max="16384" width="8.88671875" style="18"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="20.399999999999999" customHeight="1">
@@ -1425,17 +1422,17 @@
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
       <c r="J4" s="11"/>
-      <c r="K4" s="63"/>
+      <c r="K4" s="19"/>
       <c r="L4" s="11"/>
       <c r="M4" s="11"/>
       <c r="N4" s="11"/>
       <c r="O4" s="11"/>
       <c r="Q4" s="11"/>
       <c r="R4" s="11"/>
-      <c r="U4" s="64"/>
+      <c r="U4" s="20"/>
       <c r="Z4" s="7"/>
-      <c r="AG4" s="65"/>
-      <c r="AH4" s="65"/>
+      <c r="AG4" s="58"/>
+      <c r="AH4" s="58"/>
       <c r="AI4" s="11"/>
       <c r="AJ4" s="11"/>
       <c r="AK4" s="2"/>
@@ -1492,63 +1489,63 @@
       <c r="AQ5" s="2"/>
     </row>
     <row r="6" spans="1:44" ht="15" customHeight="1" thickTop="1">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="62" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="32" t="s">
+      <c r="C6" s="63"/>
+      <c r="D6" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="34" t="s">
+      <c r="E6" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="53"/>
-      <c r="M6" s="53"/>
-      <c r="N6" s="53"/>
-      <c r="O6" s="54"/>
-      <c r="P6" s="52" t="s">
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="32"/>
+      <c r="P6" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="Q6" s="53"/>
-      <c r="R6" s="53"/>
-      <c r="S6" s="53"/>
-      <c r="T6" s="53"/>
-      <c r="U6" s="54"/>
-      <c r="V6" s="55" t="s">
+      <c r="Q6" s="31"/>
+      <c r="R6" s="31"/>
+      <c r="S6" s="31"/>
+      <c r="T6" s="31"/>
+      <c r="U6" s="32"/>
+      <c r="V6" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="W6" s="26" t="s">
+      <c r="W6" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="X6" s="26" t="s">
+      <c r="X6" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="Y6" s="39" t="s">
+      <c r="Y6" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Z6" s="42" t="s">
+      <c r="Z6" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="AA6" s="32" t="s">
+      <c r="AA6" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="AB6" s="32" t="s">
+      <c r="AB6" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="AC6" s="34" t="s">
+      <c r="AC6" s="43" t="s">
         <v>13</v>
       </c>
       <c r="AD6" s="45" t="s">
@@ -1556,269 +1553,273 @@
       </c>
       <c r="AE6" s="46"/>
       <c r="AF6" s="47"/>
-      <c r="AG6" s="39" t="s">
+      <c r="AG6" s="24" t="s">
         <v>49</v>
       </c>
       <c r="AH6" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="AI6" s="34" t="s">
+      <c r="AI6" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="AJ6" s="37" t="s">
+      <c r="AJ6" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="AK6" s="26" t="s">
+      <c r="AK6" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="AL6" s="32" t="s">
+      <c r="AL6" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="AM6" s="32" t="s">
+      <c r="AM6" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="AN6" s="32" t="s">
+      <c r="AN6" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="AO6" s="32" t="s">
+      <c r="AO6" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="AP6" s="32" t="s">
+      <c r="AP6" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="AQ6" s="39" t="s">
+      <c r="AQ6" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="AR6" s="39" t="s">
+      <c r="AR6" s="24" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:44">
-      <c r="A7" s="27"/>
-      <c r="B7" s="30"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="24" t="s">
+      <c r="A7" s="37"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="I7" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="J7" s="18" t="s">
+      <c r="J7" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="K7" s="18" t="s">
+      <c r="K7" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="L7" s="18" t="s">
+      <c r="L7" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="M7" s="18" t="s">
+      <c r="M7" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="N7" s="18" t="s">
+      <c r="N7" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="O7" s="20" t="s">
+      <c r="O7" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="P7" s="22" t="s">
+      <c r="P7" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="Q7" s="18" t="s">
+      <c r="Q7" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="R7" s="18" t="s">
+      <c r="R7" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="S7" s="60" t="s">
+      <c r="S7" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="T7" s="61"/>
-      <c r="U7" s="58" t="s">
+      <c r="T7" s="42"/>
+      <c r="U7" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="V7" s="56"/>
-      <c r="W7" s="27"/>
-      <c r="X7" s="27"/>
-      <c r="Y7" s="40"/>
-      <c r="Z7" s="43"/>
-      <c r="AA7" s="33"/>
-      <c r="AB7" s="33"/>
-      <c r="AC7" s="35"/>
-      <c r="AD7" s="50" t="s">
+      <c r="V7" s="34"/>
+      <c r="W7" s="37"/>
+      <c r="X7" s="37"/>
+      <c r="Y7" s="25"/>
+      <c r="Z7" s="60"/>
+      <c r="AA7" s="54"/>
+      <c r="AB7" s="54"/>
+      <c r="AC7" s="44"/>
+      <c r="AD7" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="AE7" s="51" t="s">
+      <c r="AE7" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="AF7" s="50" t="s">
+      <c r="AF7" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="AG7" s="40"/>
+      <c r="AG7" s="25"/>
       <c r="AH7" s="49"/>
-      <c r="AI7" s="35"/>
-      <c r="AJ7" s="38"/>
-      <c r="AK7" s="27"/>
-      <c r="AL7" s="33"/>
-      <c r="AM7" s="33"/>
-      <c r="AN7" s="33"/>
-      <c r="AO7" s="33"/>
-      <c r="AP7" s="33"/>
-      <c r="AQ7" s="40"/>
-      <c r="AR7" s="40"/>
+      <c r="AI7" s="44"/>
+      <c r="AJ7" s="56"/>
+      <c r="AK7" s="37"/>
+      <c r="AL7" s="54"/>
+      <c r="AM7" s="54"/>
+      <c r="AN7" s="54"/>
+      <c r="AO7" s="54"/>
+      <c r="AP7" s="54"/>
+      <c r="AQ7" s="25"/>
+      <c r="AR7" s="25"/>
     </row>
     <row r="8" spans="1:44" ht="31.2" customHeight="1" thickBot="1">
-      <c r="A8" s="23"/>
+      <c r="A8" s="38"/>
       <c r="B8" s="15" t="s">
         <v>42</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="21"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="19"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="29"/>
+      <c r="O8" s="57"/>
+      <c r="P8" s="38"/>
+      <c r="Q8" s="29"/>
+      <c r="R8" s="29"/>
       <c r="S8" s="16" t="s">
         <v>44</v>
       </c>
       <c r="T8" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="U8" s="59"/>
-      <c r="V8" s="57"/>
-      <c r="W8" s="23"/>
-      <c r="X8" s="23"/>
-      <c r="Y8" s="41"/>
-      <c r="Z8" s="44"/>
-      <c r="AA8" s="19"/>
-      <c r="AB8" s="19"/>
-      <c r="AC8" s="36"/>
-      <c r="AD8" s="19"/>
-      <c r="AE8" s="36"/>
-      <c r="AF8" s="19"/>
-      <c r="AG8" s="41"/>
-      <c r="AH8" s="25"/>
-      <c r="AI8" s="36"/>
-      <c r="AJ8" s="21"/>
-      <c r="AK8" s="23"/>
-      <c r="AL8" s="19"/>
-      <c r="AM8" s="19"/>
-      <c r="AN8" s="19"/>
-      <c r="AO8" s="19"/>
-      <c r="AP8" s="19"/>
-      <c r="AQ8" s="41"/>
-      <c r="AR8" s="41"/>
+      <c r="U8" s="40"/>
+      <c r="V8" s="35"/>
+      <c r="W8" s="38"/>
+      <c r="X8" s="38"/>
+      <c r="Y8" s="26"/>
+      <c r="Z8" s="61"/>
+      <c r="AA8" s="29"/>
+      <c r="AB8" s="29"/>
+      <c r="AC8" s="28"/>
+      <c r="AD8" s="29"/>
+      <c r="AE8" s="28"/>
+      <c r="AF8" s="29"/>
+      <c r="AG8" s="26"/>
+      <c r="AH8" s="50"/>
+      <c r="AI8" s="28"/>
+      <c r="AJ8" s="57"/>
+      <c r="AK8" s="38"/>
+      <c r="AL8" s="29"/>
+      <c r="AM8" s="29"/>
+      <c r="AN8" s="29"/>
+      <c r="AO8" s="29"/>
+      <c r="AP8" s="29"/>
+      <c r="AQ8" s="26"/>
+      <c r="AR8" s="26"/>
     </row>
     <row r="9" spans="1:44" ht="15" thickTop="1"/>
     <row r="11" spans="1:44">
-      <c r="B11" s="66" t="s">
+      <c r="B11" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67" t="s">
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
-      <c r="J11" s="67"/>
-      <c r="K11" s="67"/>
-      <c r="L11" s="67"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="22"/>
     </row>
     <row r="12" spans="1:44">
-      <c r="B12" s="66"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="67"/>
-      <c r="K12" s="67"/>
-      <c r="L12" s="67"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
     </row>
     <row r="13" spans="1:44">
-      <c r="B13" s="67"/>
-      <c r="C13" s="68"/>
-      <c r="D13" s="68"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="67"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="68"/>
-      <c r="I13" s="68"/>
-      <c r="J13" s="68"/>
-      <c r="K13" s="68"/>
-      <c r="L13" s="67"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="22"/>
     </row>
     <row r="14" spans="1:44">
-      <c r="B14" s="67"/>
-      <c r="C14" s="70" t="s">
+      <c r="B14" s="22"/>
+      <c r="C14" s="69" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
-      <c r="F14" s="67"/>
-      <c r="H14" s="70" t="s">
+      <c r="D14" s="69"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="22"/>
+      <c r="H14" s="69" t="s">
         <v>52</v>
       </c>
-      <c r="I14" s="70"/>
-      <c r="J14" s="70"/>
-      <c r="K14" s="70"/>
-      <c r="L14" s="67"/>
+      <c r="I14" s="69"/>
+      <c r="J14" s="69"/>
+      <c r="K14" s="69"/>
+      <c r="L14" s="22"/>
     </row>
     <row r="15" spans="1:44">
-      <c r="B15" s="67"/>
-      <c r="C15" s="71" t="s">
+      <c r="B15" s="22"/>
+      <c r="C15" s="70" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="71"/>
-      <c r="E15" s="71"/>
-      <c r="F15" s="67"/>
-      <c r="H15" s="71" t="s">
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="22"/>
+      <c r="H15" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="I15" s="71"/>
-      <c r="J15" s="71"/>
-      <c r="K15" s="71"/>
-      <c r="L15" s="67"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="70"/>
+      <c r="K15" s="70"/>
+      <c r="L15" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="AQ6:AQ8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="G6:O6"/>
-    <mergeCell ref="P6:U6"/>
-    <mergeCell ref="V6:V8"/>
-    <mergeCell ref="W6:W8"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="U7:U8"/>
-    <mergeCell ref="Q7:Q8"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="H15:K15"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B6:C7"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="AG4:AH4"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="AB6:AB8"/>
     <mergeCell ref="AR6:AR8"/>
     <mergeCell ref="AC6:AC8"/>
     <mergeCell ref="AD6:AF6"/>
@@ -1835,45 +1836,23 @@
     <mergeCell ref="AJ6:AJ8"/>
     <mergeCell ref="AN6:AN8"/>
     <mergeCell ref="AP6:AP8"/>
-    <mergeCell ref="AG4:AH4"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B6:C7"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="AQ6:AQ8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="G6:O6"/>
+    <mergeCell ref="P6:U6"/>
+    <mergeCell ref="V6:V8"/>
+    <mergeCell ref="W6:W8"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="Q7:Q8"/>
+    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="L7:L8"/>
     <mergeCell ref="N7:N8"/>
     <mergeCell ref="O7:O8"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="H14:K14"/>
-    <mergeCell ref="H15:K15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4FF280D-8901-47F7-A49B-A58CF91F8AB2}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E66AD95-083B-4AB7-B7E6-04F3E141ECAC}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/iLgs/App_Data/CustodianVehiclesTemplate.xlsx
+++ b/iLgs/App_Data/CustodianVehiclesTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Templates New/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="8_{C24A2B6E-C141-4441-9F51-293C5BCBCD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B83E77C-30F8-4D7A-85D6-42E4045A9B40}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="8_{C24A2B6E-C141-4441-9F51-293C5BCBCD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62214753-6BFB-4F13-B738-111A1AF85A72}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{49C2EA6D-0E15-4E51-9FB1-ADBE484D14AF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="54">
   <si>
     <t>Custodian
 Item
@@ -48,9 +48,6 @@
     <t>Sub-Account</t>
   </si>
   <si>
-    <t>Article</t>
-  </si>
-  <si>
     <t>DESCRIPTION</t>
   </si>
   <si>
@@ -204,9 +201,6 @@
   </si>
   <si>
     <t>ANNEX</t>
-  </si>
-  <si>
-    <t>AS OF</t>
   </si>
   <si>
     <t>Location Code (of Balances)</t>
@@ -731,9 +725,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -775,140 +766,24 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
@@ -917,6 +792,123 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1237,74 +1229,73 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00C28830-284B-4C5E-B18C-8421255AA9A0}">
-  <dimension ref="A1:AR15"/>
+  <dimension ref="A1:AQ16"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" style="18" customWidth="1"/>
-    <col min="2" max="2" width="18.88671875" style="18" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.44140625" style="18" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" style="18" customWidth="1"/>
-    <col min="6" max="6" width="24.88671875" style="18" customWidth="1"/>
-    <col min="7" max="7" width="10.88671875" style="18" customWidth="1"/>
-    <col min="8" max="8" width="9.77734375" style="18" customWidth="1"/>
-    <col min="9" max="9" width="9.21875" style="18" customWidth="1"/>
-    <col min="10" max="10" width="7.33203125" style="18" customWidth="1"/>
-    <col min="11" max="12" width="15" style="18" customWidth="1"/>
-    <col min="13" max="13" width="12.33203125" style="18" customWidth="1"/>
-    <col min="14" max="14" width="11.5546875" style="18" customWidth="1"/>
-    <col min="15" max="15" width="8.88671875" style="18"/>
-    <col min="16" max="16" width="14.6640625" style="18" customWidth="1"/>
-    <col min="17" max="17" width="12.33203125" style="18" customWidth="1"/>
-    <col min="18" max="18" width="17.33203125" style="18" customWidth="1"/>
-    <col min="19" max="19" width="11.5546875" style="18" customWidth="1"/>
-    <col min="20" max="20" width="10.6640625" style="18" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.88671875" style="18"/>
-    <col min="22" max="22" width="12.44140625" style="18" customWidth="1"/>
-    <col min="23" max="24" width="8.88671875" style="18"/>
-    <col min="25" max="25" width="13.44140625" style="18" customWidth="1"/>
-    <col min="26" max="26" width="11.21875" style="18" customWidth="1"/>
-    <col min="27" max="27" width="11.5546875" style="18" customWidth="1"/>
-    <col min="28" max="28" width="13.77734375" style="18" customWidth="1"/>
-    <col min="29" max="29" width="11.109375" style="18" customWidth="1"/>
-    <col min="30" max="30" width="13.44140625" style="18" customWidth="1"/>
-    <col min="31" max="31" width="14.33203125" style="18" customWidth="1"/>
-    <col min="32" max="32" width="19.21875" style="18" customWidth="1"/>
-    <col min="33" max="33" width="22.88671875" style="18" customWidth="1"/>
-    <col min="34" max="40" width="8.88671875" style="18"/>
-    <col min="41" max="41" width="11.109375" style="18" customWidth="1"/>
-    <col min="42" max="42" width="11" style="18" customWidth="1"/>
-    <col min="43" max="16384" width="8.88671875" style="18"/>
+    <col min="1" max="1" width="13.44140625" style="17" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" style="17" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" style="17" customWidth="1"/>
+    <col min="5" max="5" width="29.88671875" style="17" customWidth="1"/>
+    <col min="6" max="6" width="10.88671875" style="17" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" style="17" customWidth="1"/>
+    <col min="8" max="8" width="9.21875" style="17" customWidth="1"/>
+    <col min="9" max="9" width="7.33203125" style="17" customWidth="1"/>
+    <col min="10" max="11" width="15" style="17" customWidth="1"/>
+    <col min="12" max="12" width="12.33203125" style="17" customWidth="1"/>
+    <col min="13" max="13" width="11.5546875" style="17" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" style="17"/>
+    <col min="15" max="15" width="14.6640625" style="17" customWidth="1"/>
+    <col min="16" max="16" width="12.33203125" style="17" customWidth="1"/>
+    <col min="17" max="17" width="17.33203125" style="17" customWidth="1"/>
+    <col min="18" max="18" width="11.5546875" style="17" customWidth="1"/>
+    <col min="19" max="19" width="10.6640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.88671875" style="17"/>
+    <col min="21" max="21" width="12.44140625" style="17" customWidth="1"/>
+    <col min="22" max="23" width="8.88671875" style="17"/>
+    <col min="24" max="24" width="13.44140625" style="17" customWidth="1"/>
+    <col min="25" max="25" width="11.21875" style="17" customWidth="1"/>
+    <col min="26" max="26" width="11.5546875" style="17" customWidth="1"/>
+    <col min="27" max="27" width="13.77734375" style="17" customWidth="1"/>
+    <col min="28" max="28" width="11.109375" style="17" customWidth="1"/>
+    <col min="29" max="29" width="13.44140625" style="17" customWidth="1"/>
+    <col min="30" max="30" width="14.33203125" style="17" customWidth="1"/>
+    <col min="31" max="31" width="19.21875" style="17" customWidth="1"/>
+    <col min="32" max="32" width="22.88671875" style="17" customWidth="1"/>
+    <col min="33" max="39" width="8.88671875" style="17"/>
+    <col min="40" max="40" width="11.109375" style="17" customWidth="1"/>
+    <col min="41" max="41" width="11" style="17" customWidth="1"/>
+    <col min="42" max="16384" width="8.88671875" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="20.399999999999999" customHeight="1">
-      <c r="A1" s="13"/>
-      <c r="B1" s="14"/>
+    <row r="1" spans="1:43" ht="20.399999999999999" customHeight="1">
+      <c r="A1" s="12"/>
+      <c r="B1" s="13"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="3"/>
-      <c r="H1" s="4"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
       <c r="I1" s="4"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="2"/>
       <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="8"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="2"/>
       <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="5"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
       <c r="Y1" s="5"/>
-      <c r="Z1" s="6"/>
-      <c r="AA1" s="5"/>
-      <c r="AB1" s="5"/>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4"/>
+      <c r="AB1" s="2"/>
       <c r="AC1" s="2"/>
       <c r="AD1" s="2"/>
       <c r="AE1" s="2"/>
@@ -1319,38 +1310,35 @@
       <c r="AN1" s="2"/>
       <c r="AO1" s="2"/>
       <c r="AP1" s="2"/>
-      <c r="AQ1" s="2"/>
     </row>
-    <row r="2" spans="1:44" ht="15.6">
-      <c r="A2" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" s="14"/>
+    <row r="2" spans="1:43" ht="15.6">
+      <c r="A2" s="12"/>
+      <c r="B2" s="13"/>
       <c r="C2" s="1"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="3"/>
-      <c r="H2" s="4"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
       <c r="I2" s="4"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="2"/>
       <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="8"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="2"/>
       <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="5"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4"/>
       <c r="Y2" s="5"/>
-      <c r="Z2" s="6"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="4"/>
+      <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
       <c r="AD2" s="2"/>
       <c r="AE2" s="2"/>
@@ -1365,36 +1353,35 @@
       <c r="AN2" s="2"/>
       <c r="AO2" s="2"/>
       <c r="AP2" s="2"/>
-      <c r="AQ2" s="2"/>
     </row>
-    <row r="3" spans="1:44">
-      <c r="A3" s="4"/>
+    <row r="3" spans="1:43">
+      <c r="A3" s="3"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="3"/>
-      <c r="H3" s="4"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
       <c r="I3" s="4"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="2"/>
       <c r="S3" s="2"/>
-      <c r="T3" s="2"/>
-      <c r="U3" s="8"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="2"/>
       <c r="V3" s="2"/>
-      <c r="W3" s="2"/>
-      <c r="X3" s="5"/>
+      <c r="W3" s="4"/>
+      <c r="X3" s="4"/>
       <c r="Y3" s="5"/>
-      <c r="Z3" s="6"/>
-      <c r="AA3" s="5"/>
-      <c r="AB3" s="5"/>
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="4"/>
+      <c r="AB3" s="2"/>
       <c r="AC3" s="2"/>
       <c r="AD3" s="2"/>
       <c r="AE3" s="2"/>
@@ -1409,449 +1396,435 @@
       <c r="AN3" s="2"/>
       <c r="AO3" s="2"/>
       <c r="AP3" s="2"/>
-      <c r="AQ3" s="2"/>
     </row>
-    <row r="4" spans="1:44" ht="15.6">
-      <c r="A4" s="14" t="s">
-        <v>50</v>
+    <row r="4" spans="1:43" ht="15.6">
+      <c r="A4" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
       <c r="I4" s="10"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="U4" s="20"/>
-      <c r="Z4" s="7"/>
-      <c r="AG4" s="58"/>
-      <c r="AH4" s="58"/>
-      <c r="AI4" s="11"/>
-      <c r="AJ4" s="11"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="T4" s="19"/>
+      <c r="Y4" s="6"/>
+      <c r="AF4" s="43"/>
+      <c r="AG4" s="43"/>
+      <c r="AH4" s="10"/>
+      <c r="AI4" s="10"/>
+      <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
       <c r="AL4" s="2"/>
       <c r="AM4" s="2"/>
       <c r="AN4" s="2"/>
       <c r="AO4" s="2"/>
       <c r="AP4" s="2"/>
-      <c r="AQ4" s="2"/>
     </row>
-    <row r="5" spans="1:44" ht="15" thickBot="1">
+    <row r="5" spans="1:43" ht="15" thickBot="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
       <c r="I5" s="10"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="2"/>
       <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-      <c r="U5" s="9"/>
+      <c r="T5" s="8"/>
+      <c r="U5" s="2"/>
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
       <c r="X5" s="2"/>
-      <c r="Y5" s="2"/>
-      <c r="Z5" s="7"/>
+      <c r="Y5" s="6"/>
+      <c r="Z5" s="2"/>
       <c r="AA5" s="2"/>
       <c r="AB5" s="2"/>
       <c r="AC5" s="2"/>
       <c r="AD5" s="2"/>
       <c r="AE5" s="2"/>
-      <c r="AF5" s="2"/>
-      <c r="AG5" s="12"/>
-      <c r="AH5" s="12"/>
-      <c r="AI5" s="11"/>
-      <c r="AJ5" s="11"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="10"/>
+      <c r="AI5" s="10"/>
+      <c r="AJ5" s="2"/>
       <c r="AK5" s="2"/>
       <c r="AL5" s="2"/>
       <c r="AM5" s="2"/>
       <c r="AN5" s="2"/>
       <c r="AO5" s="2"/>
       <c r="AP5" s="2"/>
-      <c r="AQ5" s="2"/>
     </row>
-    <row r="6" spans="1:44" ht="15" customHeight="1" thickTop="1">
-      <c r="A6" s="36" t="s">
+    <row r="6" spans="1:43" ht="15" customHeight="1" thickTop="1">
+      <c r="A6" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="62" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="63"/>
-      <c r="D6" s="53" t="s">
+      <c r="B6" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="35"/>
+      <c r="D6" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="55" t="s">
+      <c r="F6" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="62"/>
+      <c r="O6" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="31"/>
-      <c r="N6" s="31"/>
-      <c r="O6" s="32"/>
-      <c r="P6" s="30" t="s">
+      <c r="P6" s="61"/>
+      <c r="Q6" s="61"/>
+      <c r="R6" s="61"/>
+      <c r="S6" s="61"/>
+      <c r="T6" s="62"/>
+      <c r="U6" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="Q6" s="31"/>
-      <c r="R6" s="31"/>
-      <c r="S6" s="31"/>
-      <c r="T6" s="31"/>
-      <c r="U6" s="32"/>
-      <c r="V6" s="33" t="s">
+      <c r="V6" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="W6" s="36" t="s">
+      <c r="W6" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="X6" s="36" t="s">
+      <c r="X6" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="Y6" s="24" t="s">
+      <c r="Y6" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="Z6" s="59" t="s">
+      <c r="Z6" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="AA6" s="53" t="s">
+      <c r="AA6" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="AB6" s="53" t="s">
+      <c r="AB6" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="AC6" s="43" t="s">
+      <c r="AC6" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="AD6" s="45" t="s">
+      <c r="AD6" s="51"/>
+      <c r="AE6" s="52"/>
+      <c r="AF6" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG6" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="AE6" s="46"/>
-      <c r="AF6" s="47"/>
-      <c r="AG6" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="AH6" s="48" t="s">
+      <c r="AH6" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="AI6" s="43" t="s">
+      <c r="AI6" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="AJ6" s="55" t="s">
+      <c r="AJ6" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="AK6" s="36" t="s">
+      <c r="AK6" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="AL6" s="53" t="s">
+      <c r="AL6" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="AM6" s="53" t="s">
+      <c r="AM6" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="AN6" s="53" t="s">
+      <c r="AN6" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="AO6" s="53" t="s">
+      <c r="AO6" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="AP6" s="53" t="s">
+      <c r="AP6" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="AQ6" s="24" t="s">
+      <c r="AQ6" s="44" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:43">
+      <c r="A7" s="33"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="AR6" s="24" t="s">
-        <v>46</v>
-      </c>
+      <c r="G7" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="M7" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="N7" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="O7" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="P7" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q7" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R7" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="S7" s="69"/>
+      <c r="T7" s="66" t="s">
+        <v>37</v>
+      </c>
+      <c r="U7" s="64"/>
+      <c r="V7" s="33"/>
+      <c r="W7" s="33"/>
+      <c r="X7" s="45"/>
+      <c r="Y7" s="48"/>
+      <c r="Z7" s="39"/>
+      <c r="AA7" s="39"/>
+      <c r="AB7" s="41"/>
+      <c r="AC7" s="55" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD7" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE7" s="55" t="s">
+        <v>40</v>
+      </c>
+      <c r="AF7" s="45"/>
+      <c r="AG7" s="54"/>
+      <c r="AH7" s="41"/>
+      <c r="AI7" s="58"/>
+      <c r="AJ7" s="33"/>
+      <c r="AK7" s="39"/>
+      <c r="AL7" s="39"/>
+      <c r="AM7" s="39"/>
+      <c r="AN7" s="39"/>
+      <c r="AO7" s="39"/>
+      <c r="AP7" s="45"/>
+      <c r="AQ7" s="45"/>
     </row>
-    <row r="7" spans="1:44">
-      <c r="A7" s="37"/>
-      <c r="B7" s="64"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="68" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="L7" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="M7" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="N7" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="O7" s="66" t="s">
-        <v>33</v>
-      </c>
-      <c r="P7" s="67" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q7" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="R7" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="S7" s="41" t="s">
-        <v>37</v>
-      </c>
-      <c r="T7" s="42"/>
-      <c r="U7" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="V7" s="34"/>
-      <c r="W7" s="37"/>
-      <c r="X7" s="37"/>
-      <c r="Y7" s="25"/>
-      <c r="Z7" s="60"/>
-      <c r="AA7" s="54"/>
-      <c r="AB7" s="54"/>
-      <c r="AC7" s="44"/>
-      <c r="AD7" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE7" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF7" s="51" t="s">
+    <row r="8" spans="1:43" ht="34.799999999999997" customHeight="1" thickBot="1">
+      <c r="A8" s="25"/>
+      <c r="B8" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="AG7" s="25"/>
-      <c r="AH7" s="49"/>
-      <c r="AI7" s="44"/>
-      <c r="AJ7" s="56"/>
-      <c r="AK7" s="37"/>
-      <c r="AL7" s="54"/>
-      <c r="AM7" s="54"/>
-      <c r="AN7" s="54"/>
-      <c r="AO7" s="54"/>
-      <c r="AP7" s="54"/>
-      <c r="AQ7" s="25"/>
-      <c r="AR7" s="25"/>
-    </row>
-    <row r="8" spans="1:44" ht="31.2" customHeight="1" thickBot="1">
-      <c r="A8" s="38"/>
-      <c r="B8" s="15" t="s">
+      <c r="C8" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="15" t="s">
-        <v>43</v>
-      </c>
       <c r="D8" s="29"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="28"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="29"/>
       <c r="J8" s="29"/>
       <c r="K8" s="29"/>
       <c r="L8" s="29"/>
       <c r="M8" s="29"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="57"/>
-      <c r="P8" s="38"/>
+      <c r="N8" s="59"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="29"/>
       <c r="Q8" s="29"/>
-      <c r="R8" s="29"/>
+      <c r="R8" s="15" t="s">
+        <v>43</v>
+      </c>
       <c r="S8" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="T8" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="U8" s="40"/>
-      <c r="V8" s="35"/>
-      <c r="W8" s="38"/>
-      <c r="X8" s="38"/>
-      <c r="Y8" s="26"/>
-      <c r="Z8" s="61"/>
+      <c r="T8" s="67"/>
+      <c r="U8" s="65"/>
+      <c r="V8" s="25"/>
+      <c r="W8" s="25"/>
+      <c r="X8" s="46"/>
+      <c r="Y8" s="49"/>
+      <c r="Z8" s="29"/>
       <c r="AA8" s="29"/>
-      <c r="AB8" s="29"/>
-      <c r="AC8" s="28"/>
-      <c r="AD8" s="29"/>
-      <c r="AE8" s="28"/>
-      <c r="AF8" s="29"/>
-      <c r="AG8" s="26"/>
-      <c r="AH8" s="50"/>
-      <c r="AI8" s="28"/>
-      <c r="AJ8" s="57"/>
-      <c r="AK8" s="38"/>
+      <c r="AB8" s="42"/>
+      <c r="AC8" s="29"/>
+      <c r="AD8" s="42"/>
+      <c r="AE8" s="29"/>
+      <c r="AF8" s="46"/>
+      <c r="AG8" s="27"/>
+      <c r="AH8" s="42"/>
+      <c r="AI8" s="59"/>
+      <c r="AJ8" s="25"/>
+      <c r="AK8" s="29"/>
       <c r="AL8" s="29"/>
       <c r="AM8" s="29"/>
       <c r="AN8" s="29"/>
       <c r="AO8" s="29"/>
-      <c r="AP8" s="29"/>
-      <c r="AQ8" s="26"/>
-      <c r="AR8" s="26"/>
+      <c r="AP8" s="46"/>
+      <c r="AQ8" s="46"/>
     </row>
-    <row r="9" spans="1:44" ht="15" thickTop="1"/>
-    <row r="11" spans="1:44">
-      <c r="B11" s="21" t="s">
+    <row r="9" spans="1:43" ht="15" thickTop="1">
+      <c r="Y9" s="23"/>
+    </row>
+    <row r="10" spans="1:43">
+      <c r="Y10" s="23"/>
+    </row>
+    <row r="12" spans="1:43">
+      <c r="B12" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="G12" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+    </row>
+    <row r="13" spans="1:43">
+      <c r="B13" s="20"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+    </row>
+    <row r="14" spans="1:43">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="21"/>
+      <c r="H14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+    </row>
+    <row r="15" spans="1:43">
+      <c r="B15" s="21"/>
+      <c r="C15" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="H15" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="30"/>
+    </row>
+    <row r="16" spans="1:43">
+      <c r="B16" s="21"/>
+      <c r="C16" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-    </row>
-    <row r="12" spans="1:44">
-      <c r="B12" s="21"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-    </row>
-    <row r="13" spans="1:44">
-      <c r="B13" s="22"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="22"/>
-    </row>
-    <row r="14" spans="1:44">
-      <c r="B14" s="22"/>
-      <c r="C14" s="69" t="s">
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="H16" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
-      <c r="F14" s="22"/>
-      <c r="H14" s="69" t="s">
-        <v>52</v>
-      </c>
-      <c r="I14" s="69"/>
-      <c r="J14" s="69"/>
-      <c r="K14" s="69"/>
-      <c r="L14" s="22"/>
-    </row>
-    <row r="15" spans="1:44">
-      <c r="B15" s="22"/>
-      <c r="C15" s="70" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
-      <c r="F15" s="22"/>
-      <c r="H15" s="70" t="s">
-        <v>54</v>
-      </c>
-      <c r="I15" s="70"/>
-      <c r="J15" s="70"/>
-      <c r="K15" s="70"/>
-      <c r="L15" s="22"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="50">
+  <mergeCells count="49">
+    <mergeCell ref="AP6:AP8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="F6:N6"/>
+    <mergeCell ref="O6:T6"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="V6:V8"/>
+    <mergeCell ref="W6:W8"/>
+    <mergeCell ref="T7:T8"/>
     <mergeCell ref="P7:P8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="Q7:Q8"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="K7:K8"/>
     <mergeCell ref="M7:M8"/>
-    <mergeCell ref="H14:K14"/>
-    <mergeCell ref="H15:K15"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="AQ6:AQ8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="AC6:AE6"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AC7:AC8"/>
+    <mergeCell ref="AD7:AD8"/>
+    <mergeCell ref="AE7:AE8"/>
+    <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="AJ6:AJ8"/>
+    <mergeCell ref="AK6:AK8"/>
+    <mergeCell ref="AL6:AL8"/>
+    <mergeCell ref="AI6:AI8"/>
+    <mergeCell ref="AM6:AM8"/>
+    <mergeCell ref="AO6:AO8"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="B6:C7"/>
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="AG4:AH4"/>
+    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="X6:X8"/>
     <mergeCell ref="Y6:Y8"/>
     <mergeCell ref="Z6:Z8"/>
     <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="AR6:AR8"/>
-    <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="AD6:AF6"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AI6:AI8"/>
-    <mergeCell ref="AD7:AD8"/>
-    <mergeCell ref="AE7:AE8"/>
-    <mergeCell ref="AF7:AF8"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="AM6:AM8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="AP6:AP8"/>
-    <mergeCell ref="AQ6:AQ8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="G6:O6"/>
-    <mergeCell ref="P6:U6"/>
-    <mergeCell ref="V6:V8"/>
-    <mergeCell ref="W6:W8"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="U7:U8"/>
-    <mergeCell ref="Q7:Q8"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C16:E16"/>
     <mergeCell ref="L7:L8"/>
-    <mergeCell ref="N7:N8"/>
-    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="H15:K15"/>
+    <mergeCell ref="H16:K16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/iLgs/App_Data/CustodianVehiclesTemplate.xlsx
+++ b/iLgs/App_Data/CustodianVehiclesTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Templates New/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="8_{C24A2B6E-C141-4441-9F51-293C5BCBCD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62214753-6BFB-4F13-B738-111A1AF85A72}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="8_{C24A2B6E-C141-4441-9F51-293C5BCBCD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{368BE648-E03A-4E8E-90F5-B828BC45B23F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{49C2EA6D-0E15-4E51-9FB1-ADBE484D14AF}"/>
   </bookViews>
@@ -721,7 +721,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -766,25 +766,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
@@ -793,10 +774,19 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -847,6 +837,15 @@
     <xf numFmtId="43" fontId="6" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -909,6 +908,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1416,8 +1421,8 @@
       <c r="Q4" s="10"/>
       <c r="T4" s="19"/>
       <c r="Y4" s="6"/>
-      <c r="AF4" s="43"/>
-      <c r="AG4" s="43"/>
+      <c r="AF4" s="39"/>
+      <c r="AG4" s="39"/>
       <c r="AH4" s="10"/>
       <c r="AI4" s="10"/>
       <c r="AJ4" s="2"/>
@@ -1473,241 +1478,370 @@
       <c r="AP5" s="2"/>
     </row>
     <row r="6" spans="1:43" ht="15" customHeight="1" thickTop="1">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="38" t="s">
+      <c r="C6" s="31"/>
+      <c r="D6" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="40" t="s">
+      <c r="E6" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="60" t="s">
+      <c r="F6" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="61"/>
-      <c r="M6" s="61"/>
-      <c r="N6" s="62"/>
-      <c r="O6" s="60" t="s">
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="60"/>
+      <c r="K6" s="60"/>
+      <c r="L6" s="60"/>
+      <c r="M6" s="60"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="P6" s="61"/>
-      <c r="Q6" s="61"/>
-      <c r="R6" s="61"/>
-      <c r="S6" s="61"/>
-      <c r="T6" s="62"/>
-      <c r="U6" s="63" t="s">
+      <c r="P6" s="60"/>
+      <c r="Q6" s="60"/>
+      <c r="R6" s="60"/>
+      <c r="S6" s="60"/>
+      <c r="T6" s="61"/>
+      <c r="U6" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="V6" s="32" t="s">
+      <c r="V6" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="W6" s="32" t="s">
+      <c r="W6" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="X6" s="44" t="s">
+      <c r="X6" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="Y6" s="47" t="s">
+      <c r="Y6" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="Z6" s="38" t="s">
+      <c r="Z6" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="AA6" s="38" t="s">
+      <c r="AA6" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="AB6" s="40" t="s">
+      <c r="AB6" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="AC6" s="50" t="s">
+      <c r="AC6" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AD6" s="51"/>
-      <c r="AE6" s="52"/>
-      <c r="AF6" s="44" t="s">
+      <c r="AD6" s="50"/>
+      <c r="AE6" s="51"/>
+      <c r="AF6" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="AG6" s="53" t="s">
+      <c r="AG6" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="AH6" s="40" t="s">
+      <c r="AH6" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="AI6" s="57" t="s">
+      <c r="AI6" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="AJ6" s="32" t="s">
+      <c r="AJ6" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="AK6" s="38" t="s">
+      <c r="AK6" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="AL6" s="38" t="s">
+      <c r="AL6" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="AM6" s="38" t="s">
+      <c r="AM6" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="AN6" s="38" t="s">
+      <c r="AN6" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="AO6" s="38" t="s">
+      <c r="AO6" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="AP6" s="44" t="s">
+      <c r="AP6" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="AQ6" s="44" t="s">
+      <c r="AQ6" s="40" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:43">
-      <c r="A7" s="33"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="26" t="s">
+      <c r="A7" s="28"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="28" t="s">
+      <c r="G7" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="H7" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="28" t="s">
+      <c r="I7" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="J7" s="28" t="s">
+      <c r="J7" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="K7" s="28" t="s">
+      <c r="K7" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="L7" s="28" t="s">
+      <c r="L7" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="M7" s="28" t="s">
+      <c r="M7" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="N7" s="70" t="s">
+      <c r="N7" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="O7" s="24" t="s">
+      <c r="O7" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="P7" s="28" t="s">
+      <c r="P7" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="Q7" s="28" t="s">
+      <c r="Q7" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="R7" s="68" t="s">
+      <c r="R7" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="S7" s="69"/>
-      <c r="T7" s="66" t="s">
+      <c r="S7" s="68"/>
+      <c r="T7" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="U7" s="64"/>
-      <c r="V7" s="33"/>
-      <c r="W7" s="33"/>
-      <c r="X7" s="45"/>
-      <c r="Y7" s="48"/>
-      <c r="Z7" s="39"/>
-      <c r="AA7" s="39"/>
-      <c r="AB7" s="41"/>
-      <c r="AC7" s="55" t="s">
+      <c r="U7" s="63"/>
+      <c r="V7" s="28"/>
+      <c r="W7" s="28"/>
+      <c r="X7" s="41"/>
+      <c r="Y7" s="44"/>
+      <c r="Z7" s="35"/>
+      <c r="AA7" s="35"/>
+      <c r="AB7" s="37"/>
+      <c r="AC7" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="AD7" s="56" t="s">
+      <c r="AD7" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="AE7" s="55" t="s">
+      <c r="AE7" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="AF7" s="45"/>
-      <c r="AG7" s="54"/>
-      <c r="AH7" s="41"/>
-      <c r="AI7" s="58"/>
-      <c r="AJ7" s="33"/>
-      <c r="AK7" s="39"/>
-      <c r="AL7" s="39"/>
-      <c r="AM7" s="39"/>
-      <c r="AN7" s="39"/>
-      <c r="AO7" s="39"/>
-      <c r="AP7" s="45"/>
-      <c r="AQ7" s="45"/>
+      <c r="AF7" s="41"/>
+      <c r="AG7" s="53"/>
+      <c r="AH7" s="37"/>
+      <c r="AI7" s="57"/>
+      <c r="AJ7" s="28"/>
+      <c r="AK7" s="35"/>
+      <c r="AL7" s="35"/>
+      <c r="AM7" s="35"/>
+      <c r="AN7" s="35"/>
+      <c r="AO7" s="35"/>
+      <c r="AP7" s="41"/>
+      <c r="AQ7" s="41"/>
     </row>
     <row r="8" spans="1:43" ht="34.799999999999997" customHeight="1" thickBot="1">
-      <c r="A8" s="25"/>
+      <c r="A8" s="29"/>
       <c r="B8" s="14" t="s">
         <v>41</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="29"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="59"/>
-      <c r="O8" s="25"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="29"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="58"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="26"/>
       <c r="R8" s="15" t="s">
         <v>43</v>
       </c>
       <c r="S8" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="T8" s="67"/>
-      <c r="U8" s="65"/>
-      <c r="V8" s="25"/>
-      <c r="W8" s="25"/>
-      <c r="X8" s="46"/>
-      <c r="Y8" s="49"/>
-      <c r="Z8" s="29"/>
-      <c r="AA8" s="29"/>
-      <c r="AB8" s="42"/>
-      <c r="AC8" s="29"/>
-      <c r="AD8" s="42"/>
-      <c r="AE8" s="29"/>
-      <c r="AF8" s="46"/>
-      <c r="AG8" s="27"/>
-      <c r="AH8" s="42"/>
-      <c r="AI8" s="59"/>
-      <c r="AJ8" s="25"/>
-      <c r="AK8" s="29"/>
-      <c r="AL8" s="29"/>
-      <c r="AM8" s="29"/>
-      <c r="AN8" s="29"/>
-      <c r="AO8" s="29"/>
-      <c r="AP8" s="46"/>
-      <c r="AQ8" s="46"/>
+      <c r="T8" s="66"/>
+      <c r="U8" s="64"/>
+      <c r="V8" s="29"/>
+      <c r="W8" s="29"/>
+      <c r="X8" s="42"/>
+      <c r="Y8" s="45"/>
+      <c r="Z8" s="26"/>
+      <c r="AA8" s="26"/>
+      <c r="AB8" s="38"/>
+      <c r="AC8" s="26"/>
+      <c r="AD8" s="38"/>
+      <c r="AE8" s="26"/>
+      <c r="AF8" s="42"/>
+      <c r="AG8" s="48"/>
+      <c r="AH8" s="38"/>
+      <c r="AI8" s="58"/>
+      <c r="AJ8" s="29"/>
+      <c r="AK8" s="26"/>
+      <c r="AL8" s="26"/>
+      <c r="AM8" s="26"/>
+      <c r="AN8" s="26"/>
+      <c r="AO8" s="26"/>
+      <c r="AP8" s="42"/>
+      <c r="AQ8" s="42"/>
     </row>
     <row r="9" spans="1:43" ht="15" thickTop="1">
-      <c r="Y9" s="23"/>
+      <c r="A9" s="70"/>
+      <c r="B9" s="70"/>
+      <c r="C9" s="70"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="70"/>
+      <c r="K9" s="70"/>
+      <c r="L9" s="70"/>
+      <c r="M9" s="70"/>
+      <c r="N9" s="70"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="70"/>
+      <c r="Q9" s="70"/>
+      <c r="R9" s="70"/>
+      <c r="S9" s="70"/>
+      <c r="T9" s="70"/>
+      <c r="U9" s="70"/>
+      <c r="V9" s="70"/>
+      <c r="W9" s="70"/>
+      <c r="X9" s="70"/>
+      <c r="Y9" s="71"/>
+      <c r="Z9" s="70"/>
+      <c r="AA9" s="70"/>
+      <c r="AB9" s="70"/>
+      <c r="AC9" s="70"/>
+      <c r="AD9" s="70"/>
+      <c r="AE9" s="70"/>
+      <c r="AF9" s="70"/>
+      <c r="AG9" s="70"/>
+      <c r="AH9" s="70"/>
+      <c r="AI9" s="70"/>
+      <c r="AJ9" s="70"/>
+      <c r="AK9" s="70"/>
+      <c r="AL9" s="70"/>
+      <c r="AM9" s="70"/>
+      <c r="AN9" s="70"/>
+      <c r="AO9" s="70"/>
+      <c r="AP9" s="70"/>
+      <c r="AQ9" s="70"/>
     </row>
     <row r="10" spans="1:43">
-      <c r="Y10" s="23"/>
+      <c r="A10" s="70"/>
+      <c r="B10" s="70"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="70"/>
+      <c r="K10" s="70"/>
+      <c r="L10" s="70"/>
+      <c r="M10" s="70"/>
+      <c r="N10" s="70"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="70"/>
+      <c r="Q10" s="70"/>
+      <c r="R10" s="70"/>
+      <c r="S10" s="70"/>
+      <c r="T10" s="70"/>
+      <c r="U10" s="70"/>
+      <c r="V10" s="70"/>
+      <c r="W10" s="70"/>
+      <c r="X10" s="70"/>
+      <c r="Y10" s="71"/>
+      <c r="Z10" s="70"/>
+      <c r="AA10" s="70"/>
+      <c r="AB10" s="70"/>
+      <c r="AC10" s="70"/>
+      <c r="AD10" s="70"/>
+      <c r="AE10" s="70"/>
+      <c r="AF10" s="70"/>
+      <c r="AG10" s="70"/>
+      <c r="AH10" s="70"/>
+      <c r="AI10" s="70"/>
+      <c r="AJ10" s="70"/>
+      <c r="AK10" s="70"/>
+      <c r="AL10" s="70"/>
+      <c r="AM10" s="70"/>
+      <c r="AN10" s="70"/>
+      <c r="AO10" s="70"/>
+      <c r="AP10" s="70"/>
+      <c r="AQ10" s="70"/>
+    </row>
+    <row r="11" spans="1:43">
+      <c r="A11" s="70"/>
+      <c r="B11" s="70"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="70"/>
+      <c r="K11" s="70"/>
+      <c r="L11" s="70"/>
+      <c r="M11" s="70"/>
+      <c r="N11" s="70"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="70"/>
+      <c r="Q11" s="70"/>
+      <c r="R11" s="70"/>
+      <c r="S11" s="70"/>
+      <c r="T11" s="70"/>
+      <c r="U11" s="70"/>
+      <c r="V11" s="70"/>
+      <c r="W11" s="70"/>
+      <c r="X11" s="70"/>
+      <c r="Y11" s="70"/>
+      <c r="Z11" s="70"/>
+      <c r="AA11" s="70"/>
+      <c r="AB11" s="70"/>
+      <c r="AC11" s="70"/>
+      <c r="AD11" s="70"/>
+      <c r="AE11" s="70"/>
+      <c r="AF11" s="70"/>
+      <c r="AG11" s="70"/>
+      <c r="AH11" s="70"/>
+      <c r="AI11" s="70"/>
+      <c r="AJ11" s="70"/>
+      <c r="AK11" s="70"/>
+      <c r="AL11" s="70"/>
+      <c r="AM11" s="70"/>
+      <c r="AN11" s="70"/>
+      <c r="AO11" s="70"/>
+      <c r="AP11" s="70"/>
+      <c r="AQ11" s="70"/>
     </row>
     <row r="12" spans="1:43">
       <c r="B12" s="20" t="s">
@@ -1748,31 +1882,31 @@
     </row>
     <row r="15" spans="1:43">
       <c r="B15" s="21"/>
-      <c r="C15" s="30" t="s">
+      <c r="C15" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="H15" s="30" t="s">
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="H15" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
     </row>
     <row r="16" spans="1:43">
       <c r="B16" s="21"/>
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="H16" s="31" t="s">
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="H16" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="49">

--- a/iLgs/App_Data/CustodianVehiclesTemplate.xlsx
+++ b/iLgs/App_Data/CustodianVehiclesTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Templates New/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="8_{C24A2B6E-C141-4441-9F51-293C5BCBCD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{368BE648-E03A-4E8E-90F5-B828BC45B23F}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="8_{C24A2B6E-C141-4441-9F51-293C5BCBCD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A7C33AE-3A91-4BFC-952E-15A6C0369EB3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{49C2EA6D-0E15-4E51-9FB1-ADBE484D14AF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
   <si>
     <t>Custodian
 Item
@@ -45,9 +45,6 @@
 Number</t>
   </si>
   <si>
-    <t>Sub-Account</t>
-  </si>
-  <si>
     <t>DESCRIPTION</t>
   </si>
   <si>
@@ -126,9 +123,6 @@
     <t>Set/Lot #</t>
   </si>
   <si>
-    <t>Sub-Article</t>
-  </si>
-  <si>
     <t>Make / 
 Brand</t>
   </si>
@@ -227,6 +221,9 @@
   </si>
   <si>
     <t>Verified by:</t>
+  </si>
+  <si>
+    <t>Sub-Account / Article</t>
   </si>
 </sst>
 </file>
@@ -320,7 +317,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="45">
     <border>
       <left/>
       <right/>
@@ -335,154 +332,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -532,19 +381,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -618,84 +454,6 @@
         <color indexed="64"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -714,6 +472,387 @@
         <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -721,7 +860,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -748,15 +887,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -765,8 +895,65 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -774,146 +961,135 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1234,72 +1410,72 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00C28830-284B-4C5E-B18C-8421255AA9A0}">
-  <dimension ref="A1:AQ16"/>
+  <dimension ref="A1:AP16"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" style="17" customWidth="1"/>
-    <col min="2" max="2" width="18.88671875" style="17" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.44140625" style="17" customWidth="1"/>
-    <col min="5" max="5" width="29.88671875" style="17" customWidth="1"/>
-    <col min="6" max="6" width="10.88671875" style="17" customWidth="1"/>
-    <col min="7" max="7" width="9.77734375" style="17" customWidth="1"/>
-    <col min="8" max="8" width="9.21875" style="17" customWidth="1"/>
-    <col min="9" max="9" width="7.33203125" style="17" customWidth="1"/>
-    <col min="10" max="11" width="15" style="17" customWidth="1"/>
-    <col min="12" max="12" width="12.33203125" style="17" customWidth="1"/>
-    <col min="13" max="13" width="11.5546875" style="17" customWidth="1"/>
-    <col min="14" max="14" width="8.88671875" style="17"/>
-    <col min="15" max="15" width="14.6640625" style="17" customWidth="1"/>
-    <col min="16" max="16" width="12.33203125" style="17" customWidth="1"/>
-    <col min="17" max="17" width="17.33203125" style="17" customWidth="1"/>
-    <col min="18" max="18" width="11.5546875" style="17" customWidth="1"/>
-    <col min="19" max="19" width="10.6640625" style="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.88671875" style="17"/>
-    <col min="21" max="21" width="12.44140625" style="17" customWidth="1"/>
-    <col min="22" max="23" width="8.88671875" style="17"/>
-    <col min="24" max="24" width="13.44140625" style="17" customWidth="1"/>
-    <col min="25" max="25" width="11.21875" style="17" customWidth="1"/>
-    <col min="26" max="26" width="11.5546875" style="17" customWidth="1"/>
-    <col min="27" max="27" width="13.77734375" style="17" customWidth="1"/>
-    <col min="28" max="28" width="11.109375" style="17" customWidth="1"/>
-    <col min="29" max="29" width="13.44140625" style="17" customWidth="1"/>
-    <col min="30" max="30" width="14.33203125" style="17" customWidth="1"/>
-    <col min="31" max="31" width="19.21875" style="17" customWidth="1"/>
-    <col min="32" max="32" width="22.88671875" style="17" customWidth="1"/>
-    <col min="33" max="39" width="8.88671875" style="17"/>
-    <col min="40" max="40" width="11.109375" style="17" customWidth="1"/>
-    <col min="41" max="41" width="11" style="17" customWidth="1"/>
-    <col min="42" max="16384" width="8.88671875" style="17"/>
+    <col min="1" max="1" width="13.44140625" style="14" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" style="14" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" style="14" customWidth="1"/>
+    <col min="5" max="5" width="29.88671875" style="14" customWidth="1"/>
+    <col min="6" max="6" width="9.77734375" style="14" customWidth="1"/>
+    <col min="7" max="7" width="9.21875" style="14" customWidth="1"/>
+    <col min="8" max="8" width="7.33203125" style="14" customWidth="1"/>
+    <col min="9" max="10" width="15" style="14" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" style="14" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" style="14" customWidth="1"/>
+    <col min="13" max="13" width="8.88671875" style="14"/>
+    <col min="14" max="14" width="14.6640625" style="14" customWidth="1"/>
+    <col min="15" max="15" width="12.33203125" style="14" customWidth="1"/>
+    <col min="16" max="16" width="17.33203125" style="14" customWidth="1"/>
+    <col min="17" max="17" width="11.5546875" style="14" customWidth="1"/>
+    <col min="18" max="18" width="10.6640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.88671875" style="14"/>
+    <col min="20" max="20" width="12.44140625" style="14" customWidth="1"/>
+    <col min="21" max="22" width="8.88671875" style="14"/>
+    <col min="23" max="23" width="13.44140625" style="14" customWidth="1"/>
+    <col min="24" max="24" width="11.21875" style="14" customWidth="1"/>
+    <col min="25" max="25" width="11.5546875" style="14" customWidth="1"/>
+    <col min="26" max="26" width="13.77734375" style="14" customWidth="1"/>
+    <col min="27" max="27" width="11.109375" style="14" customWidth="1"/>
+    <col min="28" max="28" width="13.44140625" style="14" customWidth="1"/>
+    <col min="29" max="29" width="14.33203125" style="14" customWidth="1"/>
+    <col min="30" max="30" width="19.21875" style="14" customWidth="1"/>
+    <col min="31" max="31" width="22.88671875" style="14" customWidth="1"/>
+    <col min="32" max="38" width="8.88671875" style="14"/>
+    <col min="39" max="39" width="11.109375" style="14" customWidth="1"/>
+    <col min="40" max="40" width="11" style="14" customWidth="1"/>
+    <col min="41" max="16384" width="8.88671875" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="20.399999999999999" customHeight="1">
+    <row r="1" spans="1:42" ht="20.399999999999999" customHeight="1">
       <c r="A1" s="12"/>
       <c r="B1" s="13"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
+      <c r="F1" s="3"/>
       <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="2"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="4"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
+      <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="7"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="2"/>
       <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
+      <c r="V1" s="4"/>
       <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="4"/>
       <c r="Z1" s="4"/>
-      <c r="AA1" s="4"/>
+      <c r="AA1" s="2"/>
       <c r="AB1" s="2"/>
       <c r="AC1" s="2"/>
       <c r="AD1" s="2"/>
@@ -1314,35 +1490,35 @@
       <c r="AM1" s="2"/>
       <c r="AN1" s="2"/>
       <c r="AO1" s="2"/>
-      <c r="AP1" s="2"/>
     </row>
-    <row r="2" spans="1:43" ht="15.6">
+    <row r="2" spans="1:42" ht="15.6">
       <c r="A2" s="12"/>
       <c r="B2" s="13"/>
       <c r="C2" s="1"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
+      <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="2"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
+      <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="2"/>
       <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
+      <c r="V2" s="4"/>
       <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="4"/>
       <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
+      <c r="AA2" s="2"/>
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
       <c r="AD2" s="2"/>
@@ -1357,35 +1533,35 @@
       <c r="AM2" s="2"/>
       <c r="AN2" s="2"/>
       <c r="AO2" s="2"/>
-      <c r="AP2" s="2"/>
     </row>
-    <row r="3" spans="1:43">
+    <row r="3" spans="1:42">
       <c r="A3" s="3"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
+      <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="2"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
+      <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
-      <c r="T3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="2"/>
       <c r="U3" s="2"/>
-      <c r="V3" s="2"/>
+      <c r="V3" s="4"/>
       <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
-      <c r="AA3" s="4"/>
+      <c r="AA3" s="2"/>
       <c r="AB3" s="2"/>
       <c r="AC3" s="2"/>
       <c r="AD3" s="2"/>
@@ -1400,40 +1576,38 @@
       <c r="AM3" s="2"/>
       <c r="AN3" s="2"/>
       <c r="AO3" s="2"/>
-      <c r="AP3" s="2"/>
     </row>
-    <row r="4" spans="1:43" ht="15.6">
+    <row r="4" spans="1:42" ht="15.6">
       <c r="A4" s="13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="18"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="10"/>
       <c r="K4" s="10"/>
       <c r="L4" s="10"/>
       <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
       <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-      <c r="T4" s="19"/>
-      <c r="Y4" s="6"/>
-      <c r="AF4" s="39"/>
-      <c r="AG4" s="39"/>
+      <c r="S4" s="16"/>
+      <c r="X4" s="6"/>
+      <c r="AE4" s="37"/>
+      <c r="AF4" s="37"/>
+      <c r="AG4" s="10"/>
       <c r="AH4" s="10"/>
-      <c r="AI4" s="10"/>
+      <c r="AI4" s="2"/>
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
       <c r="AL4" s="2"/>
       <c r="AM4" s="2"/>
       <c r="AN4" s="2"/>
       <c r="AO4" s="2"/>
-      <c r="AP4" s="2"/>
     </row>
-    <row r="5" spans="1:43" ht="15" thickBot="1">
+    <row r="5" spans="1:42" ht="15" thickBot="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1441,524 +1615,512 @@
       <c r="E5" s="2"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="2"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="10"/>
       <c r="K5" s="10"/>
       <c r="L5" s="10"/>
       <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="10"/>
       <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
+      <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="8"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="2"/>
       <c r="U5" s="2"/>
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
-      <c r="X5" s="2"/>
-      <c r="Y5" s="6"/>
+      <c r="X5" s="6"/>
+      <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
       <c r="AA5" s="2"/>
       <c r="AB5" s="2"/>
       <c r="AC5" s="2"/>
       <c r="AD5" s="2"/>
-      <c r="AE5" s="2"/>
+      <c r="AE5" s="11"/>
       <c r="AF5" s="11"/>
-      <c r="AG5" s="11"/>
+      <c r="AG5" s="10"/>
       <c r="AH5" s="10"/>
-      <c r="AI5" s="10"/>
+      <c r="AI5" s="2"/>
       <c r="AJ5" s="2"/>
       <c r="AK5" s="2"/>
       <c r="AL5" s="2"/>
       <c r="AM5" s="2"/>
       <c r="AN5" s="2"/>
       <c r="AO5" s="2"/>
-      <c r="AP5" s="2"/>
     </row>
-    <row r="6" spans="1:43" ht="15" customHeight="1" thickTop="1">
-      <c r="A6" s="27" t="s">
+    <row r="6" spans="1:42" ht="15" customHeight="1">
+      <c r="A6" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="31"/>
-      <c r="D6" s="34" t="s">
+      <c r="B6" s="54" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="55"/>
+      <c r="D6" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="59" t="s">
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="46"/>
+      <c r="N6" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="60"/>
-      <c r="K6" s="60"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="60"/>
-      <c r="N6" s="61"/>
-      <c r="O6" s="59" t="s">
+      <c r="O6" s="45"/>
+      <c r="P6" s="45"/>
+      <c r="Q6" s="45"/>
+      <c r="R6" s="45"/>
+      <c r="S6" s="57"/>
+      <c r="T6" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="P6" s="60"/>
-      <c r="Q6" s="60"/>
-      <c r="R6" s="60"/>
-      <c r="S6" s="60"/>
-      <c r="T6" s="61"/>
-      <c r="U6" s="62" t="s">
+      <c r="U6" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="V6" s="27" t="s">
+      <c r="V6" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="W6" s="27" t="s">
+      <c r="W6" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="X6" s="40" t="s">
+      <c r="X6" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="Y6" s="43" t="s">
+      <c r="Y6" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="Z6" s="34" t="s">
+      <c r="Z6" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="AA6" s="34" t="s">
+      <c r="AA6" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="AB6" s="36" t="s">
+      <c r="AB6" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="AC6" s="49" t="s">
+      <c r="AC6" s="64"/>
+      <c r="AD6" s="65"/>
+      <c r="AE6" s="60" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF6" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="AD6" s="50"/>
-      <c r="AE6" s="51"/>
-      <c r="AF6" s="40" t="s">
+      <c r="AG6" s="62" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH6" s="67" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI6" s="59" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ6" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK6" s="56" t="s">
+        <v>18</v>
+      </c>
+      <c r="AL6" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM6" s="56" t="s">
+        <v>20</v>
+      </c>
+      <c r="AN6" s="56" t="s">
+        <v>21</v>
+      </c>
+      <c r="AO6" s="60" t="s">
+        <v>22</v>
+      </c>
+      <c r="AP6" s="68" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:42">
+      <c r="A7" s="69"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="N7" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="O7" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="P7" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q7" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="R7" s="28"/>
+      <c r="S7" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="T7" s="24"/>
+      <c r="U7" s="25"/>
+      <c r="V7" s="25"/>
+      <c r="W7" s="22"/>
+      <c r="X7" s="38"/>
+      <c r="Y7" s="33"/>
+      <c r="Z7" s="33"/>
+      <c r="AA7" s="29"/>
+      <c r="AB7" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC7" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD7" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE7" s="22"/>
+      <c r="AF7" s="30"/>
+      <c r="AG7" s="29"/>
+      <c r="AH7" s="34"/>
+      <c r="AI7" s="25"/>
+      <c r="AJ7" s="33"/>
+      <c r="AK7" s="33"/>
+      <c r="AL7" s="33"/>
+      <c r="AM7" s="33"/>
+      <c r="AN7" s="33"/>
+      <c r="AO7" s="22"/>
+      <c r="AP7" s="70"/>
+    </row>
+    <row r="8" spans="1:42" ht="34.799999999999997" customHeight="1" thickBot="1">
+      <c r="A8" s="49"/>
+      <c r="B8" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="71" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="51"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="51"/>
+      <c r="M8" s="52"/>
+      <c r="N8" s="73"/>
+      <c r="O8" s="51"/>
+      <c r="P8" s="51"/>
+      <c r="Q8" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="R8" s="75" t="s">
+        <v>42</v>
+      </c>
+      <c r="S8" s="76"/>
+      <c r="T8" s="77"/>
+      <c r="U8" s="78"/>
+      <c r="V8" s="78"/>
+      <c r="W8" s="79"/>
+      <c r="X8" s="80"/>
+      <c r="Y8" s="51"/>
+      <c r="Z8" s="51"/>
+      <c r="AA8" s="50"/>
+      <c r="AB8" s="51"/>
+      <c r="AC8" s="50"/>
+      <c r="AD8" s="51"/>
+      <c r="AE8" s="79"/>
+      <c r="AF8" s="81"/>
+      <c r="AG8" s="50"/>
+      <c r="AH8" s="82"/>
+      <c r="AI8" s="78"/>
+      <c r="AJ8" s="51"/>
+      <c r="AK8" s="51"/>
+      <c r="AL8" s="51"/>
+      <c r="AM8" s="51"/>
+      <c r="AN8" s="51"/>
+      <c r="AO8" s="79"/>
+      <c r="AP8" s="83"/>
+    </row>
+    <row r="9" spans="1:42">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="20"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="20"/>
+      <c r="W9" s="20"/>
+      <c r="X9" s="21"/>
+      <c r="Y9" s="20"/>
+      <c r="Z9" s="20"/>
+      <c r="AA9" s="20"/>
+      <c r="AB9" s="20"/>
+      <c r="AC9" s="20"/>
+      <c r="AD9" s="20"/>
+      <c r="AE9" s="20"/>
+      <c r="AF9" s="20"/>
+      <c r="AG9" s="20"/>
+      <c r="AH9" s="20"/>
+      <c r="AI9" s="20"/>
+      <c r="AJ9" s="20"/>
+      <c r="AK9" s="20"/>
+      <c r="AL9" s="20"/>
+      <c r="AM9" s="20"/>
+      <c r="AN9" s="20"/>
+      <c r="AO9" s="20"/>
+      <c r="AP9" s="20"/>
+    </row>
+    <row r="10" spans="1:42">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="20"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="20"/>
+      <c r="W10" s="20"/>
+      <c r="X10" s="21"/>
+      <c r="Y10" s="20"/>
+      <c r="Z10" s="20"/>
+      <c r="AA10" s="20"/>
+      <c r="AB10" s="20"/>
+      <c r="AC10" s="20"/>
+      <c r="AD10" s="20"/>
+      <c r="AE10" s="20"/>
+      <c r="AF10" s="20"/>
+      <c r="AG10" s="20"/>
+      <c r="AH10" s="20"/>
+      <c r="AI10" s="20"/>
+      <c r="AJ10" s="20"/>
+      <c r="AK10" s="20"/>
+      <c r="AL10" s="20"/>
+      <c r="AM10" s="20"/>
+      <c r="AN10" s="20"/>
+      <c r="AO10" s="20"/>
+      <c r="AP10" s="20"/>
+    </row>
+    <row r="11" spans="1:42">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="20"/>
+      <c r="U11" s="20"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="20"/>
+      <c r="X11" s="20"/>
+      <c r="Y11" s="20"/>
+      <c r="Z11" s="20"/>
+      <c r="AA11" s="20"/>
+      <c r="AB11" s="20"/>
+      <c r="AC11" s="20"/>
+      <c r="AD11" s="20"/>
+      <c r="AE11" s="20"/>
+      <c r="AF11" s="20"/>
+      <c r="AG11" s="20"/>
+      <c r="AH11" s="20"/>
+      <c r="AI11" s="20"/>
+      <c r="AJ11" s="20"/>
+      <c r="AK11" s="20"/>
+      <c r="AL11" s="20"/>
+      <c r="AM11" s="20"/>
+      <c r="AN11" s="20"/>
+      <c r="AO11" s="20"/>
+      <c r="AP11" s="20"/>
+    </row>
+    <row r="12" spans="1:42">
+      <c r="B12" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="AG6" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH6" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="AI6" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="AJ6" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="AK6" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="AL6" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="AM6" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="AN6" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="AO6" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="AP6" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="AQ6" s="40" t="s">
-        <v>45</v>
-      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="G12" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="18"/>
     </row>
-    <row r="7" spans="1:43">
-      <c r="A7" s="28"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="47" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="L7" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="M7" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="N7" s="69" t="s">
-        <v>32</v>
-      </c>
-      <c r="O7" s="46" t="s">
-        <v>33</v>
-      </c>
-      <c r="P7" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q7" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="R7" s="67" t="s">
-        <v>36</v>
-      </c>
-      <c r="S7" s="68"/>
-      <c r="T7" s="65" t="s">
-        <v>37</v>
-      </c>
-      <c r="U7" s="63"/>
-      <c r="V7" s="28"/>
-      <c r="W7" s="28"/>
-      <c r="X7" s="41"/>
-      <c r="Y7" s="44"/>
-      <c r="Z7" s="35"/>
-      <c r="AA7" s="35"/>
-      <c r="AB7" s="37"/>
-      <c r="AC7" s="54" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD7" s="55" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE7" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF7" s="41"/>
-      <c r="AG7" s="53"/>
-      <c r="AH7" s="37"/>
-      <c r="AI7" s="57"/>
-      <c r="AJ7" s="28"/>
-      <c r="AK7" s="35"/>
-      <c r="AL7" s="35"/>
-      <c r="AM7" s="35"/>
-      <c r="AN7" s="35"/>
-      <c r="AO7" s="35"/>
-      <c r="AP7" s="41"/>
-      <c r="AQ7" s="41"/>
+    <row r="13" spans="1:42">
+      <c r="B13" s="17"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
     </row>
-    <row r="8" spans="1:43" ht="34.799999999999997" customHeight="1" thickBot="1">
-      <c r="A8" s="29"/>
-      <c r="B8" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="58"/>
-      <c r="O8" s="29"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="S8" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="T8" s="66"/>
-      <c r="U8" s="64"/>
-      <c r="V8" s="29"/>
-      <c r="W8" s="29"/>
-      <c r="X8" s="42"/>
-      <c r="Y8" s="45"/>
-      <c r="Z8" s="26"/>
-      <c r="AA8" s="26"/>
-      <c r="AB8" s="38"/>
-      <c r="AC8" s="26"/>
-      <c r="AD8" s="38"/>
-      <c r="AE8" s="26"/>
-      <c r="AF8" s="42"/>
-      <c r="AG8" s="48"/>
-      <c r="AH8" s="38"/>
-      <c r="AI8" s="58"/>
-      <c r="AJ8" s="29"/>
-      <c r="AK8" s="26"/>
-      <c r="AL8" s="26"/>
-      <c r="AM8" s="26"/>
-      <c r="AN8" s="26"/>
-      <c r="AO8" s="26"/>
-      <c r="AP8" s="42"/>
-      <c r="AQ8" s="42"/>
+    <row r="14" spans="1:42">
+      <c r="B14" s="18"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
     </row>
-    <row r="9" spans="1:43" ht="15" thickTop="1">
-      <c r="A9" s="70"/>
-      <c r="B9" s="70"/>
-      <c r="C9" s="70"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="70"/>
-      <c r="H9" s="70"/>
-      <c r="I9" s="70"/>
-      <c r="J9" s="70"/>
-      <c r="K9" s="70"/>
-      <c r="L9" s="70"/>
-      <c r="M9" s="70"/>
-      <c r="N9" s="70"/>
-      <c r="O9" s="70"/>
-      <c r="P9" s="70"/>
-      <c r="Q9" s="70"/>
-      <c r="R9" s="70"/>
-      <c r="S9" s="70"/>
-      <c r="T9" s="70"/>
-      <c r="U9" s="70"/>
-      <c r="V9" s="70"/>
-      <c r="W9" s="70"/>
-      <c r="X9" s="70"/>
-      <c r="Y9" s="71"/>
-      <c r="Z9" s="70"/>
-      <c r="AA9" s="70"/>
-      <c r="AB9" s="70"/>
-      <c r="AC9" s="70"/>
-      <c r="AD9" s="70"/>
-      <c r="AE9" s="70"/>
-      <c r="AF9" s="70"/>
-      <c r="AG9" s="70"/>
-      <c r="AH9" s="70"/>
-      <c r="AI9" s="70"/>
-      <c r="AJ9" s="70"/>
-      <c r="AK9" s="70"/>
-      <c r="AL9" s="70"/>
-      <c r="AM9" s="70"/>
-      <c r="AN9" s="70"/>
-      <c r="AO9" s="70"/>
-      <c r="AP9" s="70"/>
-      <c r="AQ9" s="70"/>
+    <row r="15" spans="1:42">
+      <c r="B15" s="18"/>
+      <c r="C15" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="H15" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
     </row>
-    <row r="10" spans="1:43">
-      <c r="A10" s="70"/>
-      <c r="B10" s="70"/>
-      <c r="C10" s="70"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="70"/>
-      <c r="J10" s="70"/>
-      <c r="K10" s="70"/>
-      <c r="L10" s="70"/>
-      <c r="M10" s="70"/>
-      <c r="N10" s="70"/>
-      <c r="O10" s="70"/>
-      <c r="P10" s="70"/>
-      <c r="Q10" s="70"/>
-      <c r="R10" s="70"/>
-      <c r="S10" s="70"/>
-      <c r="T10" s="70"/>
-      <c r="U10" s="70"/>
-      <c r="V10" s="70"/>
-      <c r="W10" s="70"/>
-      <c r="X10" s="70"/>
-      <c r="Y10" s="71"/>
-      <c r="Z10" s="70"/>
-      <c r="AA10" s="70"/>
-      <c r="AB10" s="70"/>
-      <c r="AC10" s="70"/>
-      <c r="AD10" s="70"/>
-      <c r="AE10" s="70"/>
-      <c r="AF10" s="70"/>
-      <c r="AG10" s="70"/>
-      <c r="AH10" s="70"/>
-      <c r="AI10" s="70"/>
-      <c r="AJ10" s="70"/>
-      <c r="AK10" s="70"/>
-      <c r="AL10" s="70"/>
-      <c r="AM10" s="70"/>
-      <c r="AN10" s="70"/>
-      <c r="AO10" s="70"/>
-      <c r="AP10" s="70"/>
-      <c r="AQ10" s="70"/>
-    </row>
-    <row r="11" spans="1:43">
-      <c r="A11" s="70"/>
-      <c r="B11" s="70"/>
-      <c r="C11" s="70"/>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="70"/>
-      <c r="K11" s="70"/>
-      <c r="L11" s="70"/>
-      <c r="M11" s="70"/>
-      <c r="N11" s="70"/>
-      <c r="O11" s="70"/>
-      <c r="P11" s="70"/>
-      <c r="Q11" s="70"/>
-      <c r="R11" s="70"/>
-      <c r="S11" s="70"/>
-      <c r="T11" s="70"/>
-      <c r="U11" s="70"/>
-      <c r="V11" s="70"/>
-      <c r="W11" s="70"/>
-      <c r="X11" s="70"/>
-      <c r="Y11" s="70"/>
-      <c r="Z11" s="70"/>
-      <c r="AA11" s="70"/>
-      <c r="AB11" s="70"/>
-      <c r="AC11" s="70"/>
-      <c r="AD11" s="70"/>
-      <c r="AE11" s="70"/>
-      <c r="AF11" s="70"/>
-      <c r="AG11" s="70"/>
-      <c r="AH11" s="70"/>
-      <c r="AI11" s="70"/>
-      <c r="AJ11" s="70"/>
-      <c r="AK11" s="70"/>
-      <c r="AL11" s="70"/>
-      <c r="AM11" s="70"/>
-      <c r="AN11" s="70"/>
-      <c r="AO11" s="70"/>
-      <c r="AP11" s="70"/>
-      <c r="AQ11" s="70"/>
-    </row>
-    <row r="12" spans="1:43">
-      <c r="B12" s="20" t="s">
+    <row r="16" spans="1:42">
+      <c r="B16" s="18"/>
+      <c r="C16" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="G12" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-    </row>
-    <row r="13" spans="1:43">
-      <c r="B13" s="20"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-    </row>
-    <row r="14" spans="1:43">
-      <c r="B14" s="21"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="21"/>
-      <c r="H14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-    </row>
-    <row r="15" spans="1:43">
-      <c r="B15" s="21"/>
-      <c r="C15" s="23" t="s">
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="H16" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="H15" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="I15" s="23"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
-    </row>
-    <row r="16" spans="1:43">
-      <c r="B16" s="21"/>
-      <c r="C16" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="H16" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="40"/>
     </row>
   </sheetData>
-  <mergeCells count="49">
-    <mergeCell ref="AP6:AP8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="F6:N6"/>
-    <mergeCell ref="O6:T6"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="V6:V8"/>
-    <mergeCell ref="W6:W8"/>
-    <mergeCell ref="T7:T8"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="Q7:Q8"/>
-    <mergeCell ref="R7:S7"/>
+  <mergeCells count="48">
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C16:E16"/>
     <mergeCell ref="K7:K8"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="N7:N8"/>
-    <mergeCell ref="AQ6:AQ8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="AC6:AE6"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AC7:AC8"/>
-    <mergeCell ref="AD7:AD8"/>
-    <mergeCell ref="AE7:AE8"/>
-    <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="AI6:AI8"/>
-    <mergeCell ref="AM6:AM8"/>
-    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="H15:K15"/>
+    <mergeCell ref="H16:K16"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="B6:C7"/>
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="E6:E8"/>
-    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="W6:W8"/>
     <mergeCell ref="X6:X8"/>
     <mergeCell ref="Y6:Y8"/>
     <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="F6:M6"/>
+    <mergeCell ref="AP6:AP8"/>
     <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="AB6:AD6"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="AB7:AB8"/>
+    <mergeCell ref="AC7:AC8"/>
+    <mergeCell ref="AD7:AD8"/>
+    <mergeCell ref="AM6:AM8"/>
+    <mergeCell ref="AI6:AI8"/>
+    <mergeCell ref="AJ6:AJ8"/>
+    <mergeCell ref="AK6:AK8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AL6:AL8"/>
+    <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="N6:S6"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="V6:V8"/>
+    <mergeCell ref="S7:S8"/>
     <mergeCell ref="O7:O8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="J7:J8"/>
     <mergeCell ref="L7:L8"/>
-    <mergeCell ref="H15:K15"/>
-    <mergeCell ref="H16:K16"/>
+    <mergeCell ref="M7:M8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/iLgs/App_Data/CustodianVehiclesTemplate.xlsx
+++ b/iLgs/App_Data/CustodianVehiclesTemplate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Templates New/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="91" documentId="8_{C24A2B6E-C141-4441-9F51-293C5BCBCD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A7C33AE-3A91-4BFC-952E-15A6C0369EB3}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="8_{C24A2B6E-C141-4441-9F51-293C5BCBCD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B89D7F2-A978-4AFB-903C-51271F4F99C9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{49C2EA6D-0E15-4E51-9FB1-ADBE484D14AF}"/>
   </bookViews>
@@ -317,7 +317,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="45">
+  <borders count="46">
     <border>
       <left/>
       <right/>
@@ -851,6 +851,15 @@
       </right>
       <top/>
       <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="hair">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -860,7 +869,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -902,56 +911,17 @@
     <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
@@ -961,16 +931,79 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -980,115 +1013,109 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1107,10 +1134,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1410,7 +1433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00C28830-284B-4C5E-B18C-8421255AA9A0}">
-  <dimension ref="A1:AP16"/>
+  <dimension ref="A1:AP17"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="14" customWidth="1"/>
@@ -1595,8 +1618,8 @@
       <c r="P4" s="10"/>
       <c r="S4" s="16"/>
       <c r="X4" s="6"/>
-      <c r="AE4" s="37"/>
-      <c r="AF4" s="37"/>
+      <c r="AE4" s="42"/>
+      <c r="AF4" s="42"/>
       <c r="AG4" s="10"/>
       <c r="AH4" s="10"/>
       <c r="AI4" s="2"/>
@@ -1651,318 +1674,318 @@
       <c r="AO5" s="2"/>
     </row>
     <row r="6" spans="1:42" ht="15" customHeight="1">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="55"/>
-      <c r="D6" s="56" t="s">
+      <c r="C6" s="35"/>
+      <c r="D6" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="54" t="s">
+      <c r="E6" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="F6" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="45"/>
-      <c r="M6" s="46"/>
-      <c r="N6" s="45" t="s">
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="53"/>
+      <c r="M6" s="54"/>
+      <c r="N6" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="O6" s="45"/>
-      <c r="P6" s="45"/>
-      <c r="Q6" s="45"/>
-      <c r="R6" s="45"/>
-      <c r="S6" s="57"/>
-      <c r="T6" s="58" t="s">
+      <c r="O6" s="53"/>
+      <c r="P6" s="53"/>
+      <c r="Q6" s="53"/>
+      <c r="R6" s="53"/>
+      <c r="S6" s="75"/>
+      <c r="T6" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="U6" s="59" t="s">
+      <c r="U6" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="V6" s="59" t="s">
+      <c r="V6" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="W6" s="60" t="s">
+      <c r="W6" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="X6" s="61" t="s">
+      <c r="X6" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="Y6" s="56" t="s">
+      <c r="Y6" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="Z6" s="56" t="s">
+      <c r="Z6" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="AA6" s="62" t="s">
+      <c r="AA6" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="AB6" s="63" t="s">
+      <c r="AB6" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="AC6" s="64"/>
-      <c r="AD6" s="65"/>
-      <c r="AE6" s="60" t="s">
+      <c r="AC6" s="62"/>
+      <c r="AD6" s="63"/>
+      <c r="AE6" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="AF6" s="66" t="s">
+      <c r="AF6" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="AG6" s="62" t="s">
+      <c r="AG6" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="AH6" s="67" t="s">
+      <c r="AH6" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="AI6" s="59" t="s">
+      <c r="AI6" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="AJ6" s="56" t="s">
+      <c r="AJ6" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="AK6" s="56" t="s">
+      <c r="AK6" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="AL6" s="56" t="s">
+      <c r="AL6" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="AM6" s="56" t="s">
+      <c r="AM6" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="AN6" s="56" t="s">
+      <c r="AN6" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="AO6" s="60" t="s">
+      <c r="AO6" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="AP6" s="68" t="s">
+      <c r="AP6" s="55" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:42">
-      <c r="A7" s="69"/>
-      <c r="B7" s="35"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="47" t="s">
+      <c r="A7" s="32"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="G7" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H7" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="23" t="s">
+      <c r="I7" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="J7" s="23" t="s">
+      <c r="J7" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="K7" s="23" t="s">
+      <c r="K7" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="L7" s="23" t="s">
+      <c r="L7" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="M7" s="48" t="s">
+      <c r="M7" s="83" t="s">
         <v>30</v>
       </c>
-      <c r="N7" s="43" t="s">
+      <c r="N7" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="O7" s="23" t="s">
+      <c r="O7" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="P7" s="23" t="s">
+      <c r="P7" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="Q7" s="27" t="s">
+      <c r="Q7" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="R7" s="28"/>
-      <c r="S7" s="26" t="s">
+      <c r="R7" s="82"/>
+      <c r="S7" s="79" t="s">
         <v>35</v>
       </c>
-      <c r="T7" s="24"/>
-      <c r="U7" s="25"/>
-      <c r="V7" s="25"/>
-      <c r="W7" s="22"/>
-      <c r="X7" s="38"/>
-      <c r="Y7" s="33"/>
-      <c r="Z7" s="33"/>
-      <c r="AA7" s="29"/>
-      <c r="AB7" s="31" t="s">
+      <c r="T7" s="77"/>
+      <c r="U7" s="70"/>
+      <c r="V7" s="70"/>
+      <c r="W7" s="44"/>
+      <c r="X7" s="47"/>
+      <c r="Y7" s="39"/>
+      <c r="Z7" s="39"/>
+      <c r="AA7" s="59"/>
+      <c r="AB7" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="AC7" s="32" t="s">
+      <c r="AC7" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="AD7" s="31" t="s">
+      <c r="AD7" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="AE7" s="22"/>
-      <c r="AF7" s="30"/>
-      <c r="AG7" s="29"/>
-      <c r="AH7" s="34"/>
-      <c r="AI7" s="25"/>
-      <c r="AJ7" s="33"/>
-      <c r="AK7" s="33"/>
-      <c r="AL7" s="33"/>
-      <c r="AM7" s="33"/>
-      <c r="AN7" s="33"/>
-      <c r="AO7" s="22"/>
-      <c r="AP7" s="70"/>
+      <c r="AE7" s="44"/>
+      <c r="AF7" s="65"/>
+      <c r="AG7" s="59"/>
+      <c r="AH7" s="73"/>
+      <c r="AI7" s="70"/>
+      <c r="AJ7" s="39"/>
+      <c r="AK7" s="39"/>
+      <c r="AL7" s="39"/>
+      <c r="AM7" s="39"/>
+      <c r="AN7" s="39"/>
+      <c r="AO7" s="44"/>
+      <c r="AP7" s="56"/>
     </row>
     <row r="8" spans="1:42" ht="34.799999999999997" customHeight="1" thickBot="1">
-      <c r="A8" s="49"/>
-      <c r="B8" s="71" t="s">
+      <c r="A8" s="33"/>
+      <c r="B8" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="71" t="s">
+      <c r="C8" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="51"/>
-      <c r="E8" s="72"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="52"/>
-      <c r="N8" s="73"/>
-      <c r="O8" s="51"/>
-      <c r="P8" s="51"/>
-      <c r="Q8" s="74" t="s">
+      <c r="D8" s="29"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="84"/>
+      <c r="N8" s="50"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="R8" s="75" t="s">
+      <c r="R8" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="S8" s="76"/>
-      <c r="T8" s="77"/>
-      <c r="U8" s="78"/>
-      <c r="V8" s="78"/>
-      <c r="W8" s="79"/>
-      <c r="X8" s="80"/>
-      <c r="Y8" s="51"/>
-      <c r="Z8" s="51"/>
-      <c r="AA8" s="50"/>
-      <c r="AB8" s="51"/>
-      <c r="AC8" s="50"/>
-      <c r="AD8" s="51"/>
-      <c r="AE8" s="79"/>
-      <c r="AF8" s="81"/>
-      <c r="AG8" s="50"/>
-      <c r="AH8" s="82"/>
-      <c r="AI8" s="78"/>
-      <c r="AJ8" s="51"/>
-      <c r="AK8" s="51"/>
-      <c r="AL8" s="51"/>
-      <c r="AM8" s="51"/>
-      <c r="AN8" s="51"/>
-      <c r="AO8" s="79"/>
-      <c r="AP8" s="83"/>
+      <c r="S8" s="80"/>
+      <c r="T8" s="78"/>
+      <c r="U8" s="71"/>
+      <c r="V8" s="71"/>
+      <c r="W8" s="45"/>
+      <c r="X8" s="48"/>
+      <c r="Y8" s="29"/>
+      <c r="Z8" s="29"/>
+      <c r="AA8" s="60"/>
+      <c r="AB8" s="29"/>
+      <c r="AC8" s="60"/>
+      <c r="AD8" s="29"/>
+      <c r="AE8" s="45"/>
+      <c r="AF8" s="66"/>
+      <c r="AG8" s="60"/>
+      <c r="AH8" s="74"/>
+      <c r="AI8" s="71"/>
+      <c r="AJ8" s="29"/>
+      <c r="AK8" s="29"/>
+      <c r="AL8" s="29"/>
+      <c r="AM8" s="29"/>
+      <c r="AN8" s="29"/>
+      <c r="AO8" s="45"/>
+      <c r="AP8" s="57"/>
     </row>
-    <row r="9" spans="1:42">
-      <c r="A9" s="20"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="20"/>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="20"/>
-      <c r="S9" s="20"/>
-      <c r="T9" s="20"/>
-      <c r="U9" s="20"/>
-      <c r="V9" s="20"/>
-      <c r="W9" s="20"/>
-      <c r="X9" s="21"/>
-      <c r="Y9" s="20"/>
-      <c r="Z9" s="20"/>
-      <c r="AA9" s="20"/>
-      <c r="AB9" s="20"/>
-      <c r="AC9" s="20"/>
-      <c r="AD9" s="20"/>
-      <c r="AE9" s="20"/>
-      <c r="AF9" s="20"/>
-      <c r="AG9" s="20"/>
-      <c r="AH9" s="20"/>
-      <c r="AI9" s="20"/>
-      <c r="AJ9" s="20"/>
-      <c r="AK9" s="20"/>
-      <c r="AL9" s="20"/>
-      <c r="AM9" s="20"/>
-      <c r="AN9" s="20"/>
-      <c r="AO9" s="20"/>
-      <c r="AP9" s="20"/>
+    <row r="9" spans="1:42" ht="34.799999999999997" hidden="1" customHeight="1">
+      <c r="A9" s="87"/>
+      <c r="B9" s="87"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="87"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="87"/>
+      <c r="I9" s="87"/>
+      <c r="J9" s="87"/>
+      <c r="K9" s="87"/>
+      <c r="L9" s="87"/>
+      <c r="M9" s="22"/>
+      <c r="N9" s="87"/>
+      <c r="O9" s="87"/>
+      <c r="P9" s="87"/>
+      <c r="Q9" s="22"/>
+      <c r="R9" s="22"/>
+      <c r="S9" s="88"/>
+      <c r="T9" s="87"/>
+      <c r="U9" s="87"/>
+      <c r="V9" s="87"/>
+      <c r="W9" s="87"/>
+      <c r="X9" s="89"/>
+      <c r="Y9" s="87"/>
+      <c r="Z9" s="87"/>
+      <c r="AA9" s="22"/>
+      <c r="AB9" s="87"/>
+      <c r="AC9" s="22"/>
+      <c r="AD9" s="87"/>
+      <c r="AE9" s="87"/>
+      <c r="AF9" s="22"/>
+      <c r="AG9" s="22"/>
+      <c r="AH9" s="22"/>
+      <c r="AI9" s="87"/>
+      <c r="AJ9" s="87"/>
+      <c r="AK9" s="87"/>
+      <c r="AL9" s="87"/>
+      <c r="AM9" s="87"/>
+      <c r="AN9" s="87"/>
+      <c r="AO9" s="87"/>
+      <c r="AP9" s="87"/>
     </row>
     <row r="10" spans="1:42">
-      <c r="A10" s="20"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="20"/>
-      <c r="N10" s="20"/>
-      <c r="O10" s="20"/>
-      <c r="P10" s="20"/>
-      <c r="Q10" s="20"/>
-      <c r="R10" s="20"/>
-      <c r="S10" s="20"/>
-      <c r="T10" s="20"/>
-      <c r="U10" s="20"/>
-      <c r="V10" s="20"/>
-      <c r="W10" s="20"/>
-      <c r="X10" s="21"/>
-      <c r="Y10" s="20"/>
-      <c r="Z10" s="20"/>
-      <c r="AA10" s="20"/>
-      <c r="AB10" s="20"/>
-      <c r="AC10" s="20"/>
-      <c r="AD10" s="20"/>
-      <c r="AE10" s="20"/>
-      <c r="AF10" s="20"/>
-      <c r="AG10" s="20"/>
-      <c r="AH10" s="20"/>
-      <c r="AI10" s="20"/>
-      <c r="AJ10" s="20"/>
-      <c r="AK10" s="20"/>
-      <c r="AL10" s="20"/>
-      <c r="AM10" s="20"/>
-      <c r="AN10" s="20"/>
-      <c r="AO10" s="20"/>
-      <c r="AP10" s="20"/>
+      <c r="A10" s="85"/>
+      <c r="B10" s="85"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="85"/>
+      <c r="H10" s="85"/>
+      <c r="I10" s="85"/>
+      <c r="J10" s="85"/>
+      <c r="K10" s="85"/>
+      <c r="L10" s="85"/>
+      <c r="M10" s="85"/>
+      <c r="N10" s="85"/>
+      <c r="O10" s="85"/>
+      <c r="P10" s="85"/>
+      <c r="Q10" s="85"/>
+      <c r="R10" s="85"/>
+      <c r="S10" s="85"/>
+      <c r="T10" s="85"/>
+      <c r="U10" s="85"/>
+      <c r="V10" s="85"/>
+      <c r="W10" s="85"/>
+      <c r="X10" s="86"/>
+      <c r="Y10" s="85"/>
+      <c r="Z10" s="85"/>
+      <c r="AA10" s="85"/>
+      <c r="AB10" s="85"/>
+      <c r="AC10" s="85"/>
+      <c r="AD10" s="85"/>
+      <c r="AE10" s="85"/>
+      <c r="AF10" s="85"/>
+      <c r="AG10" s="85"/>
+      <c r="AH10" s="85"/>
+      <c r="AI10" s="85"/>
+      <c r="AJ10" s="85"/>
+      <c r="AK10" s="85"/>
+      <c r="AL10" s="85"/>
+      <c r="AM10" s="85"/>
+      <c r="AN10" s="85"/>
+      <c r="AO10" s="85"/>
+      <c r="AP10" s="85"/>
     </row>
     <row r="11" spans="1:42">
       <c r="A11" s="20"/>
@@ -1988,7 +2011,7 @@
       <c r="U11" s="20"/>
       <c r="V11" s="20"/>
       <c r="W11" s="20"/>
-      <c r="X11" s="20"/>
+      <c r="X11" s="21"/>
       <c r="Y11" s="20"/>
       <c r="Z11" s="20"/>
       <c r="AA11" s="20"/>
@@ -2009,87 +2032,129 @@
       <c r="AP11" s="20"/>
     </row>
     <row r="12" spans="1:42">
-      <c r="B12" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="G12" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="20"/>
+      <c r="T12" s="20"/>
+      <c r="U12" s="20"/>
+      <c r="V12" s="20"/>
+      <c r="W12" s="20"/>
+      <c r="X12" s="20"/>
+      <c r="Y12" s="20"/>
+      <c r="Z12" s="20"/>
+      <c r="AA12" s="20"/>
+      <c r="AB12" s="20"/>
+      <c r="AC12" s="20"/>
+      <c r="AD12" s="20"/>
+      <c r="AE12" s="20"/>
+      <c r="AF12" s="20"/>
+      <c r="AG12" s="20"/>
+      <c r="AH12" s="20"/>
+      <c r="AI12" s="20"/>
+      <c r="AJ12" s="20"/>
+      <c r="AK12" s="20"/>
+      <c r="AL12" s="20"/>
+      <c r="AM12" s="20"/>
+      <c r="AN12" s="20"/>
+      <c r="AO12" s="20"/>
+      <c r="AP12" s="20"/>
     </row>
     <row r="13" spans="1:42">
-      <c r="B13" s="17"/>
+      <c r="B13" s="17" t="s">
+        <v>47</v>
+      </c>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
+      <c r="G13" s="18" t="s">
+        <v>51</v>
+      </c>
       <c r="H13" s="18"/>
       <c r="I13" s="18"/>
       <c r="J13" s="18"/>
     </row>
     <row r="14" spans="1:42">
-      <c r="B14" s="18"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
     </row>
     <row r="15" spans="1:42">
       <c r="B15" s="18"/>
-      <c r="C15" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="H15" s="41" t="s">
-        <v>48</v>
-      </c>
-      <c r="I15" s="41"/>
-      <c r="J15" s="41"/>
-      <c r="K15" s="41"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
     </row>
     <row r="16" spans="1:42">
       <c r="B16" s="18"/>
-      <c r="C16" s="40" t="s">
+      <c r="C16" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="H16" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="30"/>
+    </row>
+    <row r="17" spans="2:11">
+      <c r="B17" s="18"/>
+      <c r="C17" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="H16" s="40" t="s">
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="H17" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="H15:K15"/>
-    <mergeCell ref="H16:K16"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B6:C7"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="W6:W8"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="N7:N8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="F6:M6"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="N6:S6"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="V6:V8"/>
+    <mergeCell ref="S7:S8"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="M7:M8"/>
     <mergeCell ref="AP6:AP8"/>
     <mergeCell ref="AA6:AA8"/>
     <mergeCell ref="AB6:AD6"/>
@@ -2106,21 +2171,23 @@
     <mergeCell ref="AH6:AH8"/>
     <mergeCell ref="AL6:AL8"/>
     <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="N6:S6"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="V6:V8"/>
-    <mergeCell ref="S7:S8"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B6:C7"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="W6:W8"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="F6:M6"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="H16:K16"/>
+    <mergeCell ref="H17:K17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/iLgs/App_Data/CustodianVehiclesTemplate.xlsx
+++ b/iLgs/App_Data/CustodianVehiclesTemplate.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Template 2025_03_14/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Template 2025_03_22/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{BDE9407C-8914-4A79-B041-C95AF19ACBAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06941052-6387-46DE-8BA6-46708C9B638E}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="8_{BDE9407C-8914-4A79-B041-C95AF19ACBAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4473987-129B-408E-95C6-84159CAA3D24}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="832" xr2:uid="{8F9EB15D-4C1E-42CC-8141-A131BDAE685A}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>Custodian 
 Item 
@@ -75,12 +75,6 @@
 Number</t>
   </si>
   <si>
-    <t>Old
-Amounts
-(recorded 
-in RPCPPE)</t>
-  </si>
-  <si>
     <t>P.O. 
 Date</t>
   </si>
@@ -235,21 +229,6 @@
 Number</t>
   </si>
   <si>
-    <t>Certified Correct by:</t>
-  </si>
-  <si>
-    <t>Signature over Printed Name</t>
-  </si>
-  <si>
-    <t>Custodian</t>
-  </si>
-  <si>
-    <t>Verified by:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Assistant to the Custodian</t>
-  </si>
-  <si>
     <t>Department:</t>
   </si>
   <si>
@@ -257,13 +236,21 @@
   </si>
   <si>
     <t>REPORT ON THE PHYSICAL COUNT OF VEHICLES</t>
+  </si>
+  <si>
+    <t>Old
+Amounts
+(in RPCPPE)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -312,10 +299,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri  "/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -328,14 +318,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor theme="0"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -434,18 +418,15 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -455,8 +436,10 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="medium">
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -468,42 +451,23 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
         <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="hair">
-        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -521,14 +485,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -556,25 +513,36 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -891,324 +859,118 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C18FA19-E183-4684-9A16-B0E4B19C4ED4}">
-  <dimension ref="B2:AV19"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="B2:AV14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.77734375" style="3" customWidth="1"/>
     <col min="2" max="2" width="12.77734375" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.77734375" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.21875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="8.88671875" style="3"/>
-    <col min="10" max="10" width="7.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.88671875" style="3"/>
+    <col min="5" max="5" width="12.77734375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="28.5546875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.77734375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="13.77734375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" style="3"/>
+    <col min="10" max="10" width="14.5546875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.21875" style="3" customWidth="1"/>
     <col min="13" max="13" width="16" style="3" customWidth="1"/>
-    <col min="14" max="14" width="8.88671875" style="3"/>
-    <col min="15" max="15" width="5.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="8.88671875" style="3"/>
-    <col min="20" max="20" width="10.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.21875" style="3" customWidth="1"/>
+    <col min="15" max="15" width="8" style="3" customWidth="1"/>
+    <col min="16" max="16" width="16.21875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="8.88671875" style="3"/>
+    <col min="18" max="18" width="18.6640625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="8.88671875" style="3"/>
+    <col min="20" max="20" width="12.21875" style="3" customWidth="1"/>
     <col min="21" max="21" width="7.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="23.77734375" style="3" customWidth="1"/>
     <col min="23" max="23" width="8.88671875" style="3" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="8.88671875" style="3"/>
-    <col min="25" max="25" width="10.5546875" style="3" customWidth="1"/>
-    <col min="26" max="28" width="8.88671875" style="3"/>
-    <col min="29" max="29" width="11.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.44140625" style="3" customWidth="1"/>
-    <col min="31" max="31" width="11.33203125" style="3" customWidth="1"/>
-    <col min="32" max="35" width="8.88671875" style="3"/>
-    <col min="36" max="36" width="10.88671875" style="3" customWidth="1"/>
-    <col min="37" max="38" width="8.88671875" style="3"/>
-    <col min="39" max="39" width="13.6640625" style="3" customWidth="1"/>
-    <col min="40" max="41" width="8.88671875" style="3"/>
-    <col min="42" max="42" width="11.5546875" style="3" customWidth="1"/>
-    <col min="43" max="43" width="8.88671875" style="3"/>
-    <col min="44" max="44" width="19.109375" style="3" customWidth="1"/>
-    <col min="45" max="45" width="6.5546875" style="3" customWidth="1"/>
-    <col min="46" max="46" width="9.33203125" style="3" customWidth="1"/>
-    <col min="47" max="16384" width="8.88671875" style="3"/>
+    <col min="25" max="25" width="13.109375" style="24" customWidth="1"/>
+    <col min="26" max="26" width="13" style="3" customWidth="1"/>
+    <col min="27" max="28" width="8.88671875" style="3"/>
+    <col min="29" max="29" width="13.33203125" style="3" customWidth="1"/>
+    <col min="30" max="32" width="14.21875" style="24" customWidth="1"/>
+    <col min="33" max="33" width="11.33203125" style="3" customWidth="1"/>
+    <col min="34" max="35" width="8.88671875" style="3"/>
+    <col min="36" max="36" width="10.88671875" style="24" customWidth="1"/>
+    <col min="37" max="37" width="12.88671875" style="3" customWidth="1"/>
+    <col min="38" max="38" width="8.88671875" style="3"/>
+    <col min="39" max="39" width="12.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="16.21875" style="3" customWidth="1"/>
+    <col min="41" max="41" width="19.77734375" style="3" customWidth="1"/>
+    <col min="42" max="42" width="32" style="3" customWidth="1"/>
+    <col min="43" max="43" width="15.44140625" style="3" customWidth="1"/>
+    <col min="44" max="44" width="26.77734375" style="3" customWidth="1"/>
+    <col min="45" max="45" width="4.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="20.6640625" style="3" customWidth="1"/>
+    <col min="47" max="47" width="25.33203125" style="3" customWidth="1"/>
+    <col min="48" max="48" width="6" style="3" bestFit="1" customWidth="1"/>
+    <col min="49" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:48" s="1" customFormat="1" ht="15.6">
+    <row r="2" spans="2:48" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="7"/>
+      <c r="Y2" s="22"/>
+      <c r="AD2" s="22"/>
+      <c r="AE2" s="22"/>
+      <c r="AF2" s="22"/>
+      <c r="AJ2" s="22"/>
     </row>
-    <row r="3" spans="2:48" s="2" customFormat="1" ht="18">
+    <row r="3" spans="2:48" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="B3" s="8" t="s">
-        <v>58</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="Y3" s="23"/>
+      <c r="AD3" s="23"/>
+      <c r="AE3" s="23"/>
+      <c r="AF3" s="23"/>
+      <c r="AJ3" s="23"/>
     </row>
-    <row r="4" spans="2:48" ht="15.6">
+    <row r="4" spans="2:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B4" s="1"/>
     </row>
-    <row r="5" spans="2:48" ht="15.6">
+    <row r="5" spans="2:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="1"/>
     </row>
-    <row r="6" spans="2:48" ht="15.6">
-      <c r="B6" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="12"/>
+    <row r="6" spans="2:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="1"/>
     </row>
-    <row r="7" spans="2:48" ht="15" thickBot="1"/>
-    <row r="8" spans="2:48" s="4" customFormat="1">
-      <c r="B8" s="14" t="s">
+    <row r="7" spans="2:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="1"/>
+    </row>
+    <row r="8" spans="2:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="9"/>
+    </row>
+    <row r="9" spans="2:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B9" s="1"/>
+      <c r="C9" s="9"/>
+    </row>
+    <row r="10" spans="2:48" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B10" s="1"/>
+      <c r="C10" s="9"/>
+    </row>
+    <row r="11" spans="2:48" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="2:48" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C12" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="20" t="s">
+      <c r="D12" s="13"/>
+      <c r="E12" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F12" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G12" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q8" s="17"/>
-      <c r="R8" s="17"/>
-      <c r="S8" s="17"/>
-      <c r="T8" s="17"/>
-      <c r="U8" s="17"/>
-      <c r="V8" s="17"/>
-      <c r="W8" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="X8" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y8" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z8" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA8" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="AB8" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="AC8" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD8" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="AE8" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF8" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="AG8" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="AH8" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI8" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="AJ8" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="AK8" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="AL8" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="AM8" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="AN8" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="AO8" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="AP8" s="17"/>
-      <c r="AQ8" s="17"/>
-      <c r="AR8" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="AS8" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="AT8" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AU8" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="AV8" s="17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="2:48" s="4" customFormat="1">
-      <c r="B9" s="15"/>
-      <c r="C9" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="J9" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="K9" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="L9" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="M9" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="N9" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="O9" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="P9" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q9" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="R9" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="S9" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="T9" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="U9" s="21"/>
-      <c r="V9" s="21"/>
-      <c r="W9" s="21"/>
-      <c r="X9" s="21"/>
-      <c r="Y9" s="18"/>
-      <c r="Z9" s="21"/>
-      <c r="AA9" s="21"/>
-      <c r="AB9" s="21"/>
-      <c r="AC9" s="18"/>
-      <c r="AD9" s="18"/>
-      <c r="AE9" s="18"/>
-      <c r="AF9" s="21"/>
-      <c r="AG9" s="21"/>
-      <c r="AH9" s="21"/>
-      <c r="AI9" s="21"/>
-      <c r="AJ9" s="21"/>
-      <c r="AK9" s="21"/>
-      <c r="AL9" s="21"/>
-      <c r="AM9" s="21"/>
-      <c r="AN9" s="21"/>
-      <c r="AO9" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="AP9" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="AQ9" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="AR9" s="21"/>
-      <c r="AS9" s="21"/>
-      <c r="AT9" s="21"/>
-      <c r="AU9" s="26"/>
-      <c r="AV9" s="21"/>
-    </row>
-    <row r="10" spans="2:48" s="4" customFormat="1" ht="43.2" customHeight="1" thickBot="1">
-      <c r="B10" s="16"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="22"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="22"/>
-      <c r="R10" s="22"/>
-      <c r="S10" s="22"/>
-      <c r="T10" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="U10" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="V10" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="W10" s="22"/>
-      <c r="X10" s="22"/>
-      <c r="Y10" s="19"/>
-      <c r="Z10" s="22"/>
-      <c r="AA10" s="22"/>
-      <c r="AB10" s="22"/>
-      <c r="AC10" s="19"/>
-      <c r="AD10" s="19"/>
-      <c r="AE10" s="19"/>
-      <c r="AF10" s="22"/>
-      <c r="AG10" s="22"/>
-      <c r="AH10" s="22"/>
-      <c r="AI10" s="22"/>
-      <c r="AJ10" s="22"/>
-      <c r="AK10" s="22"/>
-      <c r="AL10" s="22"/>
-      <c r="AM10" s="22"/>
-      <c r="AN10" s="22"/>
-      <c r="AO10" s="22"/>
-      <c r="AP10" s="22"/>
-      <c r="AQ10" s="22"/>
-      <c r="AR10" s="22"/>
-      <c r="AS10" s="22"/>
-      <c r="AT10" s="22"/>
-      <c r="AU10" s="27"/>
-      <c r="AV10" s="22"/>
-    </row>
-    <row r="11" spans="2:48" hidden="1"/>
-    <row r="12" spans="2:48">
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
       <c r="H12" s="13"/>
       <c r="I12" s="13"/>
       <c r="J12" s="13"/>
@@ -1217,141 +979,283 @@
       <c r="M12" s="13"/>
       <c r="N12" s="13"/>
       <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
+      <c r="P12" s="13" t="s">
+        <v>39</v>
+      </c>
       <c r="Q12" s="13"/>
       <c r="R12" s="13"/>
       <c r="S12" s="13"/>
       <c r="T12" s="13"/>
       <c r="U12" s="13"/>
       <c r="V12" s="13"/>
-      <c r="W12" s="13"/>
-      <c r="X12" s="13"/>
-      <c r="Y12" s="13"/>
-      <c r="Z12" s="13"/>
-      <c r="AA12" s="13"/>
-      <c r="AB12" s="13"/>
-      <c r="AC12" s="13"/>
-      <c r="AD12" s="13"/>
-      <c r="AE12" s="13"/>
-      <c r="AF12" s="13"/>
-      <c r="AG12" s="13"/>
-      <c r="AH12" s="13"/>
-      <c r="AI12" s="13"/>
-      <c r="AJ12" s="13"/>
-      <c r="AK12" s="13"/>
-      <c r="AL12" s="13"/>
-      <c r="AM12" s="13"/>
-      <c r="AN12" s="13"/>
-      <c r="AO12" s="13"/>
+      <c r="W12" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="X12" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y12" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z12" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA12" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB12" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC12" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD12" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE12" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF12" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG12" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH12" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI12" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ12" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK12" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL12" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM12" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="AN12" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="AO12" s="13" t="s">
+        <v>23</v>
+      </c>
       <c r="AP12" s="13"/>
       <c r="AQ12" s="13"/>
-      <c r="AR12" s="13"/>
-      <c r="AS12" s="13"/>
-      <c r="AT12" s="13"/>
-      <c r="AU12" s="13"/>
-      <c r="AV12" s="13"/>
+      <c r="AR12" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS12" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="AT12" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="AU12" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="AV12" s="13" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="15" spans="2:48">
-      <c r="C15" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
+    <row r="13" spans="2:48" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="11"/>
+      <c r="C13" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="M13" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="N13" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="O13" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="P13" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q13" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="R13" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="S13" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="T13" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="U13" s="17"/>
+      <c r="V13" s="17"/>
+      <c r="W13" s="17"/>
+      <c r="X13" s="17"/>
+      <c r="Y13" s="26"/>
+      <c r="Z13" s="17"/>
+      <c r="AA13" s="17"/>
+      <c r="AB13" s="17"/>
+      <c r="AC13" s="17"/>
+      <c r="AD13" s="28"/>
+      <c r="AE13" s="26"/>
+      <c r="AF13" s="26"/>
+      <c r="AG13" s="14"/>
+      <c r="AH13" s="17"/>
+      <c r="AI13" s="17"/>
+      <c r="AJ13" s="28"/>
+      <c r="AK13" s="17"/>
+      <c r="AL13" s="17"/>
+      <c r="AM13" s="17"/>
+      <c r="AN13" s="17"/>
+      <c r="AO13" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="AP13" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ13" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="AR13" s="17"/>
+      <c r="AS13" s="17"/>
+      <c r="AT13" s="17"/>
+      <c r="AU13" s="20"/>
+      <c r="AV13" s="17"/>
     </row>
-    <row r="16" spans="2:48">
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-    </row>
-    <row r="17" spans="4:12">
-      <c r="J17" s="10"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-    </row>
-    <row r="18" spans="4:12">
-      <c r="D18" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="L18" s="23"/>
-    </row>
-    <row r="19" spans="4:12">
-      <c r="D19" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="L19" s="24"/>
+    <row r="14" spans="2:48" s="4" customFormat="1" ht="43.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="12"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="18"/>
+      <c r="Q14" s="18"/>
+      <c r="R14" s="18"/>
+      <c r="S14" s="18"/>
+      <c r="T14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="U14" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="V14" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="W14" s="18"/>
+      <c r="X14" s="18"/>
+      <c r="Y14" s="27"/>
+      <c r="Z14" s="18"/>
+      <c r="AA14" s="18"/>
+      <c r="AB14" s="18"/>
+      <c r="AC14" s="18"/>
+      <c r="AD14" s="29"/>
+      <c r="AE14" s="27"/>
+      <c r="AF14" s="27"/>
+      <c r="AG14" s="15"/>
+      <c r="AH14" s="18"/>
+      <c r="AI14" s="18"/>
+      <c r="AJ14" s="29"/>
+      <c r="AK14" s="18"/>
+      <c r="AL14" s="18"/>
+      <c r="AM14" s="18"/>
+      <c r="AN14" s="18"/>
+      <c r="AO14" s="18"/>
+      <c r="AP14" s="18"/>
+      <c r="AQ14" s="18"/>
+      <c r="AR14" s="18"/>
+      <c r="AS14" s="18"/>
+      <c r="AT14" s="18"/>
+      <c r="AU14" s="21"/>
+      <c r="AV14" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="53">
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="AV8:AV10"/>
-    <mergeCell ref="AR8:AR10"/>
-    <mergeCell ref="AS8:AS10"/>
-    <mergeCell ref="AT8:AT10"/>
-    <mergeCell ref="AU8:AU10"/>
-    <mergeCell ref="AO9:AO10"/>
-    <mergeCell ref="AP9:AP10"/>
-    <mergeCell ref="AQ9:AQ10"/>
-    <mergeCell ref="AK8:AK10"/>
-    <mergeCell ref="AL8:AL10"/>
-    <mergeCell ref="AM8:AM10"/>
-    <mergeCell ref="AN8:AN10"/>
-    <mergeCell ref="AO8:AQ8"/>
-    <mergeCell ref="AG8:AG10"/>
-    <mergeCell ref="AH8:AH10"/>
-    <mergeCell ref="AI8:AI10"/>
-    <mergeCell ref="AJ8:AJ10"/>
-    <mergeCell ref="AF8:AF10"/>
-    <mergeCell ref="W8:W10"/>
-    <mergeCell ref="T9:V9"/>
-    <mergeCell ref="X8:X10"/>
-    <mergeCell ref="Y8:Y10"/>
-    <mergeCell ref="AA8:AA10"/>
-    <mergeCell ref="Z8:Z10"/>
-    <mergeCell ref="AB8:AB10"/>
-    <mergeCell ref="AC8:AC10"/>
-    <mergeCell ref="AD8:AD10"/>
-    <mergeCell ref="AE8:AE10"/>
-    <mergeCell ref="O9:O10"/>
-    <mergeCell ref="G8:O8"/>
-    <mergeCell ref="P8:V8"/>
-    <mergeCell ref="P9:P10"/>
-    <mergeCell ref="Q9:Q10"/>
-    <mergeCell ref="R9:R10"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="N9:N10"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="C9:C10"/>
+  <mergeCells count="49">
+    <mergeCell ref="AV12:AV14"/>
+    <mergeCell ref="AR12:AR14"/>
+    <mergeCell ref="AS12:AS14"/>
+    <mergeCell ref="AT12:AT14"/>
+    <mergeCell ref="AU12:AU14"/>
+    <mergeCell ref="AO12:AQ12"/>
+    <mergeCell ref="AG12:AG14"/>
+    <mergeCell ref="AH12:AH14"/>
+    <mergeCell ref="AI12:AI14"/>
+    <mergeCell ref="AJ12:AJ14"/>
+    <mergeCell ref="AO13:AO14"/>
+    <mergeCell ref="AP13:AP14"/>
+    <mergeCell ref="AQ13:AQ14"/>
+    <mergeCell ref="AK12:AK14"/>
+    <mergeCell ref="AL12:AL14"/>
+    <mergeCell ref="AM12:AM14"/>
+    <mergeCell ref="AN12:AN14"/>
+    <mergeCell ref="AF12:AF14"/>
+    <mergeCell ref="W12:W14"/>
+    <mergeCell ref="T13:V13"/>
+    <mergeCell ref="X12:X14"/>
+    <mergeCell ref="Y12:Y14"/>
+    <mergeCell ref="AA12:AA14"/>
+    <mergeCell ref="Z12:Z14"/>
+    <mergeCell ref="AB12:AB14"/>
+    <mergeCell ref="AC12:AC14"/>
+    <mergeCell ref="AD12:AD14"/>
+    <mergeCell ref="AE12:AE14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="G12:O12"/>
+    <mergeCell ref="P12:V12"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="R13:R14"/>
+    <mergeCell ref="S13:S14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="C13:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/iLgs/App_Data/CustodianVehiclesTemplate.xlsx
+++ b/iLgs/App_Data/CustodianVehiclesTemplate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Template 2025_03_22/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Template 2025_04_08/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="8_{BDE9407C-8914-4A79-B041-C95AF19ACBAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4473987-129B-408E-95C6-84159CAA3D24}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="8_{BDE9407C-8914-4A79-B041-C95AF19ACBAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17AA9F58-AFED-48D8-B781-9FA3D44362B8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="832" xr2:uid="{8F9EB15D-4C1E-42CC-8141-A131BDAE685A}"/>
   </bookViews>
@@ -127,9 +127,6 @@
 Location</t>
   </si>
   <si>
-    <t>PAR / ARE / MR</t>
-  </si>
-  <si>
     <t>Number</t>
   </si>
   <si>
@@ -241,6 +238,9 @@
     <t>Old
 Amounts
 (in RPCPPE)</t>
+  </si>
+  <si>
+    <t>PAR / ICS / ARE / MR / RPCPPE</t>
   </si>
 </sst>
 </file>
@@ -486,45 +486,36 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="43" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -538,6 +529,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -556,10 +556,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -886,14 +882,14 @@
     <col min="22" max="22" width="23.77734375" style="3" customWidth="1"/>
     <col min="23" max="23" width="8.88671875" style="3" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="8.88671875" style="3"/>
-    <col min="25" max="25" width="13.109375" style="24" customWidth="1"/>
+    <col min="25" max="25" width="13.109375" style="12" customWidth="1"/>
     <col min="26" max="26" width="13" style="3" customWidth="1"/>
     <col min="27" max="28" width="8.88671875" style="3"/>
     <col min="29" max="29" width="13.33203125" style="3" customWidth="1"/>
-    <col min="30" max="32" width="14.21875" style="24" customWidth="1"/>
+    <col min="30" max="32" width="14.21875" style="12" customWidth="1"/>
     <col min="33" max="33" width="11.33203125" style="3" customWidth="1"/>
     <col min="34" max="35" width="8.88671875" style="3"/>
-    <col min="36" max="36" width="10.88671875" style="24" customWidth="1"/>
+    <col min="36" max="36" width="10.88671875" style="12" customWidth="1"/>
     <col min="37" max="37" width="12.88671875" style="3" customWidth="1"/>
     <col min="38" max="38" width="8.88671875" style="3"/>
     <col min="39" max="39" width="12.44140625" style="3" bestFit="1" customWidth="1"/>
@@ -911,21 +907,21 @@
   <sheetData>
     <row r="2" spans="2:48" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="7"/>
-      <c r="Y2" s="22"/>
-      <c r="AD2" s="22"/>
-      <c r="AE2" s="22"/>
-      <c r="AF2" s="22"/>
-      <c r="AJ2" s="22"/>
+      <c r="Y2" s="10"/>
+      <c r="AD2" s="10"/>
+      <c r="AE2" s="10"/>
+      <c r="AF2" s="10"/>
+      <c r="AJ2" s="10"/>
     </row>
     <row r="3" spans="2:48" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="B3" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y3" s="23"/>
-      <c r="AD3" s="23"/>
-      <c r="AE3" s="23"/>
-      <c r="AF3" s="23"/>
-      <c r="AJ3" s="23"/>
+        <v>51</v>
+      </c>
+      <c r="Y3" s="11"/>
+      <c r="AD3" s="11"/>
+      <c r="AE3" s="11"/>
+      <c r="AF3" s="11"/>
+      <c r="AJ3" s="11"/>
     </row>
     <row r="4" spans="2:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B4" s="1"/>
@@ -941,7 +937,7 @@
     </row>
     <row r="8" spans="2:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C8" s="9"/>
     </row>
@@ -955,255 +951,255 @@
     </row>
     <row r="11" spans="2:48" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="2:48" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D12" s="13"/>
-      <c r="E12" s="16" t="s">
+      <c r="D12" s="16"/>
+      <c r="E12" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q12" s="13"/>
-      <c r="R12" s="13"/>
-      <c r="S12" s="13"/>
-      <c r="T12" s="13"/>
-      <c r="U12" s="13"/>
-      <c r="V12" s="13"/>
-      <c r="W12" s="16" t="s">
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+      <c r="T12" s="16"/>
+      <c r="U12" s="16"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="X12" s="16" t="s">
+      <c r="X12" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="Y12" s="25" t="s">
+      <c r="Y12" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z12" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA12" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB12" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC12" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD12" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE12" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF12" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG12" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH12" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI12" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ12" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK12" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL12" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM12" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="AN12" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="AO12" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="Z12" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA12" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB12" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC12" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="AD12" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="AE12" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF12" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG12" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="AH12" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI12" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ12" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="AK12" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="AL12" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="AM12" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="AN12" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="AO12" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="AP12" s="13"/>
-      <c r="AQ12" s="13"/>
-      <c r="AR12" s="16" t="s">
+      <c r="AP12" s="16"/>
+      <c r="AQ12" s="16"/>
+      <c r="AR12" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="AS12" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="AS12" s="13" t="s">
+      <c r="AT12" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="AT12" s="13" t="s">
+      <c r="AU12" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="AU12" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="AV12" s="13" t="s">
-        <v>51</v>
+      <c r="AV12" s="16" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="2:48" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="11"/>
-      <c r="C13" s="14" t="s">
+      <c r="B13" s="14"/>
+      <c r="C13" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="14" t="s">
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="H13" s="14" t="s">
+      <c r="I13" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="I13" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="J13" s="14" t="s">
+      <c r="J13" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L13" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="K13" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="L13" s="14" t="s">
+      <c r="M13" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="M13" s="14" t="s">
+      <c r="N13" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="N13" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="O13" s="17" t="s">
+      <c r="O13" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="P13" s="14" t="s">
+      <c r="P13" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q13" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="Q13" s="14" t="s">
+      <c r="R13" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="R13" s="14" t="s">
+      <c r="S13" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="T13" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="S13" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="T13" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="U13" s="17"/>
-      <c r="V13" s="17"/>
-      <c r="W13" s="17"/>
-      <c r="X13" s="17"/>
-      <c r="Y13" s="26"/>
-      <c r="Z13" s="17"/>
-      <c r="AA13" s="17"/>
-      <c r="AB13" s="17"/>
-      <c r="AC13" s="17"/>
-      <c r="AD13" s="28"/>
-      <c r="AE13" s="26"/>
-      <c r="AF13" s="26"/>
-      <c r="AG13" s="14"/>
-      <c r="AH13" s="17"/>
-      <c r="AI13" s="17"/>
-      <c r="AJ13" s="28"/>
-      <c r="AK13" s="17"/>
-      <c r="AL13" s="17"/>
-      <c r="AM13" s="17"/>
-      <c r="AN13" s="17"/>
-      <c r="AO13" s="17" t="s">
+      <c r="U13" s="20"/>
+      <c r="V13" s="20"/>
+      <c r="W13" s="20"/>
+      <c r="X13" s="20"/>
+      <c r="Y13" s="23"/>
+      <c r="Z13" s="20"/>
+      <c r="AA13" s="20"/>
+      <c r="AB13" s="20"/>
+      <c r="AC13" s="20"/>
+      <c r="AD13" s="25"/>
+      <c r="AE13" s="23"/>
+      <c r="AF13" s="23"/>
+      <c r="AG13" s="17"/>
+      <c r="AH13" s="20"/>
+      <c r="AI13" s="20"/>
+      <c r="AJ13" s="25"/>
+      <c r="AK13" s="20"/>
+      <c r="AL13" s="20"/>
+      <c r="AM13" s="20"/>
+      <c r="AN13" s="20"/>
+      <c r="AO13" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP13" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="AP13" s="14" t="s">
+      <c r="AQ13" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="AQ13" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="AR13" s="17"/>
-      <c r="AS13" s="17"/>
-      <c r="AT13" s="17"/>
-      <c r="AU13" s="20"/>
-      <c r="AV13" s="17"/>
+      <c r="AR13" s="20"/>
+      <c r="AS13" s="20"/>
+      <c r="AT13" s="20"/>
+      <c r="AU13" s="28"/>
+      <c r="AV13" s="20"/>
     </row>
     <row r="14" spans="2:48" s="4" customFormat="1" ht="43.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="12"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="18"/>
-      <c r="N14" s="18"/>
-      <c r="O14" s="18"/>
-      <c r="P14" s="18"/>
-      <c r="Q14" s="18"/>
-      <c r="R14" s="18"/>
-      <c r="S14" s="18"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="21"/>
       <c r="T14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="U14" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="U14" s="6" t="s">
-        <v>45</v>
-      </c>
       <c r="V14" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="W14" s="18"/>
-      <c r="X14" s="18"/>
-      <c r="Y14" s="27"/>
-      <c r="Z14" s="18"/>
-      <c r="AA14" s="18"/>
-      <c r="AB14" s="18"/>
-      <c r="AC14" s="18"/>
-      <c r="AD14" s="29"/>
-      <c r="AE14" s="27"/>
-      <c r="AF14" s="27"/>
-      <c r="AG14" s="15"/>
-      <c r="AH14" s="18"/>
-      <c r="AI14" s="18"/>
-      <c r="AJ14" s="29"/>
-      <c r="AK14" s="18"/>
-      <c r="AL14" s="18"/>
-      <c r="AM14" s="18"/>
-      <c r="AN14" s="18"/>
-      <c r="AO14" s="18"/>
-      <c r="AP14" s="18"/>
-      <c r="AQ14" s="18"/>
-      <c r="AR14" s="18"/>
-      <c r="AS14" s="18"/>
-      <c r="AT14" s="18"/>
-      <c r="AU14" s="21"/>
-      <c r="AV14" s="18"/>
+        <v>46</v>
+      </c>
+      <c r="W14" s="21"/>
+      <c r="X14" s="21"/>
+      <c r="Y14" s="24"/>
+      <c r="Z14" s="21"/>
+      <c r="AA14" s="21"/>
+      <c r="AB14" s="21"/>
+      <c r="AC14" s="21"/>
+      <c r="AD14" s="26"/>
+      <c r="AE14" s="24"/>
+      <c r="AF14" s="24"/>
+      <c r="AG14" s="18"/>
+      <c r="AH14" s="21"/>
+      <c r="AI14" s="21"/>
+      <c r="AJ14" s="26"/>
+      <c r="AK14" s="21"/>
+      <c r="AL14" s="21"/>
+      <c r="AM14" s="21"/>
+      <c r="AN14" s="21"/>
+      <c r="AO14" s="21"/>
+      <c r="AP14" s="21"/>
+      <c r="AQ14" s="21"/>
+      <c r="AR14" s="21"/>
+      <c r="AS14" s="21"/>
+      <c r="AT14" s="21"/>
+      <c r="AU14" s="29"/>
+      <c r="AV14" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="49">

--- a/iLgs/App_Data/CustodianVehiclesTemplate.xlsx
+++ b/iLgs/App_Data/CustodianVehiclesTemplate.xlsx
@@ -5,16 +5,161 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Template 2025_04_08/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Template  2025_04_22/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="8_{BDE9407C-8914-4A79-B041-C95AF19ACBAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17AA9F58-AFED-48D8-B781-9FA3D44362B8}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{4CCB3B42-D639-4A82-BB32-781160A643F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B137AD0-8150-4ED2-B121-4F96662E58F0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="832" xr2:uid="{8F9EB15D-4C1E-42CC-8141-A131BDAE685A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="986" xr2:uid="{8F9EB15D-4C1E-42CC-8141-A131BDAE685A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="a">#REF!</definedName>
+    <definedName name="Account">#REF!</definedName>
+    <definedName name="Account1">#REF!</definedName>
+    <definedName name="Account2">#REF!</definedName>
+    <definedName name="Account3">#REF!</definedName>
+    <definedName name="AirconditioningUnits">#REF!</definedName>
+    <definedName name="Banca">#REF!</definedName>
+    <definedName name="Books">#REF!</definedName>
+    <definedName name="BuildingComponents">#REF!</definedName>
+    <definedName name="Buildings">#REF!</definedName>
+    <definedName name="Bulldozer">#REF!</definedName>
+    <definedName name="Calendar10Month">#REF!</definedName>
+    <definedName name="Calendar10MonthOption">MATCH(Calendar10Month,Months,0)</definedName>
+    <definedName name="Calendar10Year">#REF!</definedName>
+    <definedName name="Calendar11Month">#REF!</definedName>
+    <definedName name="Calendar11MonthOption">MATCH(Calendar11Month,Months,0)</definedName>
+    <definedName name="Calendar11Year">#REF!</definedName>
+    <definedName name="Calendar12Month">#REF!</definedName>
+    <definedName name="Calendar12MonthOption">MATCH(Calendar12Month,Months,0)</definedName>
+    <definedName name="Calendar12Year">#REF!</definedName>
+    <definedName name="Calendar1Month">#REF!</definedName>
+    <definedName name="Calendar1MonthOption">MATCH(Calendar1Month,Months,0)</definedName>
+    <definedName name="Calendar1Year">#REF!</definedName>
+    <definedName name="Calendar2Month">#REF!</definedName>
+    <definedName name="Calendar2MonthOption">MATCH(Calendar2Month,Months,0)</definedName>
+    <definedName name="Calendar2Year">#REF!</definedName>
+    <definedName name="Calendar3Month">#REF!</definedName>
+    <definedName name="Calendar3MonthOption">MATCH(Calendar3Month,Months,0)</definedName>
+    <definedName name="Calendar3Year">#REF!</definedName>
+    <definedName name="Calendar4Month">#REF!</definedName>
+    <definedName name="Calendar4MonthOption">MATCH(Calendar4Month,Months,0)</definedName>
+    <definedName name="Calendar4Year">#REF!</definedName>
+    <definedName name="Calendar5Month">#REF!</definedName>
+    <definedName name="Calendar5MonthOption">MATCH(Calendar5Month,Months,0)</definedName>
+    <definedName name="Calendar5Year">#REF!</definedName>
+    <definedName name="Calendar6Month">#REF!</definedName>
+    <definedName name="Calendar6MonthOption">MATCH(Calendar6Month,Months,0)</definedName>
+    <definedName name="Calendar6Year">#REF!</definedName>
+    <definedName name="Calendar7Month">#REF!</definedName>
+    <definedName name="Calendar7MonthOption">MATCH(Calendar7Month,Months,0)</definedName>
+    <definedName name="Calendar7Year">#REF!</definedName>
+    <definedName name="Calendar8Month">#REF!</definedName>
+    <definedName name="Calendar8MonthOption">MATCH(Calendar8Month,Months,0)</definedName>
+    <definedName name="Calendar8Year">#REF!</definedName>
+    <definedName name="Calendar9Month">#REF!</definedName>
+    <definedName name="Calendar9MonthOption">MATCH(Calendar9Month,Months,0)</definedName>
+    <definedName name="Calendar9Year">#REF!</definedName>
+    <definedName name="Car">#REF!</definedName>
+    <definedName name="ClosedCircuitTelevision">#REF!</definedName>
+    <definedName name="CommunicationEquipment">#REF!</definedName>
+    <definedName name="CommunicationsNetwork">#REF!</definedName>
+    <definedName name="Compactor">#REF!</definedName>
+    <definedName name="ComputerDesktopSet">#REF!</definedName>
+    <definedName name="Condition">#REF!</definedName>
+    <definedName name="Condition1">#REF!</definedName>
+    <definedName name="Condition2">#REF!</definedName>
+    <definedName name="Condition3">#REF!</definedName>
+    <definedName name="ConstructionandHeavyEquipment">#REF!</definedName>
+    <definedName name="DataCommunicationsEquipment">#REF!</definedName>
+    <definedName name="Days">{0,1,2,3,4,5,6}</definedName>
+    <definedName name="DiagnosticEquipment">#REF!</definedName>
+    <definedName name="DisasterResponseandRescue">#REF!</definedName>
+    <definedName name="Drones">#REF!</definedName>
+    <definedName name="Dropside">#REF!</definedName>
+    <definedName name="DumpTruck">#REF!</definedName>
+    <definedName name="Duplicating\PhotocopyingMachines">#REF!</definedName>
+    <definedName name="EarthquakeRescueEquipment">#REF!</definedName>
+    <definedName name="FirefightingEquipmentandAccessories">#REF!</definedName>
+    <definedName name="FloodControlSystems">#REF!</definedName>
+    <definedName name="FloodRescueEquipment">#REF!</definedName>
+    <definedName name="Forklift">#REF!</definedName>
+    <definedName name="Furniture\Fixtures\Books">#REF!</definedName>
+    <definedName name="FurnitureandFixtures">#REF!</definedName>
+    <definedName name="Guns">#REF!</definedName>
+    <definedName name="HighwaysandBridges">#REF!</definedName>
+    <definedName name="HospitalandHealthCenters">#REF!</definedName>
+    <definedName name="HospitalBeds">#REF!</definedName>
+    <definedName name="InformationandCommunicationTechnology">#REF!</definedName>
+    <definedName name="IrrigationCanalsandLaterals">#REF!</definedName>
+    <definedName name="LandslideRescueEquipment">#REF!</definedName>
+    <definedName name="Laptop">#REF!</definedName>
+    <definedName name="LifeSupport">#REF!</definedName>
+    <definedName name="Markets">#REF!</definedName>
+    <definedName name="MedicalEquipment">#REF!</definedName>
+    <definedName name="MedicalFurniture">#REF!</definedName>
+    <definedName name="MedicineTrolleys">#REF!</definedName>
+    <definedName name="MobileCar">#REF!</definedName>
+    <definedName name="MobileClinic">#REF!</definedName>
+    <definedName name="ModeofAcquisition">#REF!</definedName>
+    <definedName name="ModeofAcquisition1">#REF!</definedName>
+    <definedName name="Monitors">#REF!</definedName>
+    <definedName name="Months">{"January","February","March","April","May","June","July","August","September","October","November","December"}</definedName>
+    <definedName name="Motorboat">#REF!</definedName>
+    <definedName name="Motorcycle">#REF!</definedName>
+    <definedName name="MotorVehicles">#REF!</definedName>
+    <definedName name="OfficeEquipment">#REF!</definedName>
+    <definedName name="OtheMedicalEquipment">#REF!</definedName>
+    <definedName name="OtherCommunication\TelecommunicationFacilities">#REF!</definedName>
+    <definedName name="OtherCommunicationEquipment">#REF!</definedName>
+    <definedName name="OtherDisasterResponseandRescue">#REF!</definedName>
+    <definedName name="OtherFloodControlSystemFacilities">#REF!</definedName>
+    <definedName name="OtherFurnitureFixturesandBooks">#REF!</definedName>
+    <definedName name="OtherICTEquipment">#REF!</definedName>
+    <definedName name="OtherInfrastructureAssets\Components">#REF!</definedName>
+    <definedName name="OtherMachineryEquipment">#REF!</definedName>
+    <definedName name="OtherOfficeEquipment">#REF!</definedName>
+    <definedName name="OtherPoliceandSecurityEquipment">#REF!</definedName>
+    <definedName name="OtherRoadNetworkFacilities">#REF!</definedName>
+    <definedName name="OtherStructures">#REF!</definedName>
+    <definedName name="OtherTransportationEquipment">#REF!</definedName>
+    <definedName name="Parks\Plazas\Monuments">#REF!</definedName>
+    <definedName name="PeripheralsandAuxiliaryEquipmentnecessarytoputthesystemintooperationalmode">#REF!</definedName>
+    <definedName name="PoliceandSecurityEquipment">#REF!</definedName>
+    <definedName name="PoliceEquipment">#REF!</definedName>
+    <definedName name="PreLoadedSoftwareOperatingSystemsincludedinthecostofthecomputerhardware">#REF!</definedName>
+    <definedName name="Printers">#REF!</definedName>
+    <definedName name="Radio">#REF!</definedName>
+    <definedName name="RiverWalls">#REF!</definedName>
+    <definedName name="RoadNetworks">#REF!</definedName>
+    <definedName name="Roads">#REF!</definedName>
+    <definedName name="Scanners">#REF!</definedName>
+    <definedName name="SchoolBuildings">#REF!</definedName>
+    <definedName name="Seawalls">#REF!</definedName>
+    <definedName name="SecurityCameras">#REF!</definedName>
+    <definedName name="Slaughterhouses">#REF!</definedName>
+    <definedName name="SpecializedEquipments">#REF!</definedName>
+    <definedName name="SurveyEquipments">#REF!</definedName>
+    <definedName name="TechnicalandScientificEquipment">#REF!</definedName>
+    <definedName name="TherapeuticEquipment">#REF!</definedName>
+    <definedName name="Towers">#REF!</definedName>
+    <definedName name="Transceivers">#REF!</definedName>
+    <definedName name="Transmitters">#REF!</definedName>
+    <definedName name="Truck">#REF!</definedName>
+    <definedName name="VolcanicEruptionRescueEquipment">#REF!</definedName>
+    <definedName name="WasteTreatmentPlants">#REF!</definedName>
+    <definedName name="Watercrafts">#REF!</definedName>
+    <definedName name="WaterSourceFacility">#REF!</definedName>
+    <definedName name="WaterSupplySystems">#REF!</definedName>
+    <definedName name="WaterTreatmentPlants">#REF!</definedName>
+    <definedName name="WeekdayOption">MATCH(WeekStart,Weekdays,0)+10</definedName>
+    <definedName name="Weekdays">{"Monday","Tuesday","Wednesday","Thursday","Friday","Saturday","Sunday"}</definedName>
+    <definedName name="WeekStart">#REF!</definedName>
+    <definedName name="WeekStartValue">IF(WeekStart="Monday",2,1)</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,6 +181,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
+    <t>REPORT ON THE PHYSICAL COUNT OF VEHICLES</t>
+  </si>
+  <si>
     <t>Custodian 
 Item 
 Number</t>
@@ -226,13 +374,7 @@
 Number</t>
   </si>
   <si>
-    <t>Department:</t>
-  </si>
-  <si>
     <t>Annex</t>
-  </si>
-  <si>
-    <t>REPORT ON THE PHYSICAL COUNT OF VEHICLES</t>
   </si>
   <si>
     <t>Old
@@ -240,16 +382,36 @@
 (in RPCPPE)</t>
   </si>
   <si>
-    <t>PAR / ICS / ARE / MR / RPCPPE</t>
+    <t>PAR / ICS / ARE / MR /RPCPPE</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Department:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -291,13 +453,14 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -418,9 +581,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -433,9 +594,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -448,9 +607,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -463,14 +620,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -478,17 +632,66 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -498,51 +701,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -556,6 +716,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -855,301 +1019,288 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C18FA19-E183-4684-9A16-B0E4B19C4ED4}">
-  <dimension ref="B2:AV14"/>
+  <dimension ref="B1:AV14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.77734375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="12.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.21875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="28.5546875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="14.77734375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="13.77734375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" style="3"/>
-    <col min="10" max="10" width="14.5546875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.21875" style="3" customWidth="1"/>
-    <col min="13" max="13" width="16" style="3" customWidth="1"/>
-    <col min="14" max="14" width="15.21875" style="3" customWidth="1"/>
-    <col min="15" max="15" width="8" style="3" customWidth="1"/>
-    <col min="16" max="16" width="16.21875" style="3" customWidth="1"/>
-    <col min="17" max="17" width="8.88671875" style="3"/>
-    <col min="18" max="18" width="18.6640625" style="3" customWidth="1"/>
-    <col min="19" max="19" width="8.88671875" style="3"/>
-    <col min="20" max="20" width="12.21875" style="3" customWidth="1"/>
-    <col min="21" max="21" width="7.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="23.77734375" style="3" customWidth="1"/>
-    <col min="23" max="23" width="8.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.88671875" style="3"/>
-    <col min="25" max="25" width="13.109375" style="12" customWidth="1"/>
-    <col min="26" max="26" width="13" style="3" customWidth="1"/>
-    <col min="27" max="28" width="8.88671875" style="3"/>
-    <col min="29" max="29" width="13.33203125" style="3" customWidth="1"/>
-    <col min="30" max="32" width="14.21875" style="12" customWidth="1"/>
-    <col min="33" max="33" width="11.33203125" style="3" customWidth="1"/>
-    <col min="34" max="35" width="8.88671875" style="3"/>
-    <col min="36" max="36" width="10.88671875" style="12" customWidth="1"/>
-    <col min="37" max="37" width="12.88671875" style="3" customWidth="1"/>
-    <col min="38" max="38" width="8.88671875" style="3"/>
-    <col min="39" max="39" width="12.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="16.21875" style="3" customWidth="1"/>
-    <col min="41" max="41" width="19.77734375" style="3" customWidth="1"/>
-    <col min="42" max="42" width="32" style="3" customWidth="1"/>
-    <col min="43" max="43" width="15.44140625" style="3" customWidth="1"/>
-    <col min="44" max="44" width="26.77734375" style="3" customWidth="1"/>
-    <col min="45" max="45" width="4.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="20.6640625" style="3" customWidth="1"/>
-    <col min="47" max="47" width="25.33203125" style="3" customWidth="1"/>
-    <col min="48" max="48" width="6" style="3" bestFit="1" customWidth="1"/>
-    <col min="49" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="2.77734375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="13" style="5" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.21875" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="5"/>
+    <col min="6" max="6" width="26.77734375" style="14" customWidth="1"/>
+    <col min="7" max="9" width="8.88671875" style="14"/>
+    <col min="10" max="10" width="7.5546875" style="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.33203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.88671875" style="14"/>
+    <col min="13" max="13" width="16" style="14" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" style="14"/>
+    <col min="15" max="15" width="5.44140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="8.88671875" style="14"/>
+    <col min="20" max="20" width="10.44140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.77734375" style="14" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.109375" style="14" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.88671875" style="14" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.88671875" style="14"/>
+    <col min="25" max="25" width="10.5546875" style="6" customWidth="1"/>
+    <col min="26" max="26" width="10.88671875" style="14" customWidth="1"/>
+    <col min="27" max="27" width="8.88671875" style="5"/>
+    <col min="28" max="28" width="8.88671875" style="14"/>
+    <col min="29" max="29" width="13.6640625" style="5" customWidth="1"/>
+    <col min="30" max="30" width="8.88671875" style="6"/>
+    <col min="31" max="31" width="11.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.44140625" style="6" customWidth="1"/>
+    <col min="33" max="33" width="11.33203125" style="14" customWidth="1"/>
+    <col min="34" max="35" width="8.88671875" style="5"/>
+    <col min="36" max="36" width="8.88671875" style="6"/>
+    <col min="37" max="37" width="8.88671875" style="14"/>
+    <col min="38" max="38" width="8.88671875" style="5"/>
+    <col min="39" max="41" width="8.88671875" style="14"/>
+    <col min="42" max="42" width="11.5546875" style="14" customWidth="1"/>
+    <col min="43" max="43" width="8.88671875" style="14"/>
+    <col min="44" max="44" width="19.109375" style="14" customWidth="1"/>
+    <col min="45" max="45" width="6.5546875" style="5" customWidth="1"/>
+    <col min="46" max="46" width="9.33203125" style="14" customWidth="1"/>
+    <col min="47" max="47" width="27.21875" style="14" customWidth="1"/>
+    <col min="48" max="48" width="8.88671875" style="14"/>
+    <col min="49" max="16384" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:48" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:48" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:48" s="8" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="7"/>
-      <c r="Y2" s="10"/>
-      <c r="AD2" s="10"/>
-      <c r="AE2" s="10"/>
-      <c r="AF2" s="10"/>
-      <c r="AJ2" s="10"/>
     </row>
-    <row r="3" spans="2:48" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="B3" s="8" t="s">
+    <row r="3" spans="2:48" s="9" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="B3" s="13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:48" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B4" s="10"/>
+    </row>
+    <row r="5" spans="2:48" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B5" s="10"/>
+    </row>
+    <row r="6" spans="2:48" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="11"/>
+    </row>
+    <row r="7" spans="2:48" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="11"/>
+    </row>
+    <row r="8" spans="2:48" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B8" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="15"/>
+    </row>
+    <row r="9" spans="2:48" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B9" s="10"/>
+    </row>
+    <row r="10" spans="2:48" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B10" s="11"/>
+    </row>
+    <row r="11" spans="2:48" s="2" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="12"/>
+    </row>
+    <row r="12" spans="2:48" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="X12" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y12" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="Y3" s="11"/>
-      <c r="AD3" s="11"/>
-      <c r="AE3" s="11"/>
-      <c r="AF3" s="11"/>
-      <c r="AJ3" s="11"/>
-    </row>
-    <row r="4" spans="2:48" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="1"/>
-    </row>
-    <row r="5" spans="2:48" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="1"/>
-    </row>
-    <row r="6" spans="2:48" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="1"/>
-    </row>
-    <row r="7" spans="2:48" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="1"/>
-    </row>
-    <row r="8" spans="2:48" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="9"/>
-    </row>
-    <row r="9" spans="2:48" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="1"/>
-      <c r="C9" s="9"/>
-    </row>
-    <row r="10" spans="2:48" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="1"/>
-      <c r="C10" s="9"/>
-    </row>
-    <row r="11" spans="2:48" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="12" spans="2:48" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q12" s="16"/>
-      <c r="R12" s="16"/>
-      <c r="S12" s="16"/>
-      <c r="T12" s="16"/>
-      <c r="U12" s="16"/>
-      <c r="V12" s="16"/>
-      <c r="W12" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="X12" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y12" s="22" t="s">
+      <c r="Z12" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA12" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB12" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC12" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD12" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE12" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF12" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG12" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI12" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ12" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK12" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="AL12" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="AM12" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="AN12" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="AO12" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="Z12" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA12" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB12" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC12" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="AD12" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="AE12" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF12" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG12" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="AH12" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI12" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="AJ12" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="AK12" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="AL12" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="AM12" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="AN12" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="AO12" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP12" s="16"/>
-      <c r="AQ12" s="16"/>
+      <c r="AP12" s="19"/>
+      <c r="AQ12" s="19"/>
       <c r="AR12" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="AS12" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="AT12" s="16" t="s">
+      <c r="AS12" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="AU12" s="27" t="s">
+      <c r="AT12" s="19" t="s">
         <v>29</v>
+      </c>
+      <c r="AU12" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="AV12" s="16" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="2:48" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="14"/>
-      <c r="C13" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>2</v>
+    <row r="13" spans="2:48" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="25"/>
+      <c r="C13" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>3</v>
       </c>
       <c r="E13" s="20"/>
       <c r="F13" s="20"/>
-      <c r="G13" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" s="17" t="s">
+      <c r="G13" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="I13" s="17" t="s">
+      <c r="H13" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="J13" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="K13" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="L13" s="17" t="s">
+      <c r="I13" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="J13" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="M13" s="17" t="s">
+      <c r="K13" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="N13" s="17" t="s">
+      <c r="M13" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="O13" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="P13" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q13" s="17" t="s">
+      <c r="N13" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="O13" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="P13" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="R13" s="17" t="s">
+      <c r="Q13" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="S13" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="T13" s="20" t="s">
+      <c r="R13" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="U13" s="20"/>
-      <c r="V13" s="20"/>
+      <c r="S13" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="T13" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="U13" s="22"/>
+      <c r="V13" s="22"/>
       <c r="W13" s="20"/>
       <c r="X13" s="20"/>
-      <c r="Y13" s="23"/>
+      <c r="Y13" s="22"/>
       <c r="Z13" s="20"/>
       <c r="AA13" s="20"/>
       <c r="AB13" s="20"/>
       <c r="AC13" s="20"/>
-      <c r="AD13" s="25"/>
-      <c r="AE13" s="23"/>
-      <c r="AF13" s="23"/>
-      <c r="AG13" s="17"/>
+      <c r="AD13" s="20"/>
+      <c r="AE13" s="22"/>
+      <c r="AF13" s="22"/>
+      <c r="AG13" s="22"/>
       <c r="AH13" s="20"/>
       <c r="AI13" s="20"/>
-      <c r="AJ13" s="25"/>
+      <c r="AJ13" s="20"/>
       <c r="AK13" s="20"/>
       <c r="AL13" s="20"/>
       <c r="AM13" s="20"/>
       <c r="AN13" s="20"/>
-      <c r="AO13" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="AP13" s="17" t="s">
+      <c r="AO13" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="AQ13" s="17" t="s">
+      <c r="AP13" s="22" t="s">
         <v>25</v>
       </c>
+      <c r="AQ13" s="22" t="s">
+        <v>26</v>
+      </c>
       <c r="AR13" s="20"/>
-      <c r="AS13" s="20"/>
-      <c r="AT13" s="20"/>
-      <c r="AU13" s="28"/>
-      <c r="AV13" s="20"/>
+      <c r="AS13" s="22"/>
+      <c r="AT13" s="22"/>
+      <c r="AU13" s="22"/>
+      <c r="AV13" s="17"/>
     </row>
-    <row r="14" spans="2:48" s="4" customFormat="1" ht="43.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="15"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
+    <row r="14" spans="2:48" s="2" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="26"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
       <c r="E14" s="21"/>
       <c r="F14" s="21"/>
       <c r="G14" s="21"/>
@@ -1160,77 +1311,55 @@
       <c r="L14" s="21"/>
       <c r="M14" s="21"/>
       <c r="N14" s="21"/>
-      <c r="O14" s="21"/>
+      <c r="O14" s="23"/>
       <c r="P14" s="21"/>
       <c r="Q14" s="21"/>
       <c r="R14" s="21"/>
       <c r="S14" s="21"/>
-      <c r="T14" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="U14" s="6" t="s">
+      <c r="T14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="V14" s="5" t="s">
-        <v>46</v>
+      <c r="U14" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="W14" s="21"/>
       <c r="X14" s="21"/>
-      <c r="Y14" s="24"/>
+      <c r="Y14" s="23"/>
       <c r="Z14" s="21"/>
       <c r="AA14" s="21"/>
       <c r="AB14" s="21"/>
       <c r="AC14" s="21"/>
-      <c r="AD14" s="26"/>
-      <c r="AE14" s="24"/>
-      <c r="AF14" s="24"/>
-      <c r="AG14" s="18"/>
+      <c r="AD14" s="21"/>
+      <c r="AE14" s="23"/>
+      <c r="AF14" s="23"/>
+      <c r="AG14" s="23"/>
       <c r="AH14" s="21"/>
       <c r="AI14" s="21"/>
-      <c r="AJ14" s="26"/>
+      <c r="AJ14" s="21"/>
       <c r="AK14" s="21"/>
       <c r="AL14" s="21"/>
       <c r="AM14" s="21"/>
       <c r="AN14" s="21"/>
-      <c r="AO14" s="21"/>
+      <c r="AO14" s="23"/>
       <c r="AP14" s="21"/>
       <c r="AQ14" s="21"/>
       <c r="AR14" s="21"/>
-      <c r="AS14" s="21"/>
-      <c r="AT14" s="21"/>
-      <c r="AU14" s="29"/>
-      <c r="AV14" s="21"/>
+      <c r="AS14" s="23"/>
+      <c r="AT14" s="23"/>
+      <c r="AU14" s="23"/>
+      <c r="AV14" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="AV12:AV14"/>
-    <mergeCell ref="AR12:AR14"/>
-    <mergeCell ref="AS12:AS14"/>
-    <mergeCell ref="AT12:AT14"/>
-    <mergeCell ref="AU12:AU14"/>
-    <mergeCell ref="AO12:AQ12"/>
-    <mergeCell ref="AG12:AG14"/>
-    <mergeCell ref="AH12:AH14"/>
-    <mergeCell ref="AI12:AI14"/>
-    <mergeCell ref="AJ12:AJ14"/>
-    <mergeCell ref="AO13:AO14"/>
-    <mergeCell ref="AP13:AP14"/>
-    <mergeCell ref="AQ13:AQ14"/>
-    <mergeCell ref="AK12:AK14"/>
-    <mergeCell ref="AL12:AL14"/>
-    <mergeCell ref="AM12:AM14"/>
-    <mergeCell ref="AN12:AN14"/>
-    <mergeCell ref="AF12:AF14"/>
-    <mergeCell ref="W12:W14"/>
-    <mergeCell ref="T13:V13"/>
-    <mergeCell ref="X12:X14"/>
-    <mergeCell ref="Y12:Y14"/>
-    <mergeCell ref="AA12:AA14"/>
-    <mergeCell ref="Z12:Z14"/>
-    <mergeCell ref="AB12:AB14"/>
-    <mergeCell ref="AC12:AC14"/>
-    <mergeCell ref="AD12:AD14"/>
-    <mergeCell ref="AE12:AE14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="C13:C14"/>
     <mergeCell ref="O13:O14"/>
     <mergeCell ref="G12:O12"/>
     <mergeCell ref="P12:V12"/>
@@ -1246,18 +1375,46 @@
     <mergeCell ref="L13:L14"/>
     <mergeCell ref="M13:M14"/>
     <mergeCell ref="N13:N14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="W12:W14"/>
+    <mergeCell ref="T13:V13"/>
+    <mergeCell ref="X12:X14"/>
+    <mergeCell ref="Y12:Y14"/>
+    <mergeCell ref="AB12:AB14"/>
+    <mergeCell ref="Z12:Z14"/>
+    <mergeCell ref="AA12:AA14"/>
+    <mergeCell ref="AO13:AO14"/>
+    <mergeCell ref="AP13:AP14"/>
+    <mergeCell ref="AQ13:AQ14"/>
+    <mergeCell ref="AC12:AC14"/>
+    <mergeCell ref="AN12:AN14"/>
+    <mergeCell ref="AO12:AQ12"/>
+    <mergeCell ref="AI12:AI14"/>
+    <mergeCell ref="AJ12:AJ14"/>
+    <mergeCell ref="AK12:AK14"/>
+    <mergeCell ref="AG12:AG14"/>
+    <mergeCell ref="AH12:AH14"/>
+    <mergeCell ref="AD12:AD14"/>
+    <mergeCell ref="AE12:AE14"/>
+    <mergeCell ref="AF12:AF14"/>
+    <mergeCell ref="AL12:AL14"/>
+    <mergeCell ref="AM12:AM14"/>
+    <mergeCell ref="AV12:AV14"/>
+    <mergeCell ref="AR12:AR14"/>
+    <mergeCell ref="AS12:AS14"/>
+    <mergeCell ref="AT12:AT14"/>
+    <mergeCell ref="AU12:AU14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DFE98289BC91294F829EFFD4DC549C76" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="19972903a613892b44bc7de177b9930c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="24f70235-d7ab-48ae-872a-f5e45d821dca" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="851bba6bbcd0ff4aaccc95eb8de2c74d" ns3:_="">
     <xsd:import namespace="24f70235-d7ab-48ae-872a-f5e45d821dca"/>
@@ -1407,12 +1564,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1423,6 +1574,22 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D6BA337-C593-4EF2-B090-937D907018AE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="24f70235-d7ab-48ae-872a-f5e45d821dca"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E727EF53-D248-4693-8734-5FECE57054A9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1440,22 +1607,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D6BA337-C593-4EF2-B090-937D907018AE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="24f70235-d7ab-48ae-872a-f5e45d821dca"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{961ECCB7-21B8-4C05-838A-3ADAC8FDED02}">
   <ds:schemaRefs>

--- a/iLgs/App_Data/CustodianVehiclesTemplate.xlsx
+++ b/iLgs/App_Data/CustodianVehiclesTemplate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Template  2025_04_22/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Tempalte 2025_06_24/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{4CCB3B42-D639-4A82-BB32-781160A643F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B137AD0-8150-4ED2-B121-4F96662E58F0}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{4CCB3B42-D639-4A82-BB32-781160A643F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9BE0AA0-695B-4340-ADAB-8881F3FB9AFD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="986" xr2:uid="{8F9EB15D-4C1E-42CC-8141-A131BDAE685A}"/>
   </bookViews>
@@ -412,7 +412,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -467,6 +470,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -620,10 +630,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -668,6 +679,22 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -692,6 +719,21 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -702,7 +744,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1034,288 +1077,360 @@
     <col min="12" max="12" width="8.88671875" style="14"/>
     <col min="13" max="13" width="16" style="14" customWidth="1"/>
     <col min="14" max="14" width="8.88671875" style="14"/>
-    <col min="15" max="15" width="5.44140625" style="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="8.88671875" style="14"/>
+    <col min="15" max="15" width="10.21875" style="14" customWidth="1"/>
+    <col min="16" max="16" width="8.88671875" style="14"/>
+    <col min="17" max="17" width="14.33203125" style="14" customWidth="1"/>
+    <col min="18" max="19" width="8.88671875" style="14"/>
     <col min="20" max="20" width="10.44140625" style="14" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.77734375" style="14" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.109375" style="14" customWidth="1"/>
     <col min="22" max="22" width="10.109375" style="14" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.88671875" style="14" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.88671875" style="14"/>
-    <col min="25" max="25" width="10.5546875" style="6" customWidth="1"/>
+    <col min="23" max="23" width="15.109375" style="14" customWidth="1"/>
+    <col min="24" max="24" width="14.6640625" style="14" customWidth="1"/>
+    <col min="25" max="25" width="10.5546875" style="20" customWidth="1"/>
     <col min="26" max="26" width="10.88671875" style="14" customWidth="1"/>
     <col min="27" max="27" width="8.88671875" style="5"/>
     <col min="28" max="28" width="8.88671875" style="14"/>
     <col min="29" max="29" width="13.6640625" style="5" customWidth="1"/>
-    <col min="30" max="30" width="8.88671875" style="6"/>
-    <col min="31" max="31" width="11.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.44140625" style="6" customWidth="1"/>
+    <col min="30" max="30" width="8.88671875" style="20"/>
+    <col min="31" max="31" width="11.33203125" style="20" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.44140625" style="20" customWidth="1"/>
     <col min="33" max="33" width="11.33203125" style="14" customWidth="1"/>
-    <col min="34" max="35" width="8.88671875" style="5"/>
-    <col min="36" max="36" width="8.88671875" style="6"/>
+    <col min="34" max="34" width="8.88671875" style="21"/>
+    <col min="35" max="35" width="8.88671875" style="5"/>
+    <col min="36" max="36" width="8.88671875" style="20"/>
     <col min="37" max="37" width="8.88671875" style="14"/>
     <col min="38" max="38" width="8.88671875" style="5"/>
-    <col min="39" max="41" width="8.88671875" style="14"/>
-    <col min="42" max="42" width="11.5546875" style="14" customWidth="1"/>
-    <col min="43" max="43" width="8.88671875" style="14"/>
+    <col min="39" max="39" width="8.88671875" style="14"/>
+    <col min="40" max="40" width="18.5546875" style="14" customWidth="1"/>
+    <col min="41" max="41" width="19.88671875" style="14" customWidth="1"/>
+    <col min="42" max="42" width="20.21875" style="14" customWidth="1"/>
+    <col min="43" max="43" width="21.109375" style="14" customWidth="1"/>
     <col min="44" max="44" width="19.109375" style="14" customWidth="1"/>
     <col min="45" max="45" width="6.5546875" style="5" customWidth="1"/>
     <col min="46" max="46" width="9.33203125" style="14" customWidth="1"/>
-    <col min="47" max="47" width="27.21875" style="14" customWidth="1"/>
+    <col min="47" max="47" width="35.33203125" style="14" customWidth="1"/>
     <col min="48" max="48" width="8.88671875" style="14"/>
     <col min="49" max="16384" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:48" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="1" spans="2:48" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Y1" s="16"/>
+      <c r="AD1" s="16"/>
+      <c r="AE1" s="16"/>
+      <c r="AF1" s="16"/>
+      <c r="AH1" s="16"/>
+      <c r="AJ1" s="16"/>
+    </row>
     <row r="2" spans="2:48" s="8" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="7"/>
+      <c r="Y2" s="17"/>
+      <c r="AD2" s="17"/>
+      <c r="AE2" s="17"/>
+      <c r="AF2" s="17"/>
+      <c r="AH2" s="17"/>
+      <c r="AJ2" s="17"/>
     </row>
     <row r="3" spans="2:48" s="9" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="B3" s="13" t="s">
         <v>0</v>
       </c>
+      <c r="Y3" s="18"/>
+      <c r="AD3" s="18"/>
+      <c r="AE3" s="18"/>
+      <c r="AF3" s="18"/>
+      <c r="AH3" s="18"/>
+      <c r="AJ3" s="18"/>
     </row>
     <row r="4" spans="2:48" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B4" s="10"/>
+      <c r="Y4" s="19"/>
+      <c r="AD4" s="19"/>
+      <c r="AE4" s="19"/>
+      <c r="AF4" s="19"/>
+      <c r="AH4" s="19"/>
+      <c r="AJ4" s="19"/>
     </row>
     <row r="5" spans="2:48" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="10"/>
+      <c r="Y5" s="19"/>
+      <c r="AD5" s="19"/>
+      <c r="AE5" s="19"/>
+      <c r="AF5" s="19"/>
+      <c r="AH5" s="19"/>
+      <c r="AJ5" s="19"/>
     </row>
     <row r="6" spans="2:48" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="11"/>
+      <c r="Y6" s="19"/>
+      <c r="AD6" s="19"/>
+      <c r="AE6" s="19"/>
+      <c r="AF6" s="19"/>
+      <c r="AH6" s="19"/>
+      <c r="AJ6" s="19"/>
     </row>
     <row r="7" spans="2:48" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7" s="11"/>
+      <c r="Y7" s="19"/>
+      <c r="AD7" s="19"/>
+      <c r="AE7" s="19"/>
+      <c r="AF7" s="19"/>
+      <c r="AH7" s="19"/>
+      <c r="AJ7" s="19"/>
     </row>
     <row r="8" spans="2:48" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B8" s="11" t="s">
         <v>53</v>
       </c>
       <c r="C8" s="15"/>
+      <c r="Y8" s="19"/>
+      <c r="AD8" s="19"/>
+      <c r="AE8" s="19"/>
+      <c r="AF8" s="19"/>
+      <c r="AH8" s="19"/>
+      <c r="AJ8" s="19"/>
     </row>
     <row r="9" spans="2:48" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B9" s="10"/>
+      <c r="Y9" s="19"/>
+      <c r="AD9" s="19"/>
+      <c r="AE9" s="19"/>
+      <c r="AF9" s="19"/>
+      <c r="AH9" s="19"/>
+      <c r="AJ9" s="19"/>
     </row>
     <row r="10" spans="2:48" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B10" s="11"/>
+      <c r="Y10" s="19"/>
+      <c r="AD10" s="19"/>
+      <c r="AE10" s="19"/>
+      <c r="AF10" s="19"/>
+      <c r="AH10" s="19"/>
+      <c r="AJ10" s="19"/>
     </row>
     <row r="11" spans="2:48" s="2" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="12"/>
+      <c r="Y11" s="19"/>
+      <c r="AD11" s="19"/>
+      <c r="AE11" s="19"/>
+      <c r="AF11" s="19"/>
+      <c r="AH11" s="19"/>
+      <c r="AJ11" s="19"/>
     </row>
     <row r="12" spans="2:48" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19" t="s">
+      <c r="D12" s="25"/>
+      <c r="E12" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="19" t="s">
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="Q12" s="19"/>
-      <c r="R12" s="19"/>
-      <c r="S12" s="19"/>
-      <c r="T12" s="19"/>
-      <c r="U12" s="19"/>
-      <c r="V12" s="19"/>
-      <c r="W12" s="19" t="s">
+      <c r="Q12" s="25"/>
+      <c r="R12" s="25"/>
+      <c r="S12" s="25"/>
+      <c r="T12" s="25"/>
+      <c r="U12" s="25"/>
+      <c r="V12" s="25"/>
+      <c r="W12" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="X12" s="19" t="s">
+      <c r="X12" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="Y12" s="19" t="s">
+      <c r="Y12" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="Z12" s="19" t="s">
+      <c r="Z12" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="AA12" s="19" t="s">
+      <c r="AA12" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="AB12" s="19" t="s">
+      <c r="AB12" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="AC12" s="19" t="s">
+      <c r="AC12" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="AD12" s="19" t="s">
+      <c r="AD12" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="AE12" s="19" t="s">
+      <c r="AE12" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="AF12" s="19" t="s">
+      <c r="AF12" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="AG12" s="19" t="s">
+      <c r="AG12" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="AH12" s="19" t="s">
+      <c r="AH12" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="AI12" s="19" t="s">
+      <c r="AI12" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="AJ12" s="19" t="s">
+      <c r="AJ12" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="AK12" s="19" t="s">
+      <c r="AK12" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="AL12" s="19" t="s">
+      <c r="AL12" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="AM12" s="19" t="s">
+      <c r="AM12" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="AN12" s="19" t="s">
+      <c r="AN12" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="AO12" s="19" t="s">
+      <c r="AO12" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="AP12" s="19"/>
-      <c r="AQ12" s="19"/>
-      <c r="AR12" s="19" t="s">
+      <c r="AP12" s="25"/>
+      <c r="AQ12" s="25"/>
+      <c r="AR12" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="AS12" s="19" t="s">
+      <c r="AS12" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="AT12" s="19" t="s">
+      <c r="AT12" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="AU12" s="19" t="s">
+      <c r="AU12" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="AV12" s="16" t="s">
+      <c r="AV12" s="22" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="13" spans="2:48" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="25"/>
-      <c r="C13" s="22" t="s">
+      <c r="B13" s="36"/>
+      <c r="C13" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="22" t="s">
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="I13" s="22" t="s">
+      <c r="I13" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="J13" s="22" t="s">
+      <c r="J13" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="K13" s="22" t="s">
+      <c r="K13" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="L13" s="22" t="s">
+      <c r="L13" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="M13" s="22" t="s">
+      <c r="M13" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="N13" s="22" t="s">
+      <c r="N13" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="O13" s="22" t="s">
+      <c r="O13" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="P13" s="22" t="s">
+      <c r="P13" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="Q13" s="22" t="s">
+      <c r="Q13" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="R13" s="22" t="s">
+      <c r="R13" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="S13" s="22" t="s">
+      <c r="S13" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="T13" s="22" t="s">
+      <c r="T13" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="U13" s="22"/>
-      <c r="V13" s="22"/>
-      <c r="W13" s="20"/>
-      <c r="X13" s="20"/>
-      <c r="Y13" s="22"/>
-      <c r="Z13" s="20"/>
-      <c r="AA13" s="20"/>
-      <c r="AB13" s="20"/>
-      <c r="AC13" s="20"/>
-      <c r="AD13" s="20"/>
-      <c r="AE13" s="22"/>
-      <c r="AF13" s="22"/>
-      <c r="AG13" s="22"/>
-      <c r="AH13" s="20"/>
-      <c r="AI13" s="20"/>
-      <c r="AJ13" s="20"/>
-      <c r="AK13" s="20"/>
-      <c r="AL13" s="20"/>
-      <c r="AM13" s="20"/>
-      <c r="AN13" s="20"/>
-      <c r="AO13" s="22" t="s">
+      <c r="U13" s="28"/>
+      <c r="V13" s="28"/>
+      <c r="W13" s="26"/>
+      <c r="X13" s="26"/>
+      <c r="Y13" s="33"/>
+      <c r="Z13" s="26"/>
+      <c r="AA13" s="26"/>
+      <c r="AB13" s="26"/>
+      <c r="AC13" s="26"/>
+      <c r="AD13" s="31"/>
+      <c r="AE13" s="33"/>
+      <c r="AF13" s="33"/>
+      <c r="AG13" s="28"/>
+      <c r="AH13" s="31"/>
+      <c r="AI13" s="26"/>
+      <c r="AJ13" s="31"/>
+      <c r="AK13" s="26"/>
+      <c r="AL13" s="26"/>
+      <c r="AM13" s="26"/>
+      <c r="AN13" s="26"/>
+      <c r="AO13" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="AP13" s="22" t="s">
+      <c r="AP13" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="AQ13" s="22" t="s">
+      <c r="AQ13" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="AR13" s="20"/>
-      <c r="AS13" s="22"/>
-      <c r="AT13" s="22"/>
-      <c r="AU13" s="22"/>
-      <c r="AV13" s="17"/>
+      <c r="AR13" s="26"/>
+      <c r="AS13" s="28"/>
+      <c r="AT13" s="28"/>
+      <c r="AU13" s="28"/>
+      <c r="AV13" s="23"/>
     </row>
     <row r="14" spans="2:48" s="2" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="26"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
-      <c r="M14" s="21"/>
-      <c r="N14" s="21"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="21"/>
-      <c r="Q14" s="21"/>
-      <c r="R14" s="21"/>
-      <c r="S14" s="21"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="27"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="27"/>
+      <c r="Q14" s="27"/>
+      <c r="R14" s="27"/>
+      <c r="S14" s="27"/>
       <c r="T14" s="3" t="s">
         <v>44</v>
       </c>
@@ -1325,32 +1440,32 @@
       <c r="V14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="W14" s="21"/>
-      <c r="X14" s="21"/>
-      <c r="Y14" s="23"/>
-      <c r="Z14" s="21"/>
-      <c r="AA14" s="21"/>
-      <c r="AB14" s="21"/>
-      <c r="AC14" s="21"/>
-      <c r="AD14" s="21"/>
-      <c r="AE14" s="23"/>
-      <c r="AF14" s="23"/>
-      <c r="AG14" s="23"/>
-      <c r="AH14" s="21"/>
-      <c r="AI14" s="21"/>
-      <c r="AJ14" s="21"/>
-      <c r="AK14" s="21"/>
-      <c r="AL14" s="21"/>
-      <c r="AM14" s="21"/>
-      <c r="AN14" s="21"/>
-      <c r="AO14" s="23"/>
-      <c r="AP14" s="21"/>
-      <c r="AQ14" s="21"/>
-      <c r="AR14" s="21"/>
-      <c r="AS14" s="23"/>
-      <c r="AT14" s="23"/>
-      <c r="AU14" s="23"/>
-      <c r="AV14" s="18"/>
+      <c r="W14" s="27"/>
+      <c r="X14" s="27"/>
+      <c r="Y14" s="34"/>
+      <c r="Z14" s="27"/>
+      <c r="AA14" s="27"/>
+      <c r="AB14" s="27"/>
+      <c r="AC14" s="27"/>
+      <c r="AD14" s="32"/>
+      <c r="AE14" s="34"/>
+      <c r="AF14" s="34"/>
+      <c r="AG14" s="29"/>
+      <c r="AH14" s="32"/>
+      <c r="AI14" s="27"/>
+      <c r="AJ14" s="32"/>
+      <c r="AK14" s="27"/>
+      <c r="AL14" s="27"/>
+      <c r="AM14" s="27"/>
+      <c r="AN14" s="27"/>
+      <c r="AO14" s="29"/>
+      <c r="AP14" s="27"/>
+      <c r="AQ14" s="27"/>
+      <c r="AR14" s="27"/>
+      <c r="AS14" s="29"/>
+      <c r="AT14" s="29"/>
+      <c r="AU14" s="29"/>
+      <c r="AV14" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="49">
